--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154172</v>
+        <v>122154188</v>
       </c>
       <c r="B19" t="n">
-        <v>5173</v>
+        <v>74747</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,25 +2754,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477879</v>
+        <v>477377</v>
       </c>
       <c r="R19" t="n">
-        <v>6951648</v>
+        <v>6951731</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154221</v>
+        <v>122154192</v>
       </c>
       <c r="B20" t="n">
-        <v>79727</v>
+        <v>79630</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2856,25 +2856,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477477</v>
+        <v>477446</v>
       </c>
       <c r="R20" t="n">
-        <v>6951466</v>
+        <v>6951749</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2946,10 +2946,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154206</v>
+        <v>122154185</v>
       </c>
       <c r="B21" t="n">
-        <v>78645</v>
+        <v>90797</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477411</v>
+        <v>477372</v>
       </c>
       <c r="R21" t="n">
-        <v>6951546</v>
+        <v>6951655</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154174</v>
+        <v>122154175</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
+        <v>90775</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477833</v>
+        <v>477793</v>
       </c>
       <c r="R22" t="n">
-        <v>6951669</v>
+        <v>6951655</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154198</v>
+        <v>122154201</v>
       </c>
       <c r="B23" t="n">
-        <v>79726</v>
+        <v>74739</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477617</v>
+        <v>477404</v>
       </c>
       <c r="R23" t="n">
-        <v>6951666</v>
+        <v>6951629</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154211</v>
+        <v>122154219</v>
       </c>
       <c r="B24" t="n">
-        <v>90726</v>
+        <v>79726</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477448</v>
+        <v>477495</v>
       </c>
       <c r="R24" t="n">
-        <v>6951476</v>
+        <v>6951463</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154219</v>
+        <v>122154200</v>
       </c>
       <c r="B25" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,21 +3370,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477495</v>
+        <v>477435</v>
       </c>
       <c r="R25" t="n">
-        <v>6951463</v>
+        <v>6951645</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154186</v>
+        <v>122154221</v>
       </c>
       <c r="B26" t="n">
-        <v>5173</v>
+        <v>79727</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3468,25 +3468,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477370</v>
+        <v>477477</v>
       </c>
       <c r="R26" t="n">
-        <v>6951711</v>
+        <v>6951466</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154225</v>
+        <v>122154172</v>
       </c>
       <c r="B27" t="n">
-        <v>79726</v>
+        <v>5173</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3570,25 +3570,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477572</v>
+        <v>477879</v>
       </c>
       <c r="R27" t="n">
-        <v>6951618</v>
+        <v>6951648</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154190</v>
+        <v>122154198</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>79726</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477407</v>
+        <v>477617</v>
       </c>
       <c r="R28" t="n">
-        <v>6951732</v>
+        <v>6951666</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154185</v>
+        <v>122154214</v>
       </c>
       <c r="B29" t="n">
-        <v>90797</v>
+        <v>79726</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3778,21 +3778,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477372</v>
+        <v>477421</v>
       </c>
       <c r="R29" t="n">
-        <v>6951655</v>
+        <v>6951454</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154203</v>
+        <v>122154170</v>
       </c>
       <c r="B30" t="n">
-        <v>90779</v>
+        <v>57485</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,38 +3876,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477381</v>
+        <v>477882</v>
       </c>
       <c r="R30" t="n">
-        <v>6951610</v>
+        <v>6951635</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3966,10 +3970,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154209</v>
+        <v>122154208</v>
       </c>
       <c r="B31" t="n">
-        <v>79755</v>
+        <v>79727</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3978,25 +3982,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4009,7 +4013,7 @@
         <v>477462</v>
       </c>
       <c r="R31" t="n">
-        <v>6951485</v>
+        <v>6951484</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4068,10 +4072,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154201</v>
+        <v>122154217</v>
       </c>
       <c r="B32" t="n">
-        <v>74739</v>
+        <v>57374</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4084,34 +4088,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477404</v>
+        <v>477473</v>
       </c>
       <c r="R32" t="n">
-        <v>6951629</v>
+        <v>6951436</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4170,10 +4178,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154200</v>
+        <v>122154227</v>
       </c>
       <c r="B33" t="n">
-        <v>78645</v>
+        <v>79726</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4186,21 +4194,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4210,10 +4218,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477435</v>
+        <v>477615</v>
       </c>
       <c r="R33" t="n">
-        <v>6951645</v>
+        <v>6951614</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4272,10 +4280,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154217</v>
+        <v>122154207</v>
       </c>
       <c r="B34" t="n">
-        <v>57374</v>
+        <v>74738</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4284,42 +4292,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477473</v>
+        <v>477445</v>
       </c>
       <c r="R34" t="n">
-        <v>6951436</v>
+        <v>6951570</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4378,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154170</v>
+        <v>122154171</v>
       </c>
       <c r="B35" t="n">
-        <v>57485</v>
+        <v>79726</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4390,42 +4394,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477882</v>
+        <v>477875</v>
       </c>
       <c r="R35" t="n">
-        <v>6951635</v>
+        <v>6951643</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154207</v>
+        <v>122154173</v>
       </c>
       <c r="B36" t="n">
-        <v>74738</v>
+        <v>78645</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4496,25 +4496,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477445</v>
+        <v>477825</v>
       </c>
       <c r="R36" t="n">
-        <v>6951570</v>
+        <v>6951660</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154218</v>
+        <v>122154203</v>
       </c>
       <c r="B37" t="n">
-        <v>98079</v>
+        <v>90779</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4598,25 +4598,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477479</v>
+        <v>477381</v>
       </c>
       <c r="R37" t="n">
-        <v>6951442</v>
+        <v>6951610</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154175</v>
+        <v>122154225</v>
       </c>
       <c r="B38" t="n">
-        <v>90775</v>
+        <v>79726</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4704,21 +4704,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477793</v>
+        <v>477572</v>
       </c>
       <c r="R38" t="n">
-        <v>6951655</v>
+        <v>6951618</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154188</v>
+        <v>122154224</v>
       </c>
       <c r="B39" t="n">
-        <v>74747</v>
+        <v>56587</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4802,25 +4802,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>102613</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477377</v>
+        <v>477538</v>
       </c>
       <c r="R39" t="n">
-        <v>6951731</v>
+        <v>6951618</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4892,10 +4892,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154191</v>
+        <v>122154197</v>
       </c>
       <c r="B40" t="n">
-        <v>98079</v>
+        <v>79755</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4908,21 +4908,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477424</v>
+        <v>477617</v>
       </c>
       <c r="R40" t="n">
-        <v>6951736</v>
+        <v>6951666</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154216</v>
+        <v>122154161</v>
       </c>
       <c r="B41" t="n">
-        <v>74747</v>
+        <v>79727</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5010,21 +5010,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477457</v>
+        <v>477944</v>
       </c>
       <c r="R41" t="n">
-        <v>6951419</v>
+        <v>6951693</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122154224</v>
+        <v>122154212</v>
       </c>
       <c r="B42" t="n">
-        <v>56587</v>
+        <v>91172</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5108,25 +5108,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102613</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5136,10 +5131,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477538</v>
+        <v>477420</v>
       </c>
       <c r="R42" t="n">
-        <v>6951618</v>
+        <v>6951455</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5180,6 +5175,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5198,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154177</v>
+        <v>122154213</v>
       </c>
       <c r="B43" t="n">
-        <v>78645</v>
+        <v>79755</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5210,25 +5206,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5238,10 +5234,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477767</v>
+        <v>477424</v>
       </c>
       <c r="R43" t="n">
-        <v>6951662</v>
+        <v>6951452</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5300,10 +5296,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154202</v>
+        <v>122154206</v>
       </c>
       <c r="B44" t="n">
-        <v>98079</v>
+        <v>78645</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5312,25 +5308,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5340,10 +5336,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477389</v>
+        <v>477411</v>
       </c>
       <c r="R44" t="n">
-        <v>6951610</v>
+        <v>6951546</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5402,10 +5398,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154212</v>
+        <v>122154191</v>
       </c>
       <c r="B45" t="n">
-        <v>91172</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5414,20 +5410,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6040186</v>
+        <v>220093</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5437,10 +5438,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477420</v>
+        <v>477424</v>
       </c>
       <c r="R45" t="n">
-        <v>6951455</v>
+        <v>6951736</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5481,7 +5482,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5500,10 +5500,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154220</v>
+        <v>122154205</v>
       </c>
       <c r="B46" t="n">
-        <v>79755</v>
+        <v>97129</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5516,21 +5516,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477476</v>
+        <v>477367</v>
       </c>
       <c r="R46" t="n">
-        <v>6951463</v>
+        <v>6951594</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5602,10 +5602,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154227</v>
+        <v>122154195</v>
       </c>
       <c r="B47" t="n">
-        <v>79726</v>
+        <v>74739</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5618,21 +5618,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477615</v>
+        <v>477495</v>
       </c>
       <c r="R47" t="n">
-        <v>6951614</v>
+        <v>6951727</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5704,10 +5704,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154208</v>
+        <v>122154186</v>
       </c>
       <c r="B48" t="n">
-        <v>79727</v>
+        <v>5173</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5716,25 +5716,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477462</v>
+        <v>477370</v>
       </c>
       <c r="R48" t="n">
-        <v>6951484</v>
+        <v>6951711</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154161</v>
+        <v>122154174</v>
       </c>
       <c r="B49" t="n">
-        <v>79727</v>
+        <v>79726</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477944</v>
+        <v>477833</v>
       </c>
       <c r="R49" t="n">
-        <v>6951693</v>
+        <v>6951669</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5908,10 +5908,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154195</v>
+        <v>122154202</v>
       </c>
       <c r="B50" t="n">
-        <v>74739</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5920,25 +5920,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>308</v>
+        <v>220093</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477495</v>
+        <v>477389</v>
       </c>
       <c r="R50" t="n">
-        <v>6951727</v>
+        <v>6951610</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6010,10 +6010,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154192</v>
+        <v>122154160</v>
       </c>
       <c r="B51" t="n">
-        <v>79630</v>
+        <v>98092</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6026,21 +6026,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477446</v>
+        <v>477847</v>
       </c>
       <c r="R51" t="n">
-        <v>6951749</v>
+        <v>6951679</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6112,10 +6112,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154171</v>
+        <v>122154211</v>
       </c>
       <c r="B52" t="n">
-        <v>79726</v>
+        <v>90726</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6128,21 +6128,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477875</v>
+        <v>477448</v>
       </c>
       <c r="R52" t="n">
-        <v>6951643</v>
+        <v>6951476</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6214,10 +6214,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154169</v>
+        <v>122154187</v>
       </c>
       <c r="B53" t="n">
-        <v>56576</v>
+        <v>5173</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6226,42 +6226,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477886</v>
+        <v>477368</v>
       </c>
       <c r="R53" t="n">
-        <v>6951641</v>
+        <v>6951718</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6422,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122154187</v>
+        <v>122154210</v>
       </c>
       <c r="B55" t="n">
-        <v>5173</v>
+        <v>79726</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6434,25 +6430,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6462,10 +6458,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477368</v>
+        <v>477464</v>
       </c>
       <c r="R55" t="n">
-        <v>6951718</v>
+        <v>6951483</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6524,7 +6520,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122154204</v>
+        <v>122154218</v>
       </c>
       <c r="B56" t="n">
         <v>98079</v>
@@ -6564,10 +6560,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477373</v>
+        <v>477479</v>
       </c>
       <c r="R56" t="n">
-        <v>6951613</v>
+        <v>6951442</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6626,10 +6622,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122154213</v>
+        <v>122154204</v>
       </c>
       <c r="B57" t="n">
-        <v>79755</v>
+        <v>98079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,21 +6638,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>220093</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6666,10 +6662,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477424</v>
+        <v>477373</v>
       </c>
       <c r="R57" t="n">
-        <v>6951452</v>
+        <v>6951613</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6728,10 +6724,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122154160</v>
+        <v>122154215</v>
       </c>
       <c r="B58" t="n">
-        <v>98092</v>
+        <v>56576</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6740,25 +6736,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6768,10 +6764,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477847</v>
+        <v>477438</v>
       </c>
       <c r="R58" t="n">
-        <v>6951679</v>
+        <v>6951412</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6830,10 +6826,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154173</v>
+        <v>122154216</v>
       </c>
       <c r="B59" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6846,21 +6842,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6870,10 +6866,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477825</v>
+        <v>477457</v>
       </c>
       <c r="R59" t="n">
-        <v>6951660</v>
+        <v>6951419</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6932,10 +6928,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154214</v>
+        <v>122154190</v>
       </c>
       <c r="B60" t="n">
-        <v>79726</v>
+        <v>98079</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6944,25 +6940,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6972,10 +6968,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477421</v>
+        <v>477407</v>
       </c>
       <c r="R60" t="n">
-        <v>6951454</v>
+        <v>6951732</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,10 +7030,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154205</v>
+        <v>122154220</v>
       </c>
       <c r="B61" t="n">
-        <v>97129</v>
+        <v>79755</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7050,21 +7046,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7074,10 +7070,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477367</v>
+        <v>477476</v>
       </c>
       <c r="R61" t="n">
-        <v>6951594</v>
+        <v>6951463</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7136,10 +7132,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154210</v>
+        <v>122154177</v>
       </c>
       <c r="B62" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7152,21 +7148,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7176,10 +7172,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477464</v>
+        <v>477767</v>
       </c>
       <c r="R62" t="n">
-        <v>6951483</v>
+        <v>6951662</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7238,7 +7234,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154197</v>
+        <v>122154209</v>
       </c>
       <c r="B63" t="n">
         <v>79755</v>
@@ -7278,10 +7274,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477617</v>
+        <v>477462</v>
       </c>
       <c r="R63" t="n">
-        <v>6951666</v>
+        <v>6951485</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7340,7 +7336,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154215</v>
+        <v>122154169</v>
       </c>
       <c r="B64" t="n">
         <v>56576</v>
@@ -7373,17 +7369,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477438</v>
+        <v>477886</v>
       </c>
       <c r="R64" t="n">
-        <v>6951412</v>
+        <v>6951641</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178235</v>
+        <v>122178236</v>
       </c>
       <c r="B65" t="n">
-        <v>79234</v>
+        <v>78645</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7458,21 +7458,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477573</v>
+        <v>477559</v>
       </c>
       <c r="R65" t="n">
-        <v>6951539</v>
+        <v>6951532</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7544,10 +7544,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178232</v>
+        <v>122178223</v>
       </c>
       <c r="B66" t="n">
-        <v>79726</v>
+        <v>94009</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7556,25 +7556,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2412</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477570</v>
+        <v>477540</v>
       </c>
       <c r="R66" t="n">
-        <v>6951563</v>
+        <v>6951613</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178231</v>
+        <v>122178229</v>
       </c>
       <c r="B67" t="n">
-        <v>79726</v>
+        <v>79762</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7658,25 +7658,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477585</v>
+        <v>477587</v>
       </c>
       <c r="R67" t="n">
-        <v>6951573</v>
+        <v>6951569</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178236</v>
+        <v>122178220</v>
       </c>
       <c r="B68" t="n">
-        <v>78645</v>
+        <v>79726</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7764,21 +7764,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477559</v>
+        <v>477556</v>
       </c>
       <c r="R68" t="n">
-        <v>6951532</v>
+        <v>6951549</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122172652</v>
+        <v>122178225</v>
       </c>
       <c r="B69" t="n">
-        <v>98079</v>
+        <v>97129</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220093</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477755</v>
+        <v>477580</v>
       </c>
       <c r="R69" t="n">
-        <v>6951671</v>
+        <v>6951617</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7940,22 +7940,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178244</v>
+        <v>122178238</v>
       </c>
       <c r="B70" t="n">
-        <v>79636</v>
+        <v>94201</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7964,25 +7964,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2080</v>
+        <v>2387</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7995,7 +7995,7 @@
         <v>477538</v>
       </c>
       <c r="R70" t="n">
-        <v>6951440</v>
+        <v>6951456</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122172653</v>
+        <v>122178227</v>
       </c>
       <c r="B71" t="n">
-        <v>90797</v>
+        <v>79726</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477642</v>
+        <v>477598</v>
       </c>
       <c r="R71" t="n">
-        <v>6951702</v>
+        <v>6951610</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8144,22 +8144,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178247</v>
+        <v>122178245</v>
       </c>
       <c r="B72" t="n">
-        <v>79726</v>
+        <v>74747</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8172,21 +8172,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477540</v>
+        <v>477542</v>
       </c>
       <c r="R72" t="n">
-        <v>6951433</v>
+        <v>6951443</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8258,7 +8258,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178227</v>
+        <v>122178243</v>
       </c>
       <c r="B73" t="n">
         <v>79726</v>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477598</v>
+        <v>477538</v>
       </c>
       <c r="R73" t="n">
-        <v>6951610</v>
+        <v>6951448</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178225</v>
+        <v>122178232</v>
       </c>
       <c r="B74" t="n">
-        <v>97129</v>
+        <v>79726</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8372,25 +8372,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477580</v>
+        <v>477570</v>
       </c>
       <c r="R74" t="n">
-        <v>6951617</v>
+        <v>6951563</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8462,7 +8462,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178243</v>
+        <v>122178234</v>
       </c>
       <c r="B75" t="n">
         <v>79726</v>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477538</v>
+        <v>477584</v>
       </c>
       <c r="R75" t="n">
-        <v>6951448</v>
+        <v>6951542</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122178223</v>
+        <v>122178235</v>
       </c>
       <c r="B76" t="n">
-        <v>94009</v>
+        <v>79234</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8576,25 +8576,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2412</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477540</v>
+        <v>477573</v>
       </c>
       <c r="R76" t="n">
-        <v>6951613</v>
+        <v>6951539</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122178238</v>
+        <v>122172654</v>
       </c>
       <c r="B77" t="n">
-        <v>94201</v>
+        <v>97129</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8682,21 +8682,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2387</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477538</v>
+        <v>477639</v>
       </c>
       <c r="R77" t="n">
-        <v>6951456</v>
+        <v>6951706</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8736,12 +8736,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8756,22 +8756,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122178228</v>
+        <v>122178226</v>
       </c>
       <c r="B78" t="n">
-        <v>79726</v>
+        <v>74739</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8784,21 +8784,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477590</v>
+        <v>477581</v>
       </c>
       <c r="R78" t="n">
-        <v>6951600</v>
+        <v>6951614</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122178220</v>
+        <v>122178231</v>
       </c>
       <c r="B79" t="n">
         <v>79726</v>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477556</v>
+        <v>477585</v>
       </c>
       <c r="R79" t="n">
-        <v>6951549</v>
+        <v>6951573</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8972,10 +8972,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122178242</v>
+        <v>122178244</v>
       </c>
       <c r="B80" t="n">
-        <v>74747</v>
+        <v>79636</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>2080</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477534</v>
+        <v>477538</v>
       </c>
       <c r="R80" t="n">
-        <v>6951448</v>
+        <v>6951440</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122172654</v>
+        <v>122172652</v>
       </c>
       <c r="B81" t="n">
-        <v>97129</v>
+        <v>98079</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9090,21 +9090,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477639</v>
+        <v>477755</v>
       </c>
       <c r="R81" t="n">
-        <v>6951706</v>
+        <v>6951671</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9176,10 +9176,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122178226</v>
+        <v>122178242</v>
       </c>
       <c r="B82" t="n">
-        <v>74739</v>
+        <v>74747</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9192,21 +9192,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477581</v>
+        <v>477534</v>
       </c>
       <c r="R82" t="n">
-        <v>6951614</v>
+        <v>6951448</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9278,10 +9278,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122178229</v>
+        <v>122178228</v>
       </c>
       <c r="B83" t="n">
-        <v>79762</v>
+        <v>79726</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9290,25 +9290,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477587</v>
+        <v>477590</v>
       </c>
       <c r="R83" t="n">
-        <v>6951569</v>
+        <v>6951600</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122178221</v>
+        <v>122178224</v>
       </c>
       <c r="B84" t="n">
-        <v>79726</v>
+        <v>94201</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9392,25 +9392,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477543</v>
+        <v>477572</v>
       </c>
       <c r="R84" t="n">
-        <v>6951588</v>
+        <v>6951626</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122178237</v>
+        <v>122172653</v>
       </c>
       <c r="B85" t="n">
-        <v>79726</v>
+        <v>90797</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9498,21 +9498,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477518</v>
+        <v>477642</v>
       </c>
       <c r="R85" t="n">
-        <v>6951490</v>
+        <v>6951702</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9552,12 +9552,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9572,19 +9572,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178246</v>
+        <v>122178237</v>
       </c>
       <c r="B86" t="n">
         <v>79726</v>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477535</v>
+        <v>477518</v>
       </c>
       <c r="R86" t="n">
-        <v>6951442</v>
+        <v>6951490</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178224</v>
+        <v>122178247</v>
       </c>
       <c r="B87" t="n">
-        <v>94201</v>
+        <v>79726</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9698,25 +9698,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477572</v>
+        <v>477540</v>
       </c>
       <c r="R87" t="n">
-        <v>6951626</v>
+        <v>6951433</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9788,7 +9788,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178234</v>
+        <v>122178221</v>
       </c>
       <c r="B88" t="n">
         <v>79726</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477584</v>
+        <v>477543</v>
       </c>
       <c r="R88" t="n">
-        <v>6951542</v>
+        <v>6951588</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9890,10 +9890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122178245</v>
+        <v>122172640</v>
       </c>
       <c r="B89" t="n">
-        <v>74747</v>
+        <v>79726</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477542</v>
+        <v>477949</v>
       </c>
       <c r="R89" t="n">
-        <v>6951443</v>
+        <v>6951706</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9960,12 +9960,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9980,22 +9980,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122178222</v>
+        <v>122178246</v>
       </c>
       <c r="B90" t="n">
-        <v>97129</v>
+        <v>79726</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10004,25 +10004,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477540</v>
+        <v>477535</v>
       </c>
       <c r="R90" t="n">
-        <v>6951594</v>
+        <v>6951442</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10094,10 +10094,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122172640</v>
+        <v>122178222</v>
       </c>
       <c r="B91" t="n">
-        <v>79726</v>
+        <v>97129</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10106,25 +10106,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>477949</v>
+        <v>477540</v>
       </c>
       <c r="R91" t="n">
-        <v>6951706</v>
+        <v>6951594</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10184,12 +10184,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -3048,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154175</v>
+        <v>122154201</v>
       </c>
       <c r="B22" t="n">
-        <v>90775</v>
+        <v>74739</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477793</v>
+        <v>477404</v>
       </c>
       <c r="R22" t="n">
-        <v>6951655</v>
+        <v>6951629</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154201</v>
+        <v>122154175</v>
       </c>
       <c r="B23" t="n">
-        <v>74739</v>
+        <v>90775</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477404</v>
+        <v>477793</v>
       </c>
       <c r="R23" t="n">
-        <v>6951629</v>
+        <v>6951655</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154170</v>
+        <v>122154208</v>
       </c>
       <c r="B30" t="n">
-        <v>57485</v>
+        <v>79727</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,42 +3876,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477882</v>
+        <v>477462</v>
       </c>
       <c r="R30" t="n">
-        <v>6951635</v>
+        <v>6951484</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3970,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154208</v>
+        <v>122154170</v>
       </c>
       <c r="B31" t="n">
-        <v>79727</v>
+        <v>57485</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,38 +3978,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477462</v>
+        <v>477882</v>
       </c>
       <c r="R31" t="n">
-        <v>6951484</v>
+        <v>6951635</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -7132,10 +7132,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154177</v>
+        <v>122154169</v>
       </c>
       <c r="B62" t="n">
-        <v>78645</v>
+        <v>56576</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7148,34 +7148,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477767</v>
+        <v>477886</v>
       </c>
       <c r="R62" t="n">
-        <v>6951662</v>
+        <v>6951641</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7336,10 +7340,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154169</v>
+        <v>122154177</v>
       </c>
       <c r="B64" t="n">
-        <v>56576</v>
+        <v>78645</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7352,38 +7356,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477886</v>
+        <v>477767</v>
       </c>
       <c r="R64" t="n">
-        <v>6951641</v>
+        <v>6951662</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -9584,7 +9584,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178237</v>
+        <v>122178247</v>
       </c>
       <c r="B86" t="n">
         <v>79726</v>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477518</v>
+        <v>477540</v>
       </c>
       <c r="R86" t="n">
-        <v>6951490</v>
+        <v>6951433</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9686,7 +9686,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178247</v>
+        <v>122178237</v>
       </c>
       <c r="B87" t="n">
         <v>79726</v>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477540</v>
+        <v>477518</v>
       </c>
       <c r="R87" t="n">
-        <v>6951433</v>
+        <v>6951490</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154188</v>
+        <v>122154191</v>
       </c>
       <c r="B19" t="n">
-        <v>74747</v>
+        <v>98089</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,25 +2754,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>220093</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477377</v>
+        <v>477424</v>
       </c>
       <c r="R19" t="n">
-        <v>6951731</v>
+        <v>6951736</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154192</v>
+        <v>122154206</v>
       </c>
       <c r="B20" t="n">
-        <v>79630</v>
+        <v>78646</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2856,25 +2856,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477446</v>
+        <v>477411</v>
       </c>
       <c r="R20" t="n">
-        <v>6951749</v>
+        <v>6951546</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2946,10 +2946,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154185</v>
+        <v>122154169</v>
       </c>
       <c r="B21" t="n">
-        <v>90797</v>
+        <v>56576</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2962,34 +2962,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477372</v>
+        <v>477886</v>
       </c>
       <c r="R21" t="n">
-        <v>6951655</v>
+        <v>6951641</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3048,10 +3052,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154201</v>
+        <v>122154221</v>
       </c>
       <c r="B22" t="n">
-        <v>74739</v>
+        <v>79728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,21 +3068,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,10 +3092,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477404</v>
+        <v>477477</v>
       </c>
       <c r="R22" t="n">
-        <v>6951629</v>
+        <v>6951466</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3150,10 +3154,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154175</v>
+        <v>122154170</v>
       </c>
       <c r="B23" t="n">
-        <v>90775</v>
+        <v>57485</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3162,38 +3166,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477793</v>
+        <v>477882</v>
       </c>
       <c r="R23" t="n">
-        <v>6951655</v>
+        <v>6951635</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3252,10 +3260,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154219</v>
+        <v>122154174</v>
       </c>
       <c r="B24" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3292,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477495</v>
+        <v>477833</v>
       </c>
       <c r="R24" t="n">
-        <v>6951463</v>
+        <v>6951669</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3354,10 +3362,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154200</v>
+        <v>122154215</v>
       </c>
       <c r="B25" t="n">
-        <v>78645</v>
+        <v>56576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,21 +3378,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3394,10 +3402,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477435</v>
+        <v>477438</v>
       </c>
       <c r="R25" t="n">
-        <v>6951645</v>
+        <v>6951412</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,10 +3464,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154221</v>
+        <v>122154185</v>
       </c>
       <c r="B26" t="n">
-        <v>79727</v>
+        <v>90807</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,21 +3480,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3496,10 +3504,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477477</v>
+        <v>477372</v>
       </c>
       <c r="R26" t="n">
-        <v>6951466</v>
+        <v>6951655</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3558,10 +3566,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154172</v>
+        <v>122154205</v>
       </c>
       <c r="B27" t="n">
-        <v>5173</v>
+        <v>97139</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3574,21 +3582,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3598,10 +3606,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477879</v>
+        <v>477367</v>
       </c>
       <c r="R27" t="n">
-        <v>6951648</v>
+        <v>6951594</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3660,10 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154198</v>
+        <v>122154204</v>
       </c>
       <c r="B28" t="n">
-        <v>79726</v>
+        <v>98089</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3672,25 +3680,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3700,10 +3708,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477617</v>
+        <v>477373</v>
       </c>
       <c r="R28" t="n">
-        <v>6951666</v>
+        <v>6951613</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3762,10 +3770,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154214</v>
+        <v>122154171</v>
       </c>
       <c r="B29" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3802,10 +3810,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477421</v>
+        <v>477875</v>
       </c>
       <c r="R29" t="n">
-        <v>6951454</v>
+        <v>6951643</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3864,10 +3872,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154208</v>
+        <v>122154224</v>
       </c>
       <c r="B30" t="n">
-        <v>79727</v>
+        <v>56587</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,25 +3884,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>102613</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3912,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477462</v>
+        <v>477538</v>
       </c>
       <c r="R30" t="n">
-        <v>6951484</v>
+        <v>6951618</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3966,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154170</v>
+        <v>122154225</v>
       </c>
       <c r="B31" t="n">
-        <v>57485</v>
+        <v>79727</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3978,42 +3986,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477882</v>
+        <v>477572</v>
       </c>
       <c r="R31" t="n">
-        <v>6951635</v>
+        <v>6951618</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4072,10 +4076,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154217</v>
+        <v>122154198</v>
       </c>
       <c r="B32" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,38 +4092,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477473</v>
+        <v>477617</v>
       </c>
       <c r="R32" t="n">
-        <v>6951436</v>
+        <v>6951666</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4178,10 +4178,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154227</v>
+        <v>122154210</v>
       </c>
       <c r="B33" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477615</v>
+        <v>477464</v>
       </c>
       <c r="R33" t="n">
-        <v>6951614</v>
+        <v>6951483</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4280,10 +4280,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154207</v>
+        <v>122154201</v>
       </c>
       <c r="B34" t="n">
-        <v>74738</v>
+        <v>74739</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,25 +4292,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477445</v>
+        <v>477404</v>
       </c>
       <c r="R34" t="n">
-        <v>6951570</v>
+        <v>6951629</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154171</v>
+        <v>122154207</v>
       </c>
       <c r="B35" t="n">
-        <v>79726</v>
+        <v>74738</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4394,25 +4394,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477875</v>
+        <v>477445</v>
       </c>
       <c r="R35" t="n">
-        <v>6951643</v>
+        <v>6951570</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154173</v>
+        <v>122154214</v>
       </c>
       <c r="B36" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477825</v>
+        <v>477421</v>
       </c>
       <c r="R36" t="n">
-        <v>6951660</v>
+        <v>6951454</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154203</v>
+        <v>122154161</v>
       </c>
       <c r="B37" t="n">
-        <v>90779</v>
+        <v>79728</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4602,21 +4602,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477381</v>
+        <v>477944</v>
       </c>
       <c r="R37" t="n">
-        <v>6951610</v>
+        <v>6951693</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154225</v>
+        <v>122154212</v>
       </c>
       <c r="B38" t="n">
-        <v>79726</v>
+        <v>91182</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4704,21 +4704,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4723,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477572</v>
+        <v>477420</v>
       </c>
       <c r="R38" t="n">
-        <v>6951618</v>
+        <v>6951455</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4772,6 +4767,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4790,10 +4786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154224</v>
+        <v>122154211</v>
       </c>
       <c r="B39" t="n">
-        <v>56587</v>
+        <v>90736</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4802,25 +4798,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102613</v>
+        <v>112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4830,10 +4826,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477538</v>
+        <v>477448</v>
       </c>
       <c r="R39" t="n">
-        <v>6951618</v>
+        <v>6951476</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4892,10 +4888,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154197</v>
+        <v>122154195</v>
       </c>
       <c r="B40" t="n">
-        <v>79755</v>
+        <v>74739</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4904,25 +4900,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4932,10 +4928,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477617</v>
+        <v>477495</v>
       </c>
       <c r="R40" t="n">
-        <v>6951666</v>
+        <v>6951727</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4994,10 +4990,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154161</v>
+        <v>122154188</v>
       </c>
       <c r="B41" t="n">
-        <v>79727</v>
+        <v>74747</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5010,21 +5006,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5034,10 +5030,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477944</v>
+        <v>477377</v>
       </c>
       <c r="R41" t="n">
-        <v>6951693</v>
+        <v>6951731</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5096,10 +5092,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122154212</v>
+        <v>122154227</v>
       </c>
       <c r="B42" t="n">
-        <v>91172</v>
+        <v>79727</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5112,16 +5108,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5131,10 +5132,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477420</v>
+        <v>477615</v>
       </c>
       <c r="R42" t="n">
-        <v>6951455</v>
+        <v>6951614</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5175,7 +5176,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154213</v>
+        <v>122154186</v>
       </c>
       <c r="B43" t="n">
-        <v>79755</v>
+        <v>5173</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5210,21 +5210,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477424</v>
+        <v>477370</v>
       </c>
       <c r="R43" t="n">
-        <v>6951452</v>
+        <v>6951711</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154206</v>
+        <v>122154200</v>
       </c>
       <c r="B44" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477411</v>
+        <v>477435</v>
       </c>
       <c r="R44" t="n">
-        <v>6951546</v>
+        <v>6951645</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154191</v>
+        <v>122154192</v>
       </c>
       <c r="B45" t="n">
-        <v>98079</v>
+        <v>79631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5414,21 +5414,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220093</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477424</v>
+        <v>477446</v>
       </c>
       <c r="R45" t="n">
-        <v>6951736</v>
+        <v>6951749</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5500,10 +5500,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154205</v>
+        <v>122154189</v>
       </c>
       <c r="B46" t="n">
-        <v>97129</v>
+        <v>74739</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5512,25 +5512,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477367</v>
+        <v>477405</v>
       </c>
       <c r="R46" t="n">
-        <v>6951594</v>
+        <v>6951731</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5602,10 +5602,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154195</v>
+        <v>122154173</v>
       </c>
       <c r="B47" t="n">
-        <v>74739</v>
+        <v>78646</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5618,21 +5618,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477495</v>
+        <v>477825</v>
       </c>
       <c r="R47" t="n">
-        <v>6951727</v>
+        <v>6951660</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5704,10 +5704,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154186</v>
+        <v>122154218</v>
       </c>
       <c r="B48" t="n">
-        <v>5173</v>
+        <v>98089</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5720,21 +5720,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220093</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477370</v>
+        <v>477479</v>
       </c>
       <c r="R48" t="n">
-        <v>6951711</v>
+        <v>6951442</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154174</v>
+        <v>122154187</v>
       </c>
       <c r="B49" t="n">
-        <v>79726</v>
+        <v>5173</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5818,25 +5818,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477833</v>
+        <v>477368</v>
       </c>
       <c r="R49" t="n">
-        <v>6951669</v>
+        <v>6951718</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5908,10 +5908,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154202</v>
+        <v>122154217</v>
       </c>
       <c r="B50" t="n">
-        <v>98079</v>
+        <v>57374</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5920,38 +5920,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477389</v>
+        <v>477473</v>
       </c>
       <c r="R50" t="n">
-        <v>6951610</v>
+        <v>6951436</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6010,10 +6014,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154160</v>
+        <v>122154219</v>
       </c>
       <c r="B51" t="n">
-        <v>98092</v>
+        <v>79727</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6022,25 +6026,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6050,10 +6054,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477847</v>
+        <v>477495</v>
       </c>
       <c r="R51" t="n">
-        <v>6951679</v>
+        <v>6951463</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6112,10 +6116,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154211</v>
+        <v>122154209</v>
       </c>
       <c r="B52" t="n">
-        <v>90726</v>
+        <v>79756</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6124,25 +6128,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6152,10 +6156,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477448</v>
+        <v>477462</v>
       </c>
       <c r="R52" t="n">
-        <v>6951476</v>
+        <v>6951485</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6214,10 +6218,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154187</v>
+        <v>122154216</v>
       </c>
       <c r="B53" t="n">
-        <v>5173</v>
+        <v>74747</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6226,25 +6230,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6254,10 +6258,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477368</v>
+        <v>477457</v>
       </c>
       <c r="R53" t="n">
-        <v>6951718</v>
+        <v>6951419</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6316,10 +6320,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122154189</v>
+        <v>122154197</v>
       </c>
       <c r="B54" t="n">
-        <v>74739</v>
+        <v>79756</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6328,25 +6332,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6356,10 +6360,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477405</v>
+        <v>477617</v>
       </c>
       <c r="R54" t="n">
-        <v>6951731</v>
+        <v>6951666</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6418,10 +6422,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122154210</v>
+        <v>122154160</v>
       </c>
       <c r="B55" t="n">
-        <v>79726</v>
+        <v>98102</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,25 +6434,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6458,10 +6462,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477464</v>
+        <v>477847</v>
       </c>
       <c r="R55" t="n">
-        <v>6951483</v>
+        <v>6951679</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6520,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122154218</v>
+        <v>122154202</v>
       </c>
       <c r="B56" t="n">
-        <v>98079</v>
+        <v>98089</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6560,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477479</v>
+        <v>477389</v>
       </c>
       <c r="R56" t="n">
-        <v>6951442</v>
+        <v>6951610</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6622,10 +6626,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122154204</v>
+        <v>122154208</v>
       </c>
       <c r="B57" t="n">
-        <v>98079</v>
+        <v>79728</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6634,25 +6638,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6662,10 +6666,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477373</v>
+        <v>477462</v>
       </c>
       <c r="R57" t="n">
-        <v>6951613</v>
+        <v>6951484</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6724,10 +6728,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122154215</v>
+        <v>122154220</v>
       </c>
       <c r="B58" t="n">
-        <v>56576</v>
+        <v>79756</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6736,25 +6740,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6764,10 +6768,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477438</v>
+        <v>477476</v>
       </c>
       <c r="R58" t="n">
-        <v>6951412</v>
+        <v>6951463</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6826,10 +6830,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154216</v>
+        <v>122154213</v>
       </c>
       <c r="B59" t="n">
-        <v>74747</v>
+        <v>79756</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6838,25 +6842,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6866,10 +6870,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477457</v>
+        <v>477424</v>
       </c>
       <c r="R59" t="n">
-        <v>6951419</v>
+        <v>6951452</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6928,10 +6932,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154190</v>
+        <v>122154175</v>
       </c>
       <c r="B60" t="n">
-        <v>98079</v>
+        <v>90785</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6940,25 +6944,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220093</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6968,10 +6972,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477407</v>
+        <v>477793</v>
       </c>
       <c r="R60" t="n">
-        <v>6951732</v>
+        <v>6951655</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7030,10 +7034,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154220</v>
+        <v>122154177</v>
       </c>
       <c r="B61" t="n">
-        <v>79755</v>
+        <v>78646</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7042,25 +7046,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7070,10 +7074,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477476</v>
+        <v>477767</v>
       </c>
       <c r="R61" t="n">
-        <v>6951463</v>
+        <v>6951662</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7132,10 +7136,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154169</v>
+        <v>122154190</v>
       </c>
       <c r="B62" t="n">
-        <v>56576</v>
+        <v>98089</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7144,42 +7148,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>220093</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477886</v>
+        <v>477407</v>
       </c>
       <c r="R62" t="n">
-        <v>6951641</v>
+        <v>6951732</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154209</v>
+        <v>122154203</v>
       </c>
       <c r="B63" t="n">
-        <v>79755</v>
+        <v>90789</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7250,25 +7250,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477462</v>
+        <v>477381</v>
       </c>
       <c r="R63" t="n">
-        <v>6951485</v>
+        <v>6951610</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154177</v>
+        <v>122154172</v>
       </c>
       <c r="B64" t="n">
-        <v>78645</v>
+        <v>5173</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477767</v>
+        <v>477879</v>
       </c>
       <c r="R64" t="n">
-        <v>6951662</v>
+        <v>6951648</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178236</v>
+        <v>122178225</v>
       </c>
       <c r="B65" t="n">
-        <v>78645</v>
+        <v>97139</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7454,25 +7454,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477559</v>
+        <v>477580</v>
       </c>
       <c r="R65" t="n">
-        <v>6951532</v>
+        <v>6951617</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7547,7 +7547,7 @@
         <v>122178223</v>
       </c>
       <c r="B66" t="n">
-        <v>94009</v>
+        <v>94019</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178229</v>
+        <v>122178245</v>
       </c>
       <c r="B67" t="n">
-        <v>79762</v>
+        <v>74747</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7658,25 +7658,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477587</v>
+        <v>477542</v>
       </c>
       <c r="R67" t="n">
-        <v>6951569</v>
+        <v>6951443</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178220</v>
+        <v>122178235</v>
       </c>
       <c r="B68" t="n">
-        <v>79726</v>
+        <v>79235</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7764,21 +7764,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477556</v>
+        <v>477573</v>
       </c>
       <c r="R68" t="n">
-        <v>6951549</v>
+        <v>6951539</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178225</v>
+        <v>122178229</v>
       </c>
       <c r="B69" t="n">
-        <v>97129</v>
+        <v>79763</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477580</v>
+        <v>477587</v>
       </c>
       <c r="R69" t="n">
-        <v>6951617</v>
+        <v>6951569</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178238</v>
+        <v>122178232</v>
       </c>
       <c r="B70" t="n">
-        <v>94201</v>
+        <v>79727</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7964,25 +7964,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477538</v>
+        <v>477570</v>
       </c>
       <c r="R70" t="n">
-        <v>6951456</v>
+        <v>6951563</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178227</v>
+        <v>122178237</v>
       </c>
       <c r="B71" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477598</v>
+        <v>477518</v>
       </c>
       <c r="R71" t="n">
-        <v>6951610</v>
+        <v>6951490</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178245</v>
+        <v>122178243</v>
       </c>
       <c r="B72" t="n">
-        <v>74747</v>
+        <v>79727</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8172,21 +8172,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477542</v>
+        <v>477538</v>
       </c>
       <c r="R72" t="n">
-        <v>6951443</v>
+        <v>6951448</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8258,10 +8258,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178243</v>
+        <v>122178231</v>
       </c>
       <c r="B73" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477538</v>
+        <v>477585</v>
       </c>
       <c r="R73" t="n">
-        <v>6951448</v>
+        <v>6951573</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178232</v>
+        <v>122178222</v>
       </c>
       <c r="B74" t="n">
-        <v>79726</v>
+        <v>97139</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8372,25 +8372,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477570</v>
+        <v>477540</v>
       </c>
       <c r="R74" t="n">
-        <v>6951563</v>
+        <v>6951594</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178234</v>
+        <v>122178221</v>
       </c>
       <c r="B75" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477584</v>
+        <v>477543</v>
       </c>
       <c r="R75" t="n">
-        <v>6951542</v>
+        <v>6951588</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122178235</v>
+        <v>122178227</v>
       </c>
       <c r="B76" t="n">
-        <v>79234</v>
+        <v>79727</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8580,21 +8580,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477573</v>
+        <v>477598</v>
       </c>
       <c r="R76" t="n">
-        <v>6951539</v>
+        <v>6951610</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122172654</v>
+        <v>122172653</v>
       </c>
       <c r="B77" t="n">
-        <v>97129</v>
+        <v>90807</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8678,25 +8678,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477639</v>
+        <v>477642</v>
       </c>
       <c r="R77" t="n">
-        <v>6951706</v>
+        <v>6951702</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8768,10 +8768,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122178226</v>
+        <v>122178220</v>
       </c>
       <c r="B78" t="n">
-        <v>74739</v>
+        <v>79727</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8784,21 +8784,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477581</v>
+        <v>477556</v>
       </c>
       <c r="R78" t="n">
-        <v>6951614</v>
+        <v>6951549</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122178231</v>
+        <v>122172640</v>
       </c>
       <c r="B79" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477585</v>
+        <v>477949</v>
       </c>
       <c r="R79" t="n">
-        <v>6951573</v>
+        <v>6951706</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8940,12 +8940,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8960,22 +8960,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122178244</v>
+        <v>122178246</v>
       </c>
       <c r="B80" t="n">
-        <v>79636</v>
+        <v>79727</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2080</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477538</v>
+        <v>477535</v>
       </c>
       <c r="R80" t="n">
-        <v>6951440</v>
+        <v>6951442</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122172652</v>
+        <v>122178242</v>
       </c>
       <c r="B81" t="n">
-        <v>98079</v>
+        <v>74747</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9086,25 +9086,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477755</v>
+        <v>477534</v>
       </c>
       <c r="R81" t="n">
-        <v>6951671</v>
+        <v>6951448</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9144,12 +9144,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9164,22 +9164,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122178242</v>
+        <v>122178244</v>
       </c>
       <c r="B82" t="n">
-        <v>74747</v>
+        <v>79637</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9192,21 +9192,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>2080</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477534</v>
+        <v>477538</v>
       </c>
       <c r="R82" t="n">
-        <v>6951448</v>
+        <v>6951440</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9278,10 +9278,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122178228</v>
+        <v>122178224</v>
       </c>
       <c r="B83" t="n">
-        <v>79726</v>
+        <v>94211</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9290,25 +9290,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477590</v>
+        <v>477572</v>
       </c>
       <c r="R83" t="n">
-        <v>6951600</v>
+        <v>6951626</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122178224</v>
+        <v>122178236</v>
       </c>
       <c r="B84" t="n">
-        <v>94201</v>
+        <v>78646</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9392,25 +9392,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477572</v>
+        <v>477559</v>
       </c>
       <c r="R84" t="n">
-        <v>6951626</v>
+        <v>6951532</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122172653</v>
+        <v>122178234</v>
       </c>
       <c r="B85" t="n">
-        <v>90797</v>
+        <v>79727</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9498,21 +9498,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477642</v>
+        <v>477584</v>
       </c>
       <c r="R85" t="n">
-        <v>6951702</v>
+        <v>6951542</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9552,12 +9552,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9572,12 +9572,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9587,7 +9587,7 @@
         <v>122178247</v>
       </c>
       <c r="B86" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178237</v>
+        <v>122178228</v>
       </c>
       <c r="B87" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477518</v>
+        <v>477590</v>
       </c>
       <c r="R87" t="n">
-        <v>6951490</v>
+        <v>6951600</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9788,10 +9788,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178221</v>
+        <v>122172652</v>
       </c>
       <c r="B88" t="n">
-        <v>79726</v>
+        <v>98089</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9800,25 +9800,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477543</v>
+        <v>477755</v>
       </c>
       <c r="R88" t="n">
-        <v>6951588</v>
+        <v>6951671</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9878,22 +9878,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122172640</v>
+        <v>122178226</v>
       </c>
       <c r="B89" t="n">
-        <v>79726</v>
+        <v>74739</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477949</v>
+        <v>477581</v>
       </c>
       <c r="R89" t="n">
-        <v>6951706</v>
+        <v>6951614</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9960,12 +9960,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9980,22 +9980,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122178246</v>
+        <v>122172654</v>
       </c>
       <c r="B90" t="n">
-        <v>79726</v>
+        <v>97139</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10004,25 +10004,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477535</v>
+        <v>477639</v>
       </c>
       <c r="R90" t="n">
-        <v>6951442</v>
+        <v>6951706</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10082,22 +10082,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122178222</v>
+        <v>122178238</v>
       </c>
       <c r="B91" t="n">
-        <v>97129</v>
+        <v>94211</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10110,21 +10110,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>2387</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>477540</v>
+        <v>477538</v>
       </c>
       <c r="R91" t="n">
-        <v>6951594</v>
+        <v>6951456</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154191</v>
+        <v>122154215</v>
       </c>
       <c r="B19" t="n">
-        <v>98089</v>
+        <v>56576</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,25 +2754,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220093</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477424</v>
+        <v>477438</v>
       </c>
       <c r="R19" t="n">
-        <v>6951736</v>
+        <v>6951412</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154206</v>
+        <v>122154173</v>
       </c>
       <c r="B20" t="n">
         <v>78646</v>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477411</v>
+        <v>477825</v>
       </c>
       <c r="R20" t="n">
-        <v>6951546</v>
+        <v>6951660</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2946,10 +2946,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154169</v>
+        <v>122154218</v>
       </c>
       <c r="B21" t="n">
-        <v>56576</v>
+        <v>98089</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2958,42 +2958,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>220093</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477886</v>
+        <v>477479</v>
       </c>
       <c r="R21" t="n">
-        <v>6951641</v>
+        <v>6951442</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3052,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154221</v>
+        <v>122154200</v>
       </c>
       <c r="B22" t="n">
-        <v>79728</v>
+        <v>78646</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3068,21 +3064,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3092,10 +3088,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477477</v>
+        <v>477435</v>
       </c>
       <c r="R22" t="n">
-        <v>6951466</v>
+        <v>6951645</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3260,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154174</v>
+        <v>122154201</v>
       </c>
       <c r="B24" t="n">
-        <v>79727</v>
+        <v>74739</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3276,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3300,10 +3296,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477833</v>
+        <v>477404</v>
       </c>
       <c r="R24" t="n">
-        <v>6951669</v>
+        <v>6951629</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3362,10 +3358,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154215</v>
+        <v>122154175</v>
       </c>
       <c r="B25" t="n">
-        <v>56576</v>
+        <v>90785</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3378,21 +3374,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3402,10 +3398,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477438</v>
+        <v>477793</v>
       </c>
       <c r="R25" t="n">
-        <v>6951412</v>
+        <v>6951655</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3464,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154185</v>
+        <v>122154203</v>
       </c>
       <c r="B26" t="n">
-        <v>90807</v>
+        <v>90789</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,21 +3476,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3504,10 +3500,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477372</v>
+        <v>477381</v>
       </c>
       <c r="R26" t="n">
-        <v>6951655</v>
+        <v>6951610</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3566,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154205</v>
+        <v>122154211</v>
       </c>
       <c r="B27" t="n">
-        <v>97139</v>
+        <v>90736</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,25 +3574,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3606,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477367</v>
+        <v>477448</v>
       </c>
       <c r="R27" t="n">
-        <v>6951594</v>
+        <v>6951476</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3668,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154204</v>
+        <v>122154188</v>
       </c>
       <c r="B28" t="n">
-        <v>98089</v>
+        <v>74747</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,25 +3676,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3708,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477373</v>
+        <v>477377</v>
       </c>
       <c r="R28" t="n">
-        <v>6951613</v>
+        <v>6951731</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3770,7 +3766,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154171</v>
+        <v>122154210</v>
       </c>
       <c r="B29" t="n">
         <v>79727</v>
@@ -3810,10 +3806,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477875</v>
+        <v>477464</v>
       </c>
       <c r="R29" t="n">
-        <v>6951643</v>
+        <v>6951483</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3872,10 +3868,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154224</v>
+        <v>122154197</v>
       </c>
       <c r="B30" t="n">
-        <v>56587</v>
+        <v>79756</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3888,21 +3884,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102613</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3912,10 +3908,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477538</v>
+        <v>477617</v>
       </c>
       <c r="R30" t="n">
-        <v>6951618</v>
+        <v>6951666</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3974,7 +3970,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154225</v>
+        <v>122154219</v>
       </c>
       <c r="B31" t="n">
         <v>79727</v>
@@ -4014,10 +4010,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477572</v>
+        <v>477495</v>
       </c>
       <c r="R31" t="n">
-        <v>6951618</v>
+        <v>6951463</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4076,10 +4072,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154198</v>
+        <v>122154172</v>
       </c>
       <c r="B32" t="n">
-        <v>79727</v>
+        <v>5173</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,25 +4084,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4116,10 +4112,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477617</v>
+        <v>477879</v>
       </c>
       <c r="R32" t="n">
-        <v>6951666</v>
+        <v>6951648</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4178,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154210</v>
+        <v>122154190</v>
       </c>
       <c r="B33" t="n">
-        <v>79727</v>
+        <v>98089</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,25 +4186,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4218,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477464</v>
+        <v>477407</v>
       </c>
       <c r="R33" t="n">
-        <v>6951483</v>
+        <v>6951732</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4280,10 +4276,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154201</v>
+        <v>122154212</v>
       </c>
       <c r="B34" t="n">
-        <v>74739</v>
+        <v>91182</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4296,21 +4292,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4320,10 +4311,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477404</v>
+        <v>477420</v>
       </c>
       <c r="R34" t="n">
-        <v>6951629</v>
+        <v>6951455</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4364,6 +4355,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4484,10 +4476,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154214</v>
+        <v>122154216</v>
       </c>
       <c r="B36" t="n">
-        <v>79727</v>
+        <v>74747</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4500,21 +4492,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4524,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477421</v>
+        <v>477457</v>
       </c>
       <c r="R36" t="n">
-        <v>6951454</v>
+        <v>6951419</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4586,10 +4578,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154161</v>
+        <v>122154195</v>
       </c>
       <c r="B37" t="n">
-        <v>79728</v>
+        <v>74739</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4602,21 +4594,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4626,10 +4618,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477944</v>
+        <v>477495</v>
       </c>
       <c r="R37" t="n">
-        <v>6951693</v>
+        <v>6951727</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4688,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154212</v>
+        <v>122154177</v>
       </c>
       <c r="B38" t="n">
-        <v>91182</v>
+        <v>78646</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4704,16 +4696,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4723,10 +4720,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477420</v>
+        <v>477767</v>
       </c>
       <c r="R38" t="n">
-        <v>6951455</v>
+        <v>6951662</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4767,7 +4764,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4786,10 +4782,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154211</v>
+        <v>122154224</v>
       </c>
       <c r="B39" t="n">
-        <v>90736</v>
+        <v>56587</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,25 +4794,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>112</v>
+        <v>102613</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4826,10 +4822,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477448</v>
+        <v>477538</v>
       </c>
       <c r="R39" t="n">
-        <v>6951476</v>
+        <v>6951618</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4888,10 +4884,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154195</v>
+        <v>122154221</v>
       </c>
       <c r="B40" t="n">
-        <v>74739</v>
+        <v>79728</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4904,21 +4900,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4928,10 +4924,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477495</v>
+        <v>477477</v>
       </c>
       <c r="R40" t="n">
-        <v>6951727</v>
+        <v>6951466</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4990,10 +4986,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154188</v>
+        <v>122154209</v>
       </c>
       <c r="B41" t="n">
-        <v>74747</v>
+        <v>79756</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5002,25 +4998,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5030,10 +5026,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477377</v>
+        <v>477462</v>
       </c>
       <c r="R41" t="n">
-        <v>6951731</v>
+        <v>6951485</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5092,10 +5088,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122154227</v>
+        <v>122154185</v>
       </c>
       <c r="B42" t="n">
-        <v>79727</v>
+        <v>90807</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5108,21 +5104,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5132,10 +5128,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477615</v>
+        <v>477372</v>
       </c>
       <c r="R42" t="n">
-        <v>6951614</v>
+        <v>6951655</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5194,10 +5190,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154186</v>
+        <v>122154217</v>
       </c>
       <c r="B43" t="n">
-        <v>5173</v>
+        <v>57374</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5206,38 +5202,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477370</v>
+        <v>477473</v>
       </c>
       <c r="R43" t="n">
-        <v>6951711</v>
+        <v>6951436</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154200</v>
+        <v>122154204</v>
       </c>
       <c r="B44" t="n">
-        <v>78646</v>
+        <v>98089</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5308,25 +5308,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477435</v>
+        <v>477373</v>
       </c>
       <c r="R44" t="n">
-        <v>6951645</v>
+        <v>6951613</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154192</v>
+        <v>122154171</v>
       </c>
       <c r="B45" t="n">
-        <v>79631</v>
+        <v>79727</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5410,25 +5410,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477446</v>
+        <v>477875</v>
       </c>
       <c r="R45" t="n">
-        <v>6951749</v>
+        <v>6951643</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5500,10 +5500,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154189</v>
+        <v>122154225</v>
       </c>
       <c r="B46" t="n">
-        <v>74739</v>
+        <v>79727</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5516,21 +5516,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477405</v>
+        <v>477572</v>
       </c>
       <c r="R46" t="n">
-        <v>6951731</v>
+        <v>6951618</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5602,10 +5602,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154173</v>
+        <v>122154214</v>
       </c>
       <c r="B47" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5618,21 +5618,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477825</v>
+        <v>477421</v>
       </c>
       <c r="R47" t="n">
-        <v>6951660</v>
+        <v>6951454</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5704,10 +5704,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154218</v>
+        <v>122154220</v>
       </c>
       <c r="B48" t="n">
-        <v>98089</v>
+        <v>79756</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5720,21 +5720,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477479</v>
+        <v>477476</v>
       </c>
       <c r="R48" t="n">
-        <v>6951442</v>
+        <v>6951463</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154187</v>
+        <v>122154186</v>
       </c>
       <c r="B49" t="n">
         <v>5173</v>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477368</v>
+        <v>477370</v>
       </c>
       <c r="R49" t="n">
-        <v>6951718</v>
+        <v>6951711</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5908,10 +5908,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154217</v>
+        <v>122154187</v>
       </c>
       <c r="B50" t="n">
-        <v>57374</v>
+        <v>5173</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5920,42 +5920,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477473</v>
+        <v>477368</v>
       </c>
       <c r="R50" t="n">
-        <v>6951436</v>
+        <v>6951718</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6014,7 +6010,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154219</v>
+        <v>122154174</v>
       </c>
       <c r="B51" t="n">
         <v>79727</v>
@@ -6054,10 +6050,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477495</v>
+        <v>477833</v>
       </c>
       <c r="R51" t="n">
-        <v>6951463</v>
+        <v>6951669</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6116,10 +6112,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154209</v>
+        <v>122154227</v>
       </c>
       <c r="B52" t="n">
-        <v>79756</v>
+        <v>79727</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6128,25 +6124,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6156,10 +6152,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477462</v>
+        <v>477615</v>
       </c>
       <c r="R52" t="n">
-        <v>6951485</v>
+        <v>6951614</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6218,10 +6214,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154216</v>
+        <v>122154205</v>
       </c>
       <c r="B53" t="n">
-        <v>74747</v>
+        <v>97139</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6230,25 +6226,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6258,10 +6254,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477457</v>
+        <v>477367</v>
       </c>
       <c r="R53" t="n">
-        <v>6951419</v>
+        <v>6951594</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6320,10 +6316,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122154197</v>
+        <v>122154192</v>
       </c>
       <c r="B54" t="n">
-        <v>79756</v>
+        <v>79631</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6336,21 +6332,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6360,10 +6356,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477617</v>
+        <v>477446</v>
       </c>
       <c r="R54" t="n">
-        <v>6951666</v>
+        <v>6951749</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6524,10 +6520,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122154202</v>
+        <v>122154213</v>
       </c>
       <c r="B56" t="n">
-        <v>98089</v>
+        <v>79756</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6540,21 +6536,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6564,10 +6560,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477389</v>
+        <v>477424</v>
       </c>
       <c r="R56" t="n">
-        <v>6951610</v>
+        <v>6951452</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6626,10 +6622,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122154208</v>
+        <v>122154198</v>
       </c>
       <c r="B57" t="n">
-        <v>79728</v>
+        <v>79727</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6642,21 +6638,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6666,10 +6662,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477462</v>
+        <v>477617</v>
       </c>
       <c r="R57" t="n">
-        <v>6951484</v>
+        <v>6951666</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6728,10 +6724,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122154220</v>
+        <v>122154202</v>
       </c>
       <c r="B58" t="n">
-        <v>79756</v>
+        <v>98089</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6744,21 +6740,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>220093</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6768,10 +6764,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477476</v>
+        <v>477389</v>
       </c>
       <c r="R58" t="n">
-        <v>6951463</v>
+        <v>6951610</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6830,10 +6826,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154213</v>
+        <v>122154161</v>
       </c>
       <c r="B59" t="n">
-        <v>79756</v>
+        <v>79728</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6842,25 +6838,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6870,10 +6866,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477424</v>
+        <v>477944</v>
       </c>
       <c r="R59" t="n">
-        <v>6951452</v>
+        <v>6951693</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6932,10 +6928,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154175</v>
+        <v>122154208</v>
       </c>
       <c r="B60" t="n">
-        <v>90785</v>
+        <v>79728</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6948,21 +6944,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6972,10 +6968,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477793</v>
+        <v>477462</v>
       </c>
       <c r="R60" t="n">
-        <v>6951655</v>
+        <v>6951484</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,10 +7030,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154177</v>
+        <v>122154189</v>
       </c>
       <c r="B61" t="n">
-        <v>78646</v>
+        <v>74739</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7050,21 +7046,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7074,10 +7070,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477767</v>
+        <v>477405</v>
       </c>
       <c r="R61" t="n">
-        <v>6951662</v>
+        <v>6951731</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7136,10 +7132,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154190</v>
+        <v>122154206</v>
       </c>
       <c r="B62" t="n">
-        <v>98089</v>
+        <v>78646</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7148,25 +7144,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7176,10 +7172,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477407</v>
+        <v>477411</v>
       </c>
       <c r="R62" t="n">
-        <v>6951732</v>
+        <v>6951546</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7238,10 +7234,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154203</v>
+        <v>122154169</v>
       </c>
       <c r="B63" t="n">
-        <v>90789</v>
+        <v>56576</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7254,34 +7250,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477381</v>
+        <v>477886</v>
       </c>
       <c r="R63" t="n">
-        <v>6951610</v>
+        <v>6951641</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154172</v>
+        <v>122154191</v>
       </c>
       <c r="B64" t="n">
-        <v>5173</v>
+        <v>98089</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7356,21 +7356,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>220093</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477879</v>
+        <v>477424</v>
       </c>
       <c r="R64" t="n">
-        <v>6951648</v>
+        <v>6951736</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178225</v>
+        <v>122178231</v>
       </c>
       <c r="B65" t="n">
-        <v>97139</v>
+        <v>79727</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7454,25 +7454,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477580</v>
+        <v>477585</v>
       </c>
       <c r="R65" t="n">
-        <v>6951617</v>
+        <v>6951573</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7544,10 +7544,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178223</v>
+        <v>122178238</v>
       </c>
       <c r="B66" t="n">
-        <v>94019</v>
+        <v>94211</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2412</v>
+        <v>2387</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477540</v>
+        <v>477538</v>
       </c>
       <c r="R66" t="n">
-        <v>6951613</v>
+        <v>6951456</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178245</v>
+        <v>122172654</v>
       </c>
       <c r="B67" t="n">
-        <v>74747</v>
+        <v>97139</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7658,25 +7658,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477542</v>
+        <v>477639</v>
       </c>
       <c r="R67" t="n">
-        <v>6951443</v>
+        <v>6951706</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,22 +7736,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178235</v>
+        <v>122178234</v>
       </c>
       <c r="B68" t="n">
-        <v>79235</v>
+        <v>79727</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7764,21 +7764,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477573</v>
+        <v>477584</v>
       </c>
       <c r="R68" t="n">
-        <v>6951539</v>
+        <v>6951542</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178237</v>
+        <v>122178244</v>
       </c>
       <c r="B71" t="n">
-        <v>79727</v>
+        <v>79637</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>2080</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477518</v>
+        <v>477538</v>
       </c>
       <c r="R71" t="n">
-        <v>6951490</v>
+        <v>6951440</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178243</v>
+        <v>122178224</v>
       </c>
       <c r="B72" t="n">
-        <v>79727</v>
+        <v>94211</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8168,25 +8168,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477538</v>
+        <v>477572</v>
       </c>
       <c r="R72" t="n">
-        <v>6951448</v>
+        <v>6951626</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8258,10 +8258,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178231</v>
+        <v>122172653</v>
       </c>
       <c r="B73" t="n">
-        <v>79727</v>
+        <v>90807</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8274,21 +8274,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477585</v>
+        <v>477642</v>
       </c>
       <c r="R73" t="n">
-        <v>6951573</v>
+        <v>6951702</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8348,22 +8348,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178222</v>
+        <v>122178221</v>
       </c>
       <c r="B74" t="n">
-        <v>97139</v>
+        <v>79727</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8372,25 +8372,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477540</v>
+        <v>477543</v>
       </c>
       <c r="R74" t="n">
-        <v>6951594</v>
+        <v>6951588</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8462,7 +8462,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178221</v>
+        <v>122172640</v>
       </c>
       <c r="B75" t="n">
         <v>79727</v>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477543</v>
+        <v>477949</v>
       </c>
       <c r="R75" t="n">
-        <v>6951588</v>
+        <v>6951706</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8552,22 +8552,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122178227</v>
+        <v>122178235</v>
       </c>
       <c r="B76" t="n">
-        <v>79727</v>
+        <v>79235</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8580,21 +8580,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477598</v>
+        <v>477573</v>
       </c>
       <c r="R76" t="n">
-        <v>6951610</v>
+        <v>6951539</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122172653</v>
+        <v>122178226</v>
       </c>
       <c r="B77" t="n">
-        <v>90807</v>
+        <v>74739</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8682,21 +8682,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477642</v>
+        <v>477581</v>
       </c>
       <c r="R77" t="n">
-        <v>6951702</v>
+        <v>6951614</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8736,12 +8736,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8756,22 +8756,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122178220</v>
+        <v>122178223</v>
       </c>
       <c r="B78" t="n">
-        <v>79727</v>
+        <v>94019</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8780,25 +8780,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>2412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477556</v>
+        <v>477540</v>
       </c>
       <c r="R78" t="n">
-        <v>6951549</v>
+        <v>6951613</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122172640</v>
+        <v>122178236</v>
       </c>
       <c r="B79" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8886,21 +8886,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477949</v>
+        <v>477559</v>
       </c>
       <c r="R79" t="n">
-        <v>6951706</v>
+        <v>6951532</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8940,12 +8940,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8960,22 +8960,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122178246</v>
+        <v>122178222</v>
       </c>
       <c r="B80" t="n">
-        <v>79727</v>
+        <v>97139</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8984,25 +8984,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477535</v>
+        <v>477540</v>
       </c>
       <c r="R80" t="n">
-        <v>6951442</v>
+        <v>6951594</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122178242</v>
+        <v>122178228</v>
       </c>
       <c r="B81" t="n">
-        <v>74747</v>
+        <v>79727</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9090,21 +9090,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477534</v>
+        <v>477590</v>
       </c>
       <c r="R81" t="n">
-        <v>6951448</v>
+        <v>6951600</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9176,10 +9176,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122178244</v>
+        <v>122172652</v>
       </c>
       <c r="B82" t="n">
-        <v>79637</v>
+        <v>98089</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9188,25 +9188,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2080</v>
+        <v>220093</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477538</v>
+        <v>477755</v>
       </c>
       <c r="R82" t="n">
-        <v>6951440</v>
+        <v>6951671</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9246,12 +9246,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9266,22 +9266,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122178224</v>
+        <v>122178246</v>
       </c>
       <c r="B83" t="n">
-        <v>94211</v>
+        <v>79727</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9290,25 +9290,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477572</v>
+        <v>477535</v>
       </c>
       <c r="R83" t="n">
-        <v>6951626</v>
+        <v>6951442</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122178236</v>
+        <v>122178225</v>
       </c>
       <c r="B84" t="n">
-        <v>78646</v>
+        <v>97139</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9392,25 +9392,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477559</v>
+        <v>477580</v>
       </c>
       <c r="R84" t="n">
-        <v>6951532</v>
+        <v>6951617</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9482,7 +9482,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122178234</v>
+        <v>122178247</v>
       </c>
       <c r="B85" t="n">
         <v>79727</v>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477584</v>
+        <v>477540</v>
       </c>
       <c r="R85" t="n">
-        <v>6951542</v>
+        <v>6951433</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178247</v>
+        <v>122178245</v>
       </c>
       <c r="B86" t="n">
-        <v>79727</v>
+        <v>74747</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477540</v>
+        <v>477542</v>
       </c>
       <c r="R86" t="n">
-        <v>6951433</v>
+        <v>6951443</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178228</v>
+        <v>122178242</v>
       </c>
       <c r="B87" t="n">
-        <v>79727</v>
+        <v>74747</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477590</v>
+        <v>477534</v>
       </c>
       <c r="R87" t="n">
-        <v>6951600</v>
+        <v>6951448</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9788,10 +9788,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122172652</v>
+        <v>122178220</v>
       </c>
       <c r="B88" t="n">
-        <v>98089</v>
+        <v>79727</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9800,25 +9800,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477755</v>
+        <v>477556</v>
       </c>
       <c r="R88" t="n">
-        <v>6951671</v>
+        <v>6951549</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9878,22 +9878,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122178226</v>
+        <v>122178227</v>
       </c>
       <c r="B89" t="n">
-        <v>74739</v>
+        <v>79727</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477581</v>
+        <v>477598</v>
       </c>
       <c r="R89" t="n">
-        <v>6951614</v>
+        <v>6951610</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122172654</v>
+        <v>122178237</v>
       </c>
       <c r="B90" t="n">
-        <v>97139</v>
+        <v>79727</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10004,25 +10004,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477639</v>
+        <v>477518</v>
       </c>
       <c r="R90" t="n">
-        <v>6951706</v>
+        <v>6951490</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10082,22 +10082,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122178238</v>
+        <v>122178243</v>
       </c>
       <c r="B91" t="n">
-        <v>94211</v>
+        <v>79727</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10106,25 +10106,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
         <v>477538</v>
       </c>
       <c r="R91" t="n">
-        <v>6951456</v>
+        <v>6951448</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -6010,10 +6010,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154174</v>
+        <v>122154192</v>
       </c>
       <c r="B51" t="n">
-        <v>79727</v>
+        <v>79631</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6022,25 +6022,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477833</v>
+        <v>477446</v>
       </c>
       <c r="R51" t="n">
-        <v>6951669</v>
+        <v>6951749</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6112,7 +6112,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154227</v>
+        <v>122154174</v>
       </c>
       <c r="B52" t="n">
         <v>79727</v>
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477615</v>
+        <v>477833</v>
       </c>
       <c r="R52" t="n">
-        <v>6951614</v>
+        <v>6951669</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6214,10 +6214,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154205</v>
+        <v>122154227</v>
       </c>
       <c r="B53" t="n">
-        <v>97139</v>
+        <v>79727</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6226,25 +6226,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477367</v>
+        <v>477615</v>
       </c>
       <c r="R53" t="n">
-        <v>6951594</v>
+        <v>6951614</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6316,10 +6316,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122154192</v>
+        <v>122154205</v>
       </c>
       <c r="B54" t="n">
-        <v>79631</v>
+        <v>97139</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6332,21 +6332,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477446</v>
+        <v>477367</v>
       </c>
       <c r="R54" t="n">
-        <v>6951749</v>
+        <v>6951594</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154215</v>
+        <v>122154169</v>
       </c>
       <c r="B19" t="n">
-        <v>56576</v>
+        <v>56581</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2775,17 +2775,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477438</v>
+        <v>477886</v>
       </c>
       <c r="R19" t="n">
-        <v>6951412</v>
+        <v>6951641</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2844,10 +2848,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154173</v>
+        <v>122154198</v>
       </c>
       <c r="B20" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2860,21 +2864,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2884,10 +2888,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477825</v>
+        <v>477617</v>
       </c>
       <c r="R20" t="n">
-        <v>6951660</v>
+        <v>6951666</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2946,10 +2950,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154218</v>
+        <v>122154204</v>
       </c>
       <c r="B21" t="n">
-        <v>98089</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2986,10 +2990,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477479</v>
+        <v>477373</v>
       </c>
       <c r="R21" t="n">
-        <v>6951442</v>
+        <v>6951613</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3048,10 +3052,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154200</v>
+        <v>122154191</v>
       </c>
       <c r="B22" t="n">
-        <v>78646</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3060,25 +3064,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,10 +3092,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477435</v>
+        <v>477424</v>
       </c>
       <c r="R22" t="n">
-        <v>6951645</v>
+        <v>6951736</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3150,10 +3154,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154170</v>
+        <v>122154212</v>
       </c>
       <c r="B23" t="n">
-        <v>57485</v>
+        <v>91194</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3162,42 +3166,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477882</v>
+        <v>477420</v>
       </c>
       <c r="R23" t="n">
-        <v>6951635</v>
+        <v>6951455</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3238,6 +3233,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154201</v>
+        <v>122154189</v>
       </c>
       <c r="B24" t="n">
-        <v>74739</v>
+        <v>74744</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3296,10 +3292,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477404</v>
+        <v>477405</v>
       </c>
       <c r="R24" t="n">
-        <v>6951629</v>
+        <v>6951731</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154175</v>
+        <v>122154172</v>
       </c>
       <c r="B25" t="n">
-        <v>90785</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,25 +3366,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3398,10 +3394,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477793</v>
+        <v>477879</v>
       </c>
       <c r="R25" t="n">
-        <v>6951655</v>
+        <v>6951648</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3460,10 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154203</v>
+        <v>122154217</v>
       </c>
       <c r="B26" t="n">
-        <v>90789</v>
+        <v>57379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,34 +3472,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477381</v>
+        <v>477473</v>
       </c>
       <c r="R26" t="n">
-        <v>6951610</v>
+        <v>6951436</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3565,7 +3565,7 @@
         <v>122154211</v>
       </c>
       <c r="B27" t="n">
-        <v>90736</v>
+        <v>90748</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154188</v>
+        <v>122154208</v>
       </c>
       <c r="B28" t="n">
-        <v>74747</v>
+        <v>79733</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477377</v>
+        <v>477462</v>
       </c>
       <c r="R28" t="n">
-        <v>6951731</v>
+        <v>6951484</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154210</v>
+        <v>122154195</v>
       </c>
       <c r="B29" t="n">
-        <v>79727</v>
+        <v>74744</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3782,21 +3782,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477464</v>
+        <v>477495</v>
       </c>
       <c r="R29" t="n">
-        <v>6951483</v>
+        <v>6951727</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154197</v>
+        <v>122154161</v>
       </c>
       <c r="B30" t="n">
-        <v>79756</v>
+        <v>79733</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3880,25 +3880,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477617</v>
+        <v>477944</v>
       </c>
       <c r="R30" t="n">
-        <v>6951666</v>
+        <v>6951693</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3970,10 +3970,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154219</v>
+        <v>122154214</v>
       </c>
       <c r="B31" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477495</v>
+        <v>477421</v>
       </c>
       <c r="R31" t="n">
-        <v>6951463</v>
+        <v>6951454</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4072,10 +4072,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154172</v>
+        <v>122154175</v>
       </c>
       <c r="B32" t="n">
-        <v>5173</v>
+        <v>90797</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4084,25 +4084,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477879</v>
+        <v>477793</v>
       </c>
       <c r="R32" t="n">
-        <v>6951648</v>
+        <v>6951655</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154190</v>
+        <v>122154200</v>
       </c>
       <c r="B33" t="n">
-        <v>98089</v>
+        <v>78651</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4186,25 +4186,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477407</v>
+        <v>477435</v>
       </c>
       <c r="R33" t="n">
-        <v>6951732</v>
+        <v>6951645</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4276,10 +4276,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154212</v>
+        <v>122154177</v>
       </c>
       <c r="B34" t="n">
-        <v>91182</v>
+        <v>78651</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,16 +4292,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4311,10 +4316,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477420</v>
+        <v>477767</v>
       </c>
       <c r="R34" t="n">
-        <v>6951455</v>
+        <v>6951662</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4355,7 +4360,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4374,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154207</v>
+        <v>122154186</v>
       </c>
       <c r="B35" t="n">
-        <v>74738</v>
+        <v>5173</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4386,25 +4390,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>492</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4414,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477445</v>
+        <v>477370</v>
       </c>
       <c r="R35" t="n">
-        <v>6951570</v>
+        <v>6951711</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4476,10 +4480,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154216</v>
+        <v>122154227</v>
       </c>
       <c r="B36" t="n">
-        <v>74747</v>
+        <v>79732</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4492,21 +4496,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4516,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477457</v>
+        <v>477615</v>
       </c>
       <c r="R36" t="n">
-        <v>6951419</v>
+        <v>6951614</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4578,10 +4582,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154195</v>
+        <v>122154171</v>
       </c>
       <c r="B37" t="n">
-        <v>74739</v>
+        <v>79732</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4594,21 +4598,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4618,10 +4622,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477495</v>
+        <v>477875</v>
       </c>
       <c r="R37" t="n">
-        <v>6951727</v>
+        <v>6951643</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4680,10 +4684,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154177</v>
+        <v>122154185</v>
       </c>
       <c r="B38" t="n">
-        <v>78646</v>
+        <v>90819</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,21 +4700,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,10 +4724,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477767</v>
+        <v>477372</v>
       </c>
       <c r="R38" t="n">
-        <v>6951662</v>
+        <v>6951655</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4785,7 +4789,7 @@
         <v>122154224</v>
       </c>
       <c r="B39" t="n">
-        <v>56587</v>
+        <v>56592</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4884,10 +4888,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154221</v>
+        <v>122154218</v>
       </c>
       <c r="B40" t="n">
-        <v>79728</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4896,25 +4900,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>220093</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4924,10 +4928,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477477</v>
+        <v>477479</v>
       </c>
       <c r="R40" t="n">
-        <v>6951466</v>
+        <v>6951442</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4986,10 +4990,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154209</v>
+        <v>122154203</v>
       </c>
       <c r="B41" t="n">
-        <v>79756</v>
+        <v>90801</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4998,25 +5002,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5026,10 +5030,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477462</v>
+        <v>477381</v>
       </c>
       <c r="R41" t="n">
-        <v>6951485</v>
+        <v>6951610</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5088,10 +5092,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122154185</v>
+        <v>122154207</v>
       </c>
       <c r="B42" t="n">
-        <v>90807</v>
+        <v>74743</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5100,25 +5104,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5128,10 +5132,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477372</v>
+        <v>477445</v>
       </c>
       <c r="R42" t="n">
-        <v>6951655</v>
+        <v>6951570</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5190,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154217</v>
+        <v>122154188</v>
       </c>
       <c r="B43" t="n">
-        <v>57374</v>
+        <v>74752</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5206,38 +5210,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477473</v>
+        <v>477377</v>
       </c>
       <c r="R43" t="n">
-        <v>6951436</v>
+        <v>6951731</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154204</v>
+        <v>122154225</v>
       </c>
       <c r="B44" t="n">
-        <v>98089</v>
+        <v>79732</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5308,25 +5308,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477373</v>
+        <v>477572</v>
       </c>
       <c r="R44" t="n">
-        <v>6951613</v>
+        <v>6951618</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154171</v>
+        <v>122154210</v>
       </c>
       <c r="B45" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477875</v>
+        <v>477464</v>
       </c>
       <c r="R45" t="n">
-        <v>6951643</v>
+        <v>6951483</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5500,10 +5500,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154225</v>
+        <v>122154202</v>
       </c>
       <c r="B46" t="n">
-        <v>79727</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5512,25 +5512,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477572</v>
+        <v>477389</v>
       </c>
       <c r="R46" t="n">
-        <v>6951618</v>
+        <v>6951610</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5602,10 +5602,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154214</v>
+        <v>122154173</v>
       </c>
       <c r="B47" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5618,21 +5618,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477421</v>
+        <v>477825</v>
       </c>
       <c r="R47" t="n">
-        <v>6951454</v>
+        <v>6951660</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5704,10 +5704,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154220</v>
+        <v>122154192</v>
       </c>
       <c r="B48" t="n">
-        <v>79756</v>
+        <v>79636</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5720,21 +5720,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477476</v>
+        <v>477446</v>
       </c>
       <c r="R48" t="n">
-        <v>6951463</v>
+        <v>6951749</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154186</v>
+        <v>122154216</v>
       </c>
       <c r="B49" t="n">
-        <v>5173</v>
+        <v>74752</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5818,25 +5818,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477370</v>
+        <v>477457</v>
       </c>
       <c r="R49" t="n">
-        <v>6951711</v>
+        <v>6951419</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5908,10 +5908,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154187</v>
+        <v>122154160</v>
       </c>
       <c r="B50" t="n">
-        <v>5173</v>
+        <v>98114</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5924,21 +5924,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>219790</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477368</v>
+        <v>477847</v>
       </c>
       <c r="R50" t="n">
-        <v>6951718</v>
+        <v>6951679</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6010,10 +6010,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154192</v>
+        <v>122154205</v>
       </c>
       <c r="B51" t="n">
-        <v>79631</v>
+        <v>97151</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6026,21 +6026,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477446</v>
+        <v>477367</v>
       </c>
       <c r="R51" t="n">
-        <v>6951749</v>
+        <v>6951594</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6112,10 +6112,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154174</v>
+        <v>122154187</v>
       </c>
       <c r="B52" t="n">
-        <v>79727</v>
+        <v>5173</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6124,25 +6124,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477833</v>
+        <v>477368</v>
       </c>
       <c r="R52" t="n">
-        <v>6951669</v>
+        <v>6951718</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6214,10 +6214,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154227</v>
+        <v>122154221</v>
       </c>
       <c r="B53" t="n">
-        <v>79727</v>
+        <v>79733</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6230,21 +6230,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477615</v>
+        <v>477477</v>
       </c>
       <c r="R53" t="n">
-        <v>6951614</v>
+        <v>6951466</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6316,10 +6316,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122154205</v>
+        <v>122154206</v>
       </c>
       <c r="B54" t="n">
-        <v>97139</v>
+        <v>78651</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6328,25 +6328,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477367</v>
+        <v>477411</v>
       </c>
       <c r="R54" t="n">
-        <v>6951594</v>
+        <v>6951546</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122154160</v>
+        <v>122154174</v>
       </c>
       <c r="B55" t="n">
-        <v>98102</v>
+        <v>79732</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6430,25 +6430,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477847</v>
+        <v>477833</v>
       </c>
       <c r="R55" t="n">
-        <v>6951679</v>
+        <v>6951669</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6520,10 +6520,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122154213</v>
+        <v>122154209</v>
       </c>
       <c r="B56" t="n">
-        <v>79756</v>
+        <v>79761</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6560,10 +6560,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477424</v>
+        <v>477462</v>
       </c>
       <c r="R56" t="n">
-        <v>6951452</v>
+        <v>6951485</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6622,10 +6622,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122154198</v>
+        <v>122154215</v>
       </c>
       <c r="B57" t="n">
-        <v>79727</v>
+        <v>56581</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477617</v>
+        <v>477438</v>
       </c>
       <c r="R57" t="n">
-        <v>6951666</v>
+        <v>6951412</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122154202</v>
+        <v>122154170</v>
       </c>
       <c r="B58" t="n">
-        <v>98089</v>
+        <v>57490</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6740,34 +6740,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220093</v>
+        <v>103031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477389</v>
+        <v>477882</v>
       </c>
       <c r="R58" t="n">
-        <v>6951610</v>
+        <v>6951635</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6826,10 +6830,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154161</v>
+        <v>122154219</v>
       </c>
       <c r="B59" t="n">
-        <v>79728</v>
+        <v>79732</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6842,21 +6846,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6866,10 +6870,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477944</v>
+        <v>477495</v>
       </c>
       <c r="R59" t="n">
-        <v>6951693</v>
+        <v>6951463</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6928,10 +6932,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154208</v>
+        <v>122154197</v>
       </c>
       <c r="B60" t="n">
-        <v>79728</v>
+        <v>79761</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6940,25 +6944,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6968,10 +6972,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477462</v>
+        <v>477617</v>
       </c>
       <c r="R60" t="n">
-        <v>6951484</v>
+        <v>6951666</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7030,10 +7034,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154189</v>
+        <v>122154190</v>
       </c>
       <c r="B61" t="n">
-        <v>74739</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7042,25 +7046,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>308</v>
+        <v>220093</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7070,10 +7074,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477405</v>
+        <v>477407</v>
       </c>
       <c r="R61" t="n">
-        <v>6951731</v>
+        <v>6951732</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7132,10 +7136,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154206</v>
+        <v>122154201</v>
       </c>
       <c r="B62" t="n">
-        <v>78646</v>
+        <v>74744</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7148,21 +7152,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7172,10 +7176,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477411</v>
+        <v>477404</v>
       </c>
       <c r="R62" t="n">
-        <v>6951546</v>
+        <v>6951629</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7234,10 +7238,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154169</v>
+        <v>122154220</v>
       </c>
       <c r="B63" t="n">
-        <v>56576</v>
+        <v>79761</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7246,42 +7250,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477886</v>
+        <v>477476</v>
       </c>
       <c r="R63" t="n">
-        <v>6951641</v>
+        <v>6951463</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154191</v>
+        <v>122154213</v>
       </c>
       <c r="B64" t="n">
-        <v>98089</v>
+        <v>79761</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7356,21 +7356,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7383,7 +7383,7 @@
         <v>477424</v>
       </c>
       <c r="R64" t="n">
-        <v>6951736</v>
+        <v>6951452</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178231</v>
+        <v>122178234</v>
       </c>
       <c r="B65" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477585</v>
+        <v>477584</v>
       </c>
       <c r="R65" t="n">
-        <v>6951573</v>
+        <v>6951542</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7544,10 +7544,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178238</v>
+        <v>122178235</v>
       </c>
       <c r="B66" t="n">
-        <v>94211</v>
+        <v>79240</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7556,25 +7556,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2387</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477538</v>
+        <v>477573</v>
       </c>
       <c r="R66" t="n">
-        <v>6951456</v>
+        <v>6951539</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122172654</v>
+        <v>122178227</v>
       </c>
       <c r="B67" t="n">
-        <v>97139</v>
+        <v>79732</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7658,25 +7658,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477639</v>
+        <v>477598</v>
       </c>
       <c r="R67" t="n">
-        <v>6951706</v>
+        <v>6951610</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,22 +7736,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178234</v>
+        <v>122178220</v>
       </c>
       <c r="B68" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477584</v>
+        <v>477556</v>
       </c>
       <c r="R68" t="n">
-        <v>6951542</v>
+        <v>6951549</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178229</v>
+        <v>122178245</v>
       </c>
       <c r="B69" t="n">
-        <v>79763</v>
+        <v>74752</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7862,25 +7862,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477587</v>
+        <v>477542</v>
       </c>
       <c r="R69" t="n">
-        <v>6951569</v>
+        <v>6951443</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178232</v>
+        <v>122178223</v>
       </c>
       <c r="B70" t="n">
-        <v>79727</v>
+        <v>94031</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7964,25 +7964,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>2412</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477570</v>
+        <v>477540</v>
       </c>
       <c r="R70" t="n">
-        <v>6951563</v>
+        <v>6951613</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178244</v>
+        <v>122178246</v>
       </c>
       <c r="B71" t="n">
-        <v>79637</v>
+        <v>79732</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2080</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477538</v>
+        <v>477535</v>
       </c>
       <c r="R71" t="n">
-        <v>6951440</v>
+        <v>6951442</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178224</v>
+        <v>122172652</v>
       </c>
       <c r="B72" t="n">
-        <v>94211</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8172,21 +8172,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2387</v>
+        <v>220093</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477572</v>
+        <v>477755</v>
       </c>
       <c r="R72" t="n">
-        <v>6951626</v>
+        <v>6951671</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8246,22 +8246,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122172653</v>
+        <v>122178226</v>
       </c>
       <c r="B73" t="n">
-        <v>90807</v>
+        <v>74744</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8274,21 +8274,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477642</v>
+        <v>477581</v>
       </c>
       <c r="R73" t="n">
-        <v>6951702</v>
+        <v>6951614</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8348,22 +8348,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178221</v>
+        <v>122178232</v>
       </c>
       <c r="B74" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477543</v>
+        <v>477570</v>
       </c>
       <c r="R74" t="n">
-        <v>6951588</v>
+        <v>6951563</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122172640</v>
+        <v>122178224</v>
       </c>
       <c r="B75" t="n">
-        <v>79727</v>
+        <v>94223</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8474,25 +8474,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477949</v>
+        <v>477572</v>
       </c>
       <c r="R75" t="n">
-        <v>6951706</v>
+        <v>6951626</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8552,22 +8552,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122178235</v>
+        <v>122172653</v>
       </c>
       <c r="B76" t="n">
-        <v>79235</v>
+        <v>90819</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8580,21 +8580,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477573</v>
+        <v>477642</v>
       </c>
       <c r="R76" t="n">
-        <v>6951539</v>
+        <v>6951702</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8654,22 +8654,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122178226</v>
+        <v>122178244</v>
       </c>
       <c r="B77" t="n">
-        <v>74739</v>
+        <v>79642</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8682,21 +8682,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>2080</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477581</v>
+        <v>477538</v>
       </c>
       <c r="R77" t="n">
-        <v>6951614</v>
+        <v>6951440</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8768,10 +8768,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122178223</v>
+        <v>122178247</v>
       </c>
       <c r="B78" t="n">
-        <v>94019</v>
+        <v>79732</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8780,25 +8780,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2412</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8811,7 +8811,7 @@
         <v>477540</v>
       </c>
       <c r="R78" t="n">
-        <v>6951613</v>
+        <v>6951433</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122178236</v>
+        <v>122178228</v>
       </c>
       <c r="B79" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8886,21 +8886,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477559</v>
+        <v>477590</v>
       </c>
       <c r="R79" t="n">
-        <v>6951532</v>
+        <v>6951600</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8972,10 +8972,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122178222</v>
+        <v>122178236</v>
       </c>
       <c r="B80" t="n">
-        <v>97139</v>
+        <v>78651</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8984,25 +8984,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477540</v>
+        <v>477559</v>
       </c>
       <c r="R80" t="n">
-        <v>6951594</v>
+        <v>6951532</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122178228</v>
+        <v>122178231</v>
       </c>
       <c r="B81" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477590</v>
+        <v>477585</v>
       </c>
       <c r="R81" t="n">
-        <v>6951600</v>
+        <v>6951573</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9176,10 +9176,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122172652</v>
+        <v>122178242</v>
       </c>
       <c r="B82" t="n">
-        <v>98089</v>
+        <v>74752</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9188,25 +9188,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477755</v>
+        <v>477534</v>
       </c>
       <c r="R82" t="n">
-        <v>6951671</v>
+        <v>6951448</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9246,12 +9246,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9266,22 +9266,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122178246</v>
+        <v>122172640</v>
       </c>
       <c r="B83" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477535</v>
+        <v>477949</v>
       </c>
       <c r="R83" t="n">
-        <v>6951442</v>
+        <v>6951706</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9348,12 +9348,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9368,22 +9368,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122178225</v>
+        <v>122172654</v>
       </c>
       <c r="B84" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477580</v>
+        <v>477639</v>
       </c>
       <c r="R84" t="n">
-        <v>6951617</v>
+        <v>6951706</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9470,22 +9470,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122178247</v>
+        <v>122178222</v>
       </c>
       <c r="B85" t="n">
-        <v>79727</v>
+        <v>97151</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9494,25 +9494,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9525,7 +9525,7 @@
         <v>477540</v>
       </c>
       <c r="R85" t="n">
-        <v>6951433</v>
+        <v>6951594</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178245</v>
+        <v>122178225</v>
       </c>
       <c r="B86" t="n">
-        <v>74747</v>
+        <v>97151</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9596,25 +9596,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477542</v>
+        <v>477580</v>
       </c>
       <c r="R86" t="n">
-        <v>6951443</v>
+        <v>6951617</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178242</v>
+        <v>122178238</v>
       </c>
       <c r="B87" t="n">
-        <v>74747</v>
+        <v>94223</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9698,25 +9698,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>2387</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477534</v>
+        <v>477538</v>
       </c>
       <c r="R87" t="n">
-        <v>6951448</v>
+        <v>6951456</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9788,10 +9788,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178220</v>
+        <v>122178221</v>
       </c>
       <c r="B88" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477556</v>
+        <v>477543</v>
       </c>
       <c r="R88" t="n">
-        <v>6951549</v>
+        <v>6951588</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9890,10 +9890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122178227</v>
+        <v>122178229</v>
       </c>
       <c r="B89" t="n">
-        <v>79727</v>
+        <v>79768</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9902,25 +9902,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477598</v>
+        <v>477587</v>
       </c>
       <c r="R89" t="n">
-        <v>6951610</v>
+        <v>6951569</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9995,7 +9995,7 @@
         <v>122178237</v>
       </c>
       <c r="B90" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>122178243</v>
       </c>
       <c r="B91" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154169</v>
+        <v>122154221</v>
       </c>
       <c r="B19" t="n">
-        <v>56581</v>
+        <v>79733</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2758,38 +2758,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477886</v>
+        <v>477477</v>
       </c>
       <c r="R19" t="n">
-        <v>6951641</v>
+        <v>6951466</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2848,10 +2844,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154198</v>
+        <v>122154206</v>
       </c>
       <c r="B20" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2864,21 +2860,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2888,10 +2884,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477617</v>
+        <v>477411</v>
       </c>
       <c r="R20" t="n">
-        <v>6951666</v>
+        <v>6951546</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2950,10 +2946,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154204</v>
+        <v>122154217</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2962,38 +2958,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477373</v>
+        <v>477473</v>
       </c>
       <c r="R21" t="n">
-        <v>6951613</v>
+        <v>6951436</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3052,10 +3052,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154191</v>
+        <v>122154161</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>79733</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,25 +3064,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477424</v>
+        <v>477944</v>
       </c>
       <c r="R22" t="n">
-        <v>6951736</v>
+        <v>6951693</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3154,10 +3154,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154212</v>
+        <v>122154195</v>
       </c>
       <c r="B23" t="n">
-        <v>91194</v>
+        <v>74744</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,16 +3170,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>308</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3189,10 +3194,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477420</v>
+        <v>477495</v>
       </c>
       <c r="R23" t="n">
-        <v>6951455</v>
+        <v>6951727</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3233,7 +3238,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3252,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154189</v>
+        <v>122154224</v>
       </c>
       <c r="B24" t="n">
-        <v>74744</v>
+        <v>56592</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3264,25 +3268,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>102613</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3292,10 +3296,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477405</v>
+        <v>477538</v>
       </c>
       <c r="R24" t="n">
-        <v>6951731</v>
+        <v>6951618</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3354,10 +3358,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154172</v>
+        <v>122154213</v>
       </c>
       <c r="B25" t="n">
-        <v>5173</v>
+        <v>79761</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,21 +3374,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3394,10 +3398,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477879</v>
+        <v>477424</v>
       </c>
       <c r="R25" t="n">
-        <v>6951648</v>
+        <v>6951452</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3456,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154217</v>
+        <v>122154216</v>
       </c>
       <c r="B26" t="n">
-        <v>57379</v>
+        <v>74752</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,38 +3476,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477473</v>
+        <v>477457</v>
       </c>
       <c r="R26" t="n">
-        <v>6951436</v>
+        <v>6951419</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154211</v>
+        <v>122154201</v>
       </c>
       <c r="B27" t="n">
-        <v>90748</v>
+        <v>74744</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477448</v>
+        <v>477404</v>
       </c>
       <c r="R27" t="n">
-        <v>6951476</v>
+        <v>6951629</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154208</v>
+        <v>122154169</v>
       </c>
       <c r="B28" t="n">
-        <v>79733</v>
+        <v>56581</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,34 +3680,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477462</v>
+        <v>477886</v>
       </c>
       <c r="R28" t="n">
-        <v>6951484</v>
+        <v>6951641</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3766,10 +3770,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154195</v>
+        <v>122154219</v>
       </c>
       <c r="B29" t="n">
-        <v>74744</v>
+        <v>79732</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3782,21 +3786,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3809,7 +3813,7 @@
         <v>477495</v>
       </c>
       <c r="R29" t="n">
-        <v>6951727</v>
+        <v>6951463</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3868,7 +3872,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154161</v>
+        <v>122154208</v>
       </c>
       <c r="B30" t="n">
         <v>79733</v>
@@ -3908,10 +3912,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477944</v>
+        <v>477462</v>
       </c>
       <c r="R30" t="n">
-        <v>6951693</v>
+        <v>6951484</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3970,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154214</v>
+        <v>122154189</v>
       </c>
       <c r="B31" t="n">
-        <v>79732</v>
+        <v>74744</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3986,21 +3990,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4010,10 +4014,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477421</v>
+        <v>477405</v>
       </c>
       <c r="R31" t="n">
-        <v>6951454</v>
+        <v>6951731</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4072,10 +4076,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154175</v>
+        <v>122154212</v>
       </c>
       <c r="B32" t="n">
-        <v>90797</v>
+        <v>91199</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4088,21 +4092,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4112,10 +4111,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477793</v>
+        <v>477420</v>
       </c>
       <c r="R32" t="n">
-        <v>6951655</v>
+        <v>6951455</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4156,6 +4155,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154200</v>
+        <v>122154170</v>
       </c>
       <c r="B33" t="n">
-        <v>78651</v>
+        <v>57490</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4186,38 +4186,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477435</v>
+        <v>477882</v>
       </c>
       <c r="R33" t="n">
-        <v>6951645</v>
+        <v>6951635</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4276,10 +4280,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154177</v>
+        <v>122154214</v>
       </c>
       <c r="B34" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,21 +4296,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4316,10 +4320,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477767</v>
+        <v>477421</v>
       </c>
       <c r="R34" t="n">
-        <v>6951662</v>
+        <v>6951454</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4378,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154186</v>
+        <v>122154220</v>
       </c>
       <c r="B35" t="n">
-        <v>5173</v>
+        <v>79761</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4394,21 +4398,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4418,10 +4422,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477370</v>
+        <v>477476</v>
       </c>
       <c r="R35" t="n">
-        <v>6951711</v>
+        <v>6951463</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4480,10 +4484,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154227</v>
+        <v>122154207</v>
       </c>
       <c r="B36" t="n">
-        <v>79732</v>
+        <v>74743</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4492,25 +4496,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4520,10 +4524,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477615</v>
+        <v>477445</v>
       </c>
       <c r="R36" t="n">
-        <v>6951614</v>
+        <v>6951570</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4582,10 +4586,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154171</v>
+        <v>122154215</v>
       </c>
       <c r="B37" t="n">
-        <v>79732</v>
+        <v>56581</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4598,21 +4602,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4622,10 +4626,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477875</v>
+        <v>477438</v>
       </c>
       <c r="R37" t="n">
-        <v>6951643</v>
+        <v>6951412</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4684,10 +4688,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154185</v>
+        <v>122154209</v>
       </c>
       <c r="B38" t="n">
-        <v>90819</v>
+        <v>79761</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,25 +4700,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4724,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477372</v>
+        <v>477462</v>
       </c>
       <c r="R38" t="n">
-        <v>6951655</v>
+        <v>6951485</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4786,10 +4790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154224</v>
+        <v>122154188</v>
       </c>
       <c r="B39" t="n">
-        <v>56592</v>
+        <v>74752</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,25 +4802,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102613</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4826,10 +4830,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477538</v>
+        <v>477377</v>
       </c>
       <c r="R39" t="n">
-        <v>6951618</v>
+        <v>6951731</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4888,10 +4892,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154218</v>
+        <v>122154185</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>90826</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4900,25 +4904,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220093</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4928,10 +4932,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477479</v>
+        <v>477372</v>
       </c>
       <c r="R40" t="n">
-        <v>6951442</v>
+        <v>6951655</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4990,10 +4994,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154203</v>
+        <v>122154177</v>
       </c>
       <c r="B41" t="n">
-        <v>90801</v>
+        <v>78651</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5006,21 +5010,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5030,10 +5034,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477381</v>
+        <v>477767</v>
       </c>
       <c r="R41" t="n">
-        <v>6951610</v>
+        <v>6951662</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5092,10 +5096,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122154207</v>
+        <v>122154225</v>
       </c>
       <c r="B42" t="n">
-        <v>74743</v>
+        <v>79732</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5104,25 +5108,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5132,10 +5136,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477445</v>
+        <v>477572</v>
       </c>
       <c r="R42" t="n">
-        <v>6951570</v>
+        <v>6951618</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5194,10 +5198,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154188</v>
+        <v>122154218</v>
       </c>
       <c r="B43" t="n">
-        <v>74752</v>
+        <v>98106</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5206,25 +5210,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>220093</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5234,10 +5238,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477377</v>
+        <v>477479</v>
       </c>
       <c r="R43" t="n">
-        <v>6951731</v>
+        <v>6951442</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5296,10 +5300,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154225</v>
+        <v>122154200</v>
       </c>
       <c r="B44" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5312,21 +5316,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5336,10 +5340,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477572</v>
+        <v>477435</v>
       </c>
       <c r="R44" t="n">
-        <v>6951618</v>
+        <v>6951645</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5398,7 +5402,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154210</v>
+        <v>122154174</v>
       </c>
       <c r="B45" t="n">
         <v>79732</v>
@@ -5438,10 +5442,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477464</v>
+        <v>477833</v>
       </c>
       <c r="R45" t="n">
-        <v>6951483</v>
+        <v>6951669</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5500,10 +5504,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154202</v>
+        <v>122154175</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>90804</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5512,25 +5516,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220093</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5540,10 +5544,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477389</v>
+        <v>477793</v>
       </c>
       <c r="R46" t="n">
-        <v>6951610</v>
+        <v>6951655</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5602,10 +5606,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154173</v>
+        <v>122154171</v>
       </c>
       <c r="B47" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5618,21 +5622,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5642,10 +5646,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477825</v>
+        <v>477875</v>
       </c>
       <c r="R47" t="n">
-        <v>6951660</v>
+        <v>6951643</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5704,10 +5708,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154192</v>
+        <v>122154227</v>
       </c>
       <c r="B48" t="n">
-        <v>79636</v>
+        <v>79732</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5716,25 +5720,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5744,10 +5748,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477446</v>
+        <v>477615</v>
       </c>
       <c r="R48" t="n">
-        <v>6951749</v>
+        <v>6951614</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5806,10 +5810,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154216</v>
+        <v>122154198</v>
       </c>
       <c r="B49" t="n">
-        <v>74752</v>
+        <v>79732</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5822,21 +5826,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5846,10 +5850,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477457</v>
+        <v>477617</v>
       </c>
       <c r="R49" t="n">
-        <v>6951419</v>
+        <v>6951666</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5908,10 +5912,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154160</v>
+        <v>122154190</v>
       </c>
       <c r="B50" t="n">
-        <v>98114</v>
+        <v>98106</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5924,21 +5928,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5948,10 +5952,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477847</v>
+        <v>477407</v>
       </c>
       <c r="R50" t="n">
-        <v>6951679</v>
+        <v>6951732</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6010,10 +6014,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154205</v>
+        <v>122154204</v>
       </c>
       <c r="B51" t="n">
-        <v>97151</v>
+        <v>98106</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6026,21 +6030,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6050,10 +6054,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477367</v>
+        <v>477373</v>
       </c>
       <c r="R51" t="n">
-        <v>6951594</v>
+        <v>6951613</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6112,10 +6116,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154187</v>
+        <v>122154173</v>
       </c>
       <c r="B52" t="n">
-        <v>5173</v>
+        <v>78651</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6124,25 +6128,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6152,10 +6156,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477368</v>
+        <v>477825</v>
       </c>
       <c r="R52" t="n">
-        <v>6951718</v>
+        <v>6951660</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6214,10 +6218,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154221</v>
+        <v>122154186</v>
       </c>
       <c r="B53" t="n">
-        <v>79733</v>
+        <v>5173</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6226,25 +6230,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6254,10 +6258,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477477</v>
+        <v>477370</v>
       </c>
       <c r="R53" t="n">
-        <v>6951466</v>
+        <v>6951711</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6316,10 +6320,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122154206</v>
+        <v>122154172</v>
       </c>
       <c r="B54" t="n">
-        <v>78651</v>
+        <v>5173</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6328,25 +6332,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6356,10 +6360,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477411</v>
+        <v>477879</v>
       </c>
       <c r="R54" t="n">
-        <v>6951546</v>
+        <v>6951648</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6418,7 +6422,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122154174</v>
+        <v>122154210</v>
       </c>
       <c r="B55" t="n">
         <v>79732</v>
@@ -6458,10 +6462,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477833</v>
+        <v>477464</v>
       </c>
       <c r="R55" t="n">
-        <v>6951669</v>
+        <v>6951483</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6520,7 +6524,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122154209</v>
+        <v>122154197</v>
       </c>
       <c r="B56" t="n">
         <v>79761</v>
@@ -6560,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477462</v>
+        <v>477617</v>
       </c>
       <c r="R56" t="n">
-        <v>6951485</v>
+        <v>6951666</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6622,10 +6626,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122154215</v>
+        <v>122154160</v>
       </c>
       <c r="B57" t="n">
-        <v>56581</v>
+        <v>98119</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6634,25 +6638,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6662,10 +6666,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477438</v>
+        <v>477847</v>
       </c>
       <c r="R57" t="n">
-        <v>6951412</v>
+        <v>6951679</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6724,10 +6728,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122154170</v>
+        <v>122154187</v>
       </c>
       <c r="B58" t="n">
-        <v>57490</v>
+        <v>5173</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6740,38 +6744,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103031</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477882</v>
+        <v>477368</v>
       </c>
       <c r="R58" t="n">
-        <v>6951635</v>
+        <v>6951718</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154219</v>
+        <v>122154192</v>
       </c>
       <c r="B59" t="n">
-        <v>79732</v>
+        <v>79636</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6842,25 +6842,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477495</v>
+        <v>477446</v>
       </c>
       <c r="R59" t="n">
-        <v>6951463</v>
+        <v>6951749</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154197</v>
+        <v>122154202</v>
       </c>
       <c r="B60" t="n">
-        <v>79761</v>
+        <v>98106</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>220093</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477617</v>
+        <v>477389</v>
       </c>
       <c r="R60" t="n">
-        <v>6951666</v>
+        <v>6951610</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154190</v>
+        <v>122154191</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>98106</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477407</v>
+        <v>477424</v>
       </c>
       <c r="R61" t="n">
-        <v>6951732</v>
+        <v>6951736</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154201</v>
+        <v>122154205</v>
       </c>
       <c r="B62" t="n">
-        <v>74744</v>
+        <v>97156</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7148,25 +7148,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477404</v>
+        <v>477367</v>
       </c>
       <c r="R62" t="n">
-        <v>6951629</v>
+        <v>6951594</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154220</v>
+        <v>122154211</v>
       </c>
       <c r="B63" t="n">
-        <v>79761</v>
+        <v>90752</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7250,25 +7250,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477476</v>
+        <v>477448</v>
       </c>
       <c r="R63" t="n">
-        <v>6951463</v>
+        <v>6951476</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154213</v>
+        <v>122154203</v>
       </c>
       <c r="B64" t="n">
-        <v>79761</v>
+        <v>90808</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477424</v>
+        <v>477381</v>
       </c>
       <c r="R64" t="n">
-        <v>6951452</v>
+        <v>6951610</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178234</v>
+        <v>122178224</v>
       </c>
       <c r="B65" t="n">
-        <v>79732</v>
+        <v>94228</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7454,25 +7454,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477584</v>
+        <v>477572</v>
       </c>
       <c r="R65" t="n">
-        <v>6951542</v>
+        <v>6951626</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7544,10 +7544,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178235</v>
+        <v>122178236</v>
       </c>
       <c r="B66" t="n">
-        <v>79240</v>
+        <v>78651</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477573</v>
+        <v>477559</v>
       </c>
       <c r="R66" t="n">
-        <v>6951539</v>
+        <v>6951532</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7646,7 +7646,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178227</v>
+        <v>122178247</v>
       </c>
       <c r="B67" t="n">
         <v>79732</v>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477598</v>
+        <v>477540</v>
       </c>
       <c r="R67" t="n">
-        <v>6951610</v>
+        <v>6951433</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178245</v>
+        <v>122172640</v>
       </c>
       <c r="B69" t="n">
-        <v>74752</v>
+        <v>79732</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477542</v>
+        <v>477949</v>
       </c>
       <c r="R69" t="n">
-        <v>6951443</v>
+        <v>6951706</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7940,22 +7940,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178223</v>
+        <v>122178243</v>
       </c>
       <c r="B70" t="n">
-        <v>94031</v>
+        <v>79732</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7964,25 +7964,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2412</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477540</v>
+        <v>477538</v>
       </c>
       <c r="R70" t="n">
-        <v>6951613</v>
+        <v>6951448</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178246</v>
+        <v>122178235</v>
       </c>
       <c r="B71" t="n">
-        <v>79732</v>
+        <v>79240</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477535</v>
+        <v>477573</v>
       </c>
       <c r="R71" t="n">
-        <v>6951442</v>
+        <v>6951539</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8159,7 +8159,7 @@
         <v>122172652</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>98106</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8258,10 +8258,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178226</v>
+        <v>122178245</v>
       </c>
       <c r="B73" t="n">
-        <v>74744</v>
+        <v>74752</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8274,21 +8274,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477581</v>
+        <v>477542</v>
       </c>
       <c r="R73" t="n">
-        <v>6951614</v>
+        <v>6951443</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8360,7 +8360,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178232</v>
+        <v>122178228</v>
       </c>
       <c r="B74" t="n">
         <v>79732</v>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477570</v>
+        <v>477590</v>
       </c>
       <c r="R74" t="n">
-        <v>6951563</v>
+        <v>6951600</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178224</v>
+        <v>122178221</v>
       </c>
       <c r="B75" t="n">
-        <v>94223</v>
+        <v>79732</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8474,25 +8474,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477572</v>
+        <v>477543</v>
       </c>
       <c r="R75" t="n">
-        <v>6951626</v>
+        <v>6951588</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122172653</v>
+        <v>122178237</v>
       </c>
       <c r="B76" t="n">
-        <v>90819</v>
+        <v>79732</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8580,21 +8580,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477642</v>
+        <v>477518</v>
       </c>
       <c r="R76" t="n">
-        <v>6951702</v>
+        <v>6951490</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8654,22 +8654,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122178244</v>
+        <v>122178231</v>
       </c>
       <c r="B77" t="n">
-        <v>79642</v>
+        <v>79732</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8682,21 +8682,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2080</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477538</v>
+        <v>477585</v>
       </c>
       <c r="R77" t="n">
-        <v>6951440</v>
+        <v>6951573</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8768,7 +8768,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122178247</v>
+        <v>122178246</v>
       </c>
       <c r="B78" t="n">
         <v>79732</v>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477540</v>
+        <v>477535</v>
       </c>
       <c r="R78" t="n">
-        <v>6951433</v>
+        <v>6951442</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122178228</v>
+        <v>122178232</v>
       </c>
       <c r="B79" t="n">
         <v>79732</v>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477590</v>
+        <v>477570</v>
       </c>
       <c r="R79" t="n">
-        <v>6951600</v>
+        <v>6951563</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8972,10 +8972,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122178236</v>
+        <v>122178234</v>
       </c>
       <c r="B80" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477559</v>
+        <v>477584</v>
       </c>
       <c r="R80" t="n">
-        <v>6951532</v>
+        <v>6951542</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122178231</v>
+        <v>122178222</v>
       </c>
       <c r="B81" t="n">
-        <v>79732</v>
+        <v>97156</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9086,25 +9086,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477585</v>
+        <v>477540</v>
       </c>
       <c r="R81" t="n">
-        <v>6951573</v>
+        <v>6951594</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9176,10 +9176,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122178242</v>
+        <v>122178223</v>
       </c>
       <c r="B82" t="n">
-        <v>74752</v>
+        <v>94036</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9188,25 +9188,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>2412</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477534</v>
+        <v>477540</v>
       </c>
       <c r="R82" t="n">
-        <v>6951448</v>
+        <v>6951613</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9278,10 +9278,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122172640</v>
+        <v>122172653</v>
       </c>
       <c r="B83" t="n">
-        <v>79732</v>
+        <v>90826</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9294,21 +9294,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477949</v>
+        <v>477642</v>
       </c>
       <c r="R83" t="n">
-        <v>6951706</v>
+        <v>6951702</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122172654</v>
+        <v>122178229</v>
       </c>
       <c r="B84" t="n">
-        <v>97151</v>
+        <v>79768</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477639</v>
+        <v>477587</v>
       </c>
       <c r="R84" t="n">
-        <v>6951706</v>
+        <v>6951569</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9450,12 +9450,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9470,22 +9470,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122178222</v>
+        <v>122172654</v>
       </c>
       <c r="B85" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477540</v>
+        <v>477639</v>
       </c>
       <c r="R85" t="n">
-        <v>6951594</v>
+        <v>6951706</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9552,12 +9552,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9572,22 +9572,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178225</v>
+        <v>122178242</v>
       </c>
       <c r="B86" t="n">
-        <v>97151</v>
+        <v>74752</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9596,25 +9596,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477580</v>
+        <v>477534</v>
       </c>
       <c r="R86" t="n">
-        <v>6951617</v>
+        <v>6951448</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178238</v>
+        <v>122178226</v>
       </c>
       <c r="B87" t="n">
-        <v>94223</v>
+        <v>74744</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9698,25 +9698,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2387</v>
+        <v>308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477538</v>
+        <v>477581</v>
       </c>
       <c r="R87" t="n">
-        <v>6951456</v>
+        <v>6951614</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9788,7 +9788,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178221</v>
+        <v>122178227</v>
       </c>
       <c r="B88" t="n">
         <v>79732</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477543</v>
+        <v>477598</v>
       </c>
       <c r="R88" t="n">
-        <v>6951588</v>
+        <v>6951610</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9890,10 +9890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122178229</v>
+        <v>122178238</v>
       </c>
       <c r="B89" t="n">
-        <v>79768</v>
+        <v>94228</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6464</v>
+        <v>2387</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477587</v>
+        <v>477538</v>
       </c>
       <c r="R89" t="n">
-        <v>6951569</v>
+        <v>6951456</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122178237</v>
+        <v>122178225</v>
       </c>
       <c r="B90" t="n">
-        <v>79732</v>
+        <v>97156</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10004,25 +10004,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477518</v>
+        <v>477580</v>
       </c>
       <c r="R90" t="n">
-        <v>6951490</v>
+        <v>6951617</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10094,10 +10094,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122178243</v>
+        <v>122178244</v>
       </c>
       <c r="B91" t="n">
-        <v>79732</v>
+        <v>79642</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10110,21 +10110,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>2080</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
         <v>477538</v>
       </c>
       <c r="R91" t="n">
-        <v>6951448</v>
+        <v>6951440</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -6014,10 +6014,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154204</v>
+        <v>122154173</v>
       </c>
       <c r="B51" t="n">
-        <v>98106</v>
+        <v>78651</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6026,25 +6026,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477373</v>
+        <v>477825</v>
       </c>
       <c r="R51" t="n">
-        <v>6951613</v>
+        <v>6951660</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6116,10 +6116,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154173</v>
+        <v>122154186</v>
       </c>
       <c r="B52" t="n">
-        <v>78651</v>
+        <v>5173</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6128,25 +6128,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477825</v>
+        <v>477370</v>
       </c>
       <c r="R52" t="n">
-        <v>6951660</v>
+        <v>6951711</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6218,10 +6218,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154186</v>
+        <v>122154204</v>
       </c>
       <c r="B53" t="n">
-        <v>5173</v>
+        <v>98106</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6234,21 +6234,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477370</v>
+        <v>477373</v>
       </c>
       <c r="R53" t="n">
-        <v>6951711</v>
+        <v>6951613</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154191</v>
+        <v>122154211</v>
       </c>
       <c r="B61" t="n">
-        <v>98106</v>
+        <v>90752</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7046,25 +7046,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220093</v>
+        <v>112</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477424</v>
+        <v>477448</v>
       </c>
       <c r="R61" t="n">
-        <v>6951736</v>
+        <v>6951476</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154205</v>
+        <v>122154203</v>
       </c>
       <c r="B62" t="n">
-        <v>97156</v>
+        <v>90808</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7148,25 +7148,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477367</v>
+        <v>477381</v>
       </c>
       <c r="R62" t="n">
-        <v>6951594</v>
+        <v>6951610</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154211</v>
+        <v>122154191</v>
       </c>
       <c r="B63" t="n">
-        <v>90752</v>
+        <v>98106</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7250,25 +7250,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>112</v>
+        <v>220093</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477448</v>
+        <v>477424</v>
       </c>
       <c r="R63" t="n">
-        <v>6951476</v>
+        <v>6951736</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154203</v>
+        <v>122154205</v>
       </c>
       <c r="B64" t="n">
-        <v>90808</v>
+        <v>97156</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477381</v>
+        <v>477367</v>
       </c>
       <c r="R64" t="n">
-        <v>6951610</v>
+        <v>6951594</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122172654</v>
+        <v>122178242</v>
       </c>
       <c r="B85" t="n">
-        <v>97156</v>
+        <v>74752</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9494,25 +9494,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477639</v>
+        <v>477534</v>
       </c>
       <c r="R85" t="n">
-        <v>6951706</v>
+        <v>6951448</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9552,12 +9552,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9572,22 +9572,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178242</v>
+        <v>122178226</v>
       </c>
       <c r="B86" t="n">
-        <v>74752</v>
+        <v>74744</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477534</v>
+        <v>477581</v>
       </c>
       <c r="R86" t="n">
-        <v>6951448</v>
+        <v>6951614</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9686,10 +9686,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178226</v>
+        <v>122178227</v>
       </c>
       <c r="B87" t="n">
-        <v>74744</v>
+        <v>79732</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477581</v>
+        <v>477598</v>
       </c>
       <c r="R87" t="n">
-        <v>6951614</v>
+        <v>6951610</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9788,10 +9788,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178227</v>
+        <v>122172654</v>
       </c>
       <c r="B88" t="n">
-        <v>79732</v>
+        <v>97156</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9800,25 +9800,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477598</v>
+        <v>477639</v>
       </c>
       <c r="R88" t="n">
-        <v>6951610</v>
+        <v>6951706</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9878,12 +9878,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -4688,10 +4688,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154209</v>
+        <v>122154188</v>
       </c>
       <c r="B38" t="n">
-        <v>79761</v>
+        <v>74752</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4700,25 +4700,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477462</v>
+        <v>477377</v>
       </c>
       <c r="R38" t="n">
-        <v>6951485</v>
+        <v>6951731</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154188</v>
+        <v>122154185</v>
       </c>
       <c r="B39" t="n">
-        <v>74752</v>
+        <v>90826</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4806,21 +4806,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477377</v>
+        <v>477372</v>
       </c>
       <c r="R39" t="n">
-        <v>6951731</v>
+        <v>6951655</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4892,10 +4892,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154185</v>
+        <v>122154209</v>
       </c>
       <c r="B40" t="n">
-        <v>90826</v>
+        <v>79761</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4904,25 +4904,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477372</v>
+        <v>477462</v>
       </c>
       <c r="R40" t="n">
-        <v>6951655</v>
+        <v>6951485</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -6014,10 +6014,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154173</v>
+        <v>122154204</v>
       </c>
       <c r="B51" t="n">
-        <v>78651</v>
+        <v>98106</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6026,25 +6026,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477825</v>
+        <v>477373</v>
       </c>
       <c r="R51" t="n">
-        <v>6951660</v>
+        <v>6951613</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6116,10 +6116,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154186</v>
+        <v>122154173</v>
       </c>
       <c r="B52" t="n">
-        <v>5173</v>
+        <v>78651</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6128,25 +6128,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477370</v>
+        <v>477825</v>
       </c>
       <c r="R52" t="n">
-        <v>6951711</v>
+        <v>6951660</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6218,10 +6218,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154204</v>
+        <v>122154186</v>
       </c>
       <c r="B53" t="n">
-        <v>98106</v>
+        <v>5173</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6234,21 +6234,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220093</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477373</v>
+        <v>477370</v>
       </c>
       <c r="R53" t="n">
-        <v>6951613</v>
+        <v>6951711</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154211</v>
+        <v>122154191</v>
       </c>
       <c r="B61" t="n">
-        <v>90752</v>
+        <v>98106</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7046,25 +7046,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>112</v>
+        <v>220093</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477448</v>
+        <v>477424</v>
       </c>
       <c r="R61" t="n">
-        <v>6951476</v>
+        <v>6951736</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154203</v>
+        <v>122154205</v>
       </c>
       <c r="B62" t="n">
-        <v>90808</v>
+        <v>97156</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7148,25 +7148,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477381</v>
+        <v>477367</v>
       </c>
       <c r="R62" t="n">
-        <v>6951610</v>
+        <v>6951594</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154191</v>
+        <v>122154211</v>
       </c>
       <c r="B63" t="n">
-        <v>98106</v>
+        <v>90752</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7250,25 +7250,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220093</v>
+        <v>112</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477424</v>
+        <v>477448</v>
       </c>
       <c r="R63" t="n">
-        <v>6951736</v>
+        <v>6951476</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154205</v>
+        <v>122154203</v>
       </c>
       <c r="B64" t="n">
-        <v>97156</v>
+        <v>90808</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477367</v>
+        <v>477381</v>
       </c>
       <c r="R64" t="n">
-        <v>6951594</v>
+        <v>6951610</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154221</v>
+        <v>122154175</v>
       </c>
       <c r="B19" t="n">
-        <v>79733</v>
+        <v>90809</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2758,21 +2758,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>1108</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2782,10 +2777,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477477</v>
+        <v>477793</v>
       </c>
       <c r="R19" t="n">
-        <v>6951466</v>
+        <v>6951655</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2844,10 +2839,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154206</v>
+        <v>122154219</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2860,21 +2855,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2884,10 +2874,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477411</v>
+        <v>477495</v>
       </c>
       <c r="R20" t="n">
-        <v>6951546</v>
+        <v>6951463</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2946,10 +2936,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154217</v>
+        <v>122154224</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>56592</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2958,20 +2948,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>102613</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2979,21 +2964,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477473</v>
+        <v>477538</v>
       </c>
       <c r="R21" t="n">
-        <v>6951436</v>
+        <v>6951618</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3052,10 +3033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154161</v>
+        <v>122154192</v>
       </c>
       <c r="B22" t="n">
-        <v>79733</v>
+        <v>79637</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,25 +3045,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6456</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3092,10 +3068,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477944</v>
+        <v>477446</v>
       </c>
       <c r="R22" t="n">
-        <v>6951693</v>
+        <v>6951749</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3154,10 +3130,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154195</v>
+        <v>122154214</v>
       </c>
       <c r="B23" t="n">
-        <v>74744</v>
+        <v>79733</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,21 +3146,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3194,10 +3165,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477495</v>
+        <v>477421</v>
       </c>
       <c r="R23" t="n">
-        <v>6951727</v>
+        <v>6951454</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3256,10 +3227,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154224</v>
+        <v>122154197</v>
       </c>
       <c r="B24" t="n">
-        <v>56592</v>
+        <v>79762</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3272,21 +3243,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102613</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3296,10 +3262,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477538</v>
+        <v>477617</v>
       </c>
       <c r="R24" t="n">
-        <v>6951618</v>
+        <v>6951666</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,10 +3324,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154213</v>
+        <v>122154170</v>
       </c>
       <c r="B25" t="n">
-        <v>79761</v>
+        <v>57490</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3374,34 +3340,33 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>103031</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477424</v>
+        <v>477882</v>
       </c>
       <c r="R25" t="n">
-        <v>6951452</v>
+        <v>6951635</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3460,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154216</v>
+        <v>122154207</v>
       </c>
       <c r="B26" t="n">
-        <v>74752</v>
+        <v>74744</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,25 +3437,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>492</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3500,10 +3460,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477457</v>
+        <v>477445</v>
       </c>
       <c r="R26" t="n">
-        <v>6951419</v>
+        <v>6951570</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3562,10 +3522,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154201</v>
+        <v>122154202</v>
       </c>
       <c r="B27" t="n">
-        <v>74744</v>
+        <v>98115</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3574,25 +3534,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
+        <v>220093</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,10 +3557,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477404</v>
+        <v>477389</v>
       </c>
       <c r="R27" t="n">
-        <v>6951629</v>
+        <v>6951610</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3664,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154169</v>
+        <v>122154203</v>
       </c>
       <c r="B28" t="n">
-        <v>56581</v>
+        <v>90813</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,38 +3635,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477886</v>
+        <v>477381</v>
       </c>
       <c r="R28" t="n">
-        <v>6951641</v>
+        <v>6951610</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3770,10 +3716,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154219</v>
+        <v>122154209</v>
       </c>
       <c r="B29" t="n">
-        <v>79732</v>
+        <v>79762</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3782,25 +3728,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3810,10 +3751,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477495</v>
+        <v>477462</v>
       </c>
       <c r="R29" t="n">
-        <v>6951463</v>
+        <v>6951485</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3872,10 +3813,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154208</v>
+        <v>122154213</v>
       </c>
       <c r="B30" t="n">
-        <v>79733</v>
+        <v>79762</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3884,25 +3825,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3912,10 +3848,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477462</v>
+        <v>477424</v>
       </c>
       <c r="R30" t="n">
-        <v>6951484</v>
+        <v>6951452</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3974,10 +3910,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154189</v>
+        <v>122154173</v>
       </c>
       <c r="B31" t="n">
-        <v>74744</v>
+        <v>78652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3990,21 +3926,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4014,10 +3945,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477405</v>
+        <v>477825</v>
       </c>
       <c r="R31" t="n">
-        <v>6951731</v>
+        <v>6951660</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4076,10 +4007,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154212</v>
+        <v>122154225</v>
       </c>
       <c r="B32" t="n">
-        <v>91199</v>
+        <v>79733</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4092,16 +4023,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6040186</v>
+        <v>6458</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4111,10 +4042,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477420</v>
+        <v>477572</v>
       </c>
       <c r="R32" t="n">
-        <v>6951455</v>
+        <v>6951618</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4155,7 +4086,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4174,10 +4104,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154170</v>
+        <v>122154204</v>
       </c>
       <c r="B33" t="n">
-        <v>57490</v>
+        <v>98115</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,38 +4120,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
+        <v>220093</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477882</v>
+        <v>477373</v>
       </c>
       <c r="R33" t="n">
-        <v>6951635</v>
+        <v>6951613</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4280,10 +4201,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154214</v>
+        <v>122154189</v>
       </c>
       <c r="B34" t="n">
-        <v>79732</v>
+        <v>74745</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4296,21 +4217,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>308</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4320,10 +4236,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477421</v>
+        <v>477405</v>
       </c>
       <c r="R34" t="n">
-        <v>6951454</v>
+        <v>6951731</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4382,10 +4298,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154220</v>
+        <v>122154195</v>
       </c>
       <c r="B35" t="n">
-        <v>79761</v>
+        <v>74745</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4394,25 +4310,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>308</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4422,10 +4333,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477476</v>
+        <v>477495</v>
       </c>
       <c r="R35" t="n">
-        <v>6951463</v>
+        <v>6951727</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4484,10 +4395,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154207</v>
+        <v>122154171</v>
       </c>
       <c r="B36" t="n">
-        <v>74743</v>
+        <v>79733</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4496,25 +4407,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>492</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Smalskaftslav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4524,10 +4430,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477445</v>
+        <v>477875</v>
       </c>
       <c r="R36" t="n">
-        <v>6951570</v>
+        <v>6951643</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4586,10 +4492,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154215</v>
+        <v>122154216</v>
       </c>
       <c r="B37" t="n">
-        <v>56581</v>
+        <v>74753</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4602,21 +4508,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>6440</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4626,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477438</v>
+        <v>477457</v>
       </c>
       <c r="R37" t="n">
-        <v>6951412</v>
+        <v>6951419</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4688,10 +4589,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154188</v>
+        <v>122154227</v>
       </c>
       <c r="B38" t="n">
-        <v>74752</v>
+        <v>79733</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4704,21 +4605,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,10 +4624,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477377</v>
+        <v>477615</v>
       </c>
       <c r="R38" t="n">
-        <v>6951731</v>
+        <v>6951614</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,10 +4686,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154185</v>
+        <v>122154212</v>
       </c>
       <c r="B39" t="n">
-        <v>90826</v>
+        <v>91204</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4806,21 +4702,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4830,10 +4721,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477372</v>
+        <v>477420</v>
       </c>
       <c r="R39" t="n">
-        <v>6951655</v>
+        <v>6951455</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4874,6 +4765,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4892,10 +4784,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154209</v>
+        <v>122154191</v>
       </c>
       <c r="B40" t="n">
-        <v>79761</v>
+        <v>98115</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4908,21 +4800,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>220093</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4932,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477462</v>
+        <v>477424</v>
       </c>
       <c r="R40" t="n">
-        <v>6951485</v>
+        <v>6951736</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4994,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154177</v>
+        <v>122154174</v>
       </c>
       <c r="B41" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5010,21 +4897,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5034,10 +4916,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477767</v>
+        <v>477833</v>
       </c>
       <c r="R41" t="n">
-        <v>6951662</v>
+        <v>6951669</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5096,10 +4978,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122154225</v>
+        <v>122154177</v>
       </c>
       <c r="B42" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5112,21 +4994,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5136,10 +5013,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477572</v>
+        <v>477767</v>
       </c>
       <c r="R42" t="n">
-        <v>6951618</v>
+        <v>6951662</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5198,10 +5075,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154218</v>
+        <v>122154220</v>
       </c>
       <c r="B43" t="n">
-        <v>98106</v>
+        <v>79762</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5214,21 +5091,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
+        <v>6462</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5238,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477479</v>
+        <v>477476</v>
       </c>
       <c r="R43" t="n">
-        <v>6951442</v>
+        <v>6951463</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5300,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154200</v>
+        <v>122154172</v>
       </c>
       <c r="B44" t="n">
-        <v>78651</v>
+        <v>5173</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5312,25 +5184,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5340,10 +5207,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477435</v>
+        <v>477879</v>
       </c>
       <c r="R44" t="n">
-        <v>6951645</v>
+        <v>6951648</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5402,10 +5269,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154174</v>
+        <v>122154187</v>
       </c>
       <c r="B45" t="n">
-        <v>79732</v>
+        <v>5173</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5414,25 +5281,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5442,10 +5304,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477833</v>
+        <v>477368</v>
       </c>
       <c r="R45" t="n">
-        <v>6951669</v>
+        <v>6951718</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5504,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154175</v>
+        <v>122154186</v>
       </c>
       <c r="B46" t="n">
-        <v>90804</v>
+        <v>5173</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5516,25 +5378,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5544,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477793</v>
+        <v>477370</v>
       </c>
       <c r="R46" t="n">
-        <v>6951655</v>
+        <v>6951711</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5606,10 +5463,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154171</v>
+        <v>122154208</v>
       </c>
       <c r="B47" t="n">
-        <v>79732</v>
+        <v>79734</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5622,21 +5479,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5646,10 +5498,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477875</v>
+        <v>477462</v>
       </c>
       <c r="R47" t="n">
-        <v>6951643</v>
+        <v>6951484</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5708,10 +5560,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154227</v>
+        <v>122154217</v>
       </c>
       <c r="B48" t="n">
-        <v>79732</v>
+        <v>57379</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5724,34 +5576,33 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477615</v>
+        <v>477473</v>
       </c>
       <c r="R48" t="n">
-        <v>6951614</v>
+        <v>6951436</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5810,10 +5661,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154198</v>
+        <v>122154201</v>
       </c>
       <c r="B49" t="n">
-        <v>79732</v>
+        <v>74745</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5826,21 +5677,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>308</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5850,10 +5696,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477617</v>
+        <v>477404</v>
       </c>
       <c r="R49" t="n">
-        <v>6951666</v>
+        <v>6951629</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5912,10 +5758,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154190</v>
+        <v>122154211</v>
       </c>
       <c r="B50" t="n">
-        <v>98106</v>
+        <v>90757</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5924,25 +5770,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
+        <v>112</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5952,10 +5793,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477407</v>
+        <v>477448</v>
       </c>
       <c r="R50" t="n">
-        <v>6951732</v>
+        <v>6951476</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6014,10 +5855,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154204</v>
+        <v>122154210</v>
       </c>
       <c r="B51" t="n">
-        <v>98106</v>
+        <v>79733</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6026,25 +5867,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6054,10 +5890,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477373</v>
+        <v>477464</v>
       </c>
       <c r="R51" t="n">
-        <v>6951613</v>
+        <v>6951483</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6116,10 +5952,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154173</v>
+        <v>122154160</v>
       </c>
       <c r="B52" t="n">
-        <v>78651</v>
+        <v>98128</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6128,25 +5964,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>219790</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6156,10 +5987,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477825</v>
+        <v>477847</v>
       </c>
       <c r="R52" t="n">
-        <v>6951660</v>
+        <v>6951679</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6218,10 +6049,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154186</v>
+        <v>122154221</v>
       </c>
       <c r="B53" t="n">
-        <v>5173</v>
+        <v>79734</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6230,25 +6061,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6258,10 +6084,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477370</v>
+        <v>477477</v>
       </c>
       <c r="R53" t="n">
-        <v>6951711</v>
+        <v>6951466</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6320,10 +6146,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122154172</v>
+        <v>122154185</v>
       </c>
       <c r="B54" t="n">
-        <v>5173</v>
+        <v>90831</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6332,25 +6158,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6360,10 +6181,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477879</v>
+        <v>477372</v>
       </c>
       <c r="R54" t="n">
-        <v>6951648</v>
+        <v>6951655</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6422,10 +6243,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122154210</v>
+        <v>122154198</v>
       </c>
       <c r="B55" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6440,11 +6261,6 @@
       <c r="E55" t="n">
         <v>6458</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -6462,10 +6278,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477464</v>
+        <v>477617</v>
       </c>
       <c r="R55" t="n">
-        <v>6951483</v>
+        <v>6951666</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6524,10 +6340,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122154197</v>
+        <v>122154206</v>
       </c>
       <c r="B56" t="n">
-        <v>79761</v>
+        <v>78652</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,25 +6352,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6564,10 +6375,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477617</v>
+        <v>477411</v>
       </c>
       <c r="R56" t="n">
-        <v>6951666</v>
+        <v>6951546</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6626,10 +6437,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122154160</v>
+        <v>122154169</v>
       </c>
       <c r="B57" t="n">
-        <v>98119</v>
+        <v>56581</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6638,38 +6449,37 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
+        <v>102612</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477847</v>
+        <v>477886</v>
       </c>
       <c r="R57" t="n">
-        <v>6951679</v>
+        <v>6951641</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6728,10 +6538,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122154187</v>
+        <v>122154188</v>
       </c>
       <c r="B58" t="n">
-        <v>5173</v>
+        <v>74753</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6740,25 +6550,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6440</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6768,10 +6573,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477368</v>
+        <v>477377</v>
       </c>
       <c r="R58" t="n">
-        <v>6951718</v>
+        <v>6951731</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6830,10 +6635,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154192</v>
+        <v>122154218</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>98115</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6846,21 +6651,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
+        <v>220093</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6870,10 +6670,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477446</v>
+        <v>477479</v>
       </c>
       <c r="R59" t="n">
-        <v>6951749</v>
+        <v>6951442</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6932,10 +6732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154202</v>
+        <v>122154161</v>
       </c>
       <c r="B60" t="n">
-        <v>98106</v>
+        <v>79734</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6944,25 +6744,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6972,10 +6767,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477389</v>
+        <v>477944</v>
       </c>
       <c r="R60" t="n">
-        <v>6951610</v>
+        <v>6951693</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,10 +6829,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154191</v>
+        <v>122154215</v>
       </c>
       <c r="B61" t="n">
-        <v>98106</v>
+        <v>56581</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7046,25 +6841,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
+        <v>102612</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7074,10 +6864,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477424</v>
+        <v>477438</v>
       </c>
       <c r="R61" t="n">
-        <v>6951736</v>
+        <v>6951412</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7139,7 +6929,7 @@
         <v>122154205</v>
       </c>
       <c r="B62" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7153,11 +6943,6 @@
       </c>
       <c r="E62" t="n">
         <v>221945</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7238,10 +7023,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154211</v>
+        <v>122154200</v>
       </c>
       <c r="B63" t="n">
-        <v>90752</v>
+        <v>78652</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7254,21 +7039,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>112</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Stjärntagging</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477448</v>
+        <v>477435</v>
       </c>
       <c r="R63" t="n">
-        <v>6951476</v>
+        <v>6951645</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7340,10 +7120,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154203</v>
+        <v>122154190</v>
       </c>
       <c r="B64" t="n">
-        <v>90808</v>
+        <v>98115</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7352,25 +7132,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>220093</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7380,10 +7155,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477381</v>
+        <v>477407</v>
       </c>
       <c r="R64" t="n">
-        <v>6951610</v>
+        <v>6951732</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7442,10 +7217,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178224</v>
+        <v>122178235</v>
       </c>
       <c r="B65" t="n">
-        <v>94228</v>
+        <v>79241</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7454,25 +7229,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2387</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Källpraktmossa</t>
-        </is>
+        <v>229821</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7482,10 +7252,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477572</v>
+        <v>477573</v>
       </c>
       <c r="R65" t="n">
-        <v>6951626</v>
+        <v>6951539</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7544,10 +7314,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178236</v>
+        <v>122178228</v>
       </c>
       <c r="B66" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7560,21 +7330,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7584,10 +7349,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477559</v>
+        <v>477590</v>
       </c>
       <c r="R66" t="n">
-        <v>6951532</v>
+        <v>6951600</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7646,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178247</v>
+        <v>122178221</v>
       </c>
       <c r="B67" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7664,11 +7429,6 @@
       <c r="E67" t="n">
         <v>6458</v>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -7686,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477540</v>
+        <v>477543</v>
       </c>
       <c r="R67" t="n">
-        <v>6951433</v>
+        <v>6951588</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7748,10 +7508,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178220</v>
+        <v>122178246</v>
       </c>
       <c r="B68" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7766,11 +7526,6 @@
       <c r="E68" t="n">
         <v>6458</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -7788,10 +7543,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477556</v>
+        <v>477535</v>
       </c>
       <c r="R68" t="n">
-        <v>6951549</v>
+        <v>6951442</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7850,10 +7605,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122172640</v>
+        <v>122178247</v>
       </c>
       <c r="B69" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7868,11 +7623,6 @@
       <c r="E69" t="n">
         <v>6458</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -7890,10 +7640,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477949</v>
+        <v>477540</v>
       </c>
       <c r="R69" t="n">
-        <v>6951706</v>
+        <v>6951433</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7920,12 +7670,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7940,22 +7690,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178243</v>
+        <v>122178223</v>
       </c>
       <c r="B70" t="n">
-        <v>79732</v>
+        <v>94045</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7964,25 +7714,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>2412</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7992,10 +7737,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477538</v>
+        <v>477540</v>
       </c>
       <c r="R70" t="n">
-        <v>6951448</v>
+        <v>6951613</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8054,10 +7799,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178235</v>
+        <v>122178229</v>
       </c>
       <c r="B71" t="n">
-        <v>79240</v>
+        <v>79769</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8066,25 +7811,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
+        <v>6464</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8094,10 +7834,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477573</v>
+        <v>477587</v>
       </c>
       <c r="R71" t="n">
-        <v>6951539</v>
+        <v>6951569</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8156,10 +7896,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122172652</v>
+        <v>122178236</v>
       </c>
       <c r="B72" t="n">
-        <v>98106</v>
+        <v>78652</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8168,25 +7908,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8196,10 +7931,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477755</v>
+        <v>477559</v>
       </c>
       <c r="R72" t="n">
-        <v>6951671</v>
+        <v>6951532</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8226,12 +7961,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8246,22 +7981,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178245</v>
+        <v>122178237</v>
       </c>
       <c r="B73" t="n">
-        <v>74752</v>
+        <v>79733</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8274,21 +8009,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8298,10 +8028,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477542</v>
+        <v>477518</v>
       </c>
       <c r="R73" t="n">
-        <v>6951443</v>
+        <v>6951490</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8360,10 +8090,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178228</v>
+        <v>122172640</v>
       </c>
       <c r="B74" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8378,11 +8108,6 @@
       <c r="E74" t="n">
         <v>6458</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -8400,10 +8125,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477590</v>
+        <v>477949</v>
       </c>
       <c r="R74" t="n">
-        <v>6951600</v>
+        <v>6951706</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8430,12 +8155,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8450,22 +8175,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178221</v>
+        <v>122178242</v>
       </c>
       <c r="B75" t="n">
-        <v>79732</v>
+        <v>74753</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8478,21 +8203,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6440</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8502,10 +8222,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477543</v>
+        <v>477534</v>
       </c>
       <c r="R75" t="n">
-        <v>6951588</v>
+        <v>6951448</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8564,10 +8284,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122178237</v>
+        <v>122178245</v>
       </c>
       <c r="B76" t="n">
-        <v>79732</v>
+        <v>74753</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8580,21 +8300,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6440</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8604,10 +8319,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477518</v>
+        <v>477542</v>
       </c>
       <c r="R76" t="n">
-        <v>6951490</v>
+        <v>6951443</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8666,10 +8381,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122178231</v>
+        <v>122172654</v>
       </c>
       <c r="B77" t="n">
-        <v>79732</v>
+        <v>97165</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8678,25 +8393,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8706,10 +8416,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477585</v>
+        <v>477639</v>
       </c>
       <c r="R77" t="n">
-        <v>6951573</v>
+        <v>6951706</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8736,12 +8446,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8756,22 +8466,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122178246</v>
+        <v>122178227</v>
       </c>
       <c r="B78" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8786,11 +8496,6 @@
       <c r="E78" t="n">
         <v>6458</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -8808,10 +8513,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477535</v>
+        <v>477598</v>
       </c>
       <c r="R78" t="n">
-        <v>6951442</v>
+        <v>6951610</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8870,10 +8575,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122178232</v>
+        <v>122178231</v>
       </c>
       <c r="B79" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8888,11 +8593,6 @@
       <c r="E79" t="n">
         <v>6458</v>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -8910,10 +8610,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477570</v>
+        <v>477585</v>
       </c>
       <c r="R79" t="n">
-        <v>6951563</v>
+        <v>6951573</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8972,10 +8672,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122178234</v>
+        <v>122178226</v>
       </c>
       <c r="B80" t="n">
-        <v>79732</v>
+        <v>74745</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8988,21 +8688,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>308</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9012,10 +8707,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477584</v>
+        <v>477581</v>
       </c>
       <c r="R80" t="n">
-        <v>6951542</v>
+        <v>6951614</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9074,10 +8769,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122178222</v>
+        <v>122178234</v>
       </c>
       <c r="B81" t="n">
-        <v>97156</v>
+        <v>79733</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9086,25 +8781,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9114,10 +8804,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477540</v>
+        <v>477584</v>
       </c>
       <c r="R81" t="n">
-        <v>6951594</v>
+        <v>6951542</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9176,10 +8866,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122178223</v>
+        <v>122178220</v>
       </c>
       <c r="B82" t="n">
-        <v>94036</v>
+        <v>79733</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9188,25 +8878,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2412</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Källmossa</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9216,10 +8901,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477540</v>
+        <v>477556</v>
       </c>
       <c r="R82" t="n">
-        <v>6951613</v>
+        <v>6951549</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9278,10 +8963,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122172653</v>
+        <v>122178225</v>
       </c>
       <c r="B83" t="n">
-        <v>90826</v>
+        <v>97165</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9290,25 +8975,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9318,10 +8998,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477642</v>
+        <v>477580</v>
       </c>
       <c r="R83" t="n">
-        <v>6951702</v>
+        <v>6951617</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9348,12 +9028,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9368,22 +9048,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122178229</v>
+        <v>122178222</v>
       </c>
       <c r="B84" t="n">
-        <v>79768</v>
+        <v>97165</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9396,21 +9076,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9420,10 +9095,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477587</v>
+        <v>477540</v>
       </c>
       <c r="R84" t="n">
-        <v>6951569</v>
+        <v>6951594</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9482,10 +9157,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122178242</v>
+        <v>122172652</v>
       </c>
       <c r="B85" t="n">
-        <v>74752</v>
+        <v>98115</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9494,25 +9169,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>220093</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9522,10 +9192,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477534</v>
+        <v>477755</v>
       </c>
       <c r="R85" t="n">
-        <v>6951448</v>
+        <v>6951671</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9552,12 +9222,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9572,22 +9242,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178226</v>
+        <v>122178243</v>
       </c>
       <c r="B86" t="n">
-        <v>74744</v>
+        <v>79733</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9600,21 +9270,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>308</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9624,10 +9289,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477581</v>
+        <v>477538</v>
       </c>
       <c r="R86" t="n">
-        <v>6951614</v>
+        <v>6951448</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9686,10 +9351,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178227</v>
+        <v>122178244</v>
       </c>
       <c r="B87" t="n">
-        <v>79732</v>
+        <v>79643</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9702,21 +9367,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>2080</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9726,10 +9386,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477598</v>
+        <v>477538</v>
       </c>
       <c r="R87" t="n">
-        <v>6951610</v>
+        <v>6951440</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9788,10 +9448,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122172654</v>
+        <v>122178238</v>
       </c>
       <c r="B88" t="n">
-        <v>97156</v>
+        <v>94237</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9804,21 +9464,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>2387</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9828,10 +9483,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477639</v>
+        <v>477538</v>
       </c>
       <c r="R88" t="n">
-        <v>6951706</v>
+        <v>6951456</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9858,12 +9513,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9878,22 +9533,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122178238</v>
+        <v>122172653</v>
       </c>
       <c r="B89" t="n">
-        <v>94228</v>
+        <v>90831</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9902,25 +9557,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2387</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Källpraktmossa</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9930,10 +9580,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477538</v>
+        <v>477642</v>
       </c>
       <c r="R89" t="n">
-        <v>6951456</v>
+        <v>6951702</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9960,12 +9610,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9980,22 +9630,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122178225</v>
+        <v>122178232</v>
       </c>
       <c r="B90" t="n">
-        <v>97156</v>
+        <v>79733</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10004,25 +9654,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10032,10 +9677,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477580</v>
+        <v>477570</v>
       </c>
       <c r="R90" t="n">
-        <v>6951617</v>
+        <v>6951563</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10094,10 +9739,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122178244</v>
+        <v>122178224</v>
       </c>
       <c r="B91" t="n">
-        <v>79642</v>
+        <v>94237</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10106,25 +9751,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2080</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Skorpgelélav</t>
-        </is>
+        <v>2387</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10134,10 +9774,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>477538</v>
+        <v>477572</v>
       </c>
       <c r="R91" t="n">
-        <v>6951440</v>
+        <v>6951626</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -3619,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154203</v>
+        <v>122154173</v>
       </c>
       <c r="B28" t="n">
-        <v>90813</v>
+        <v>78652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477381</v>
+        <v>477825</v>
       </c>
       <c r="R28" t="n">
-        <v>6951610</v>
+        <v>6951660</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154173</v>
+        <v>122154203</v>
       </c>
       <c r="B31" t="n">
-        <v>78652</v>
+        <v>90813</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3926,16 +3926,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477825</v>
+        <v>477381</v>
       </c>
       <c r="R31" t="n">
-        <v>6951660</v>
+        <v>6951610</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154186</v>
+        <v>122154208</v>
       </c>
       <c r="B46" t="n">
-        <v>5173</v>
+        <v>79734</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,20 +5378,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477370</v>
+        <v>477462</v>
       </c>
       <c r="R46" t="n">
-        <v>6951711</v>
+        <v>6951484</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154208</v>
+        <v>122154186</v>
       </c>
       <c r="B47" t="n">
-        <v>79734</v>
+        <v>5173</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5475,20 +5475,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477462</v>
+        <v>477370</v>
       </c>
       <c r="R47" t="n">
-        <v>6951484</v>
+        <v>6951711</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154201</v>
+        <v>122154210</v>
       </c>
       <c r="B49" t="n">
-        <v>74745</v>
+        <v>79733</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5677,16 +5677,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477404</v>
+        <v>477464</v>
       </c>
       <c r="R49" t="n">
-        <v>6951629</v>
+        <v>6951483</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154211</v>
+        <v>122154201</v>
       </c>
       <c r="B50" t="n">
-        <v>90757</v>
+        <v>74745</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5774,16 +5774,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477448</v>
+        <v>477404</v>
       </c>
       <c r="R50" t="n">
-        <v>6951476</v>
+        <v>6951629</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5855,10 +5855,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154210</v>
+        <v>122154211</v>
       </c>
       <c r="B51" t="n">
-        <v>79733</v>
+        <v>90757</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5871,16 +5871,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477464</v>
+        <v>477448</v>
       </c>
       <c r="R51" t="n">
-        <v>6951483</v>
+        <v>6951476</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6635,10 +6635,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154218</v>
+        <v>122154161</v>
       </c>
       <c r="B59" t="n">
-        <v>98115</v>
+        <v>79734</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6647,20 +6647,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477479</v>
+        <v>477944</v>
       </c>
       <c r="R59" t="n">
-        <v>6951442</v>
+        <v>6951693</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6732,10 +6732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154161</v>
+        <v>122154218</v>
       </c>
       <c r="B60" t="n">
-        <v>79734</v>
+        <v>98115</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6744,20 +6744,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>220093</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477944</v>
+        <v>477479</v>
       </c>
       <c r="R60" t="n">
-        <v>6951693</v>
+        <v>6951442</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178229</v>
+        <v>122178236</v>
       </c>
       <c r="B71" t="n">
-        <v>79769</v>
+        <v>78652</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7811,20 +7811,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477587</v>
+        <v>477559</v>
       </c>
       <c r="R71" t="n">
-        <v>6951569</v>
+        <v>6951532</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178236</v>
+        <v>122178229</v>
       </c>
       <c r="B72" t="n">
-        <v>78652</v>
+        <v>79769</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7908,20 +7908,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7931,10 +7931,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477559</v>
+        <v>477587</v>
       </c>
       <c r="R72" t="n">
-        <v>6951532</v>
+        <v>6951569</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9060,10 +9060,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122178222</v>
+        <v>122172652</v>
       </c>
       <c r="B84" t="n">
-        <v>97165</v>
+        <v>98115</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9076,16 +9076,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9095,10 +9095,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477540</v>
+        <v>477755</v>
       </c>
       <c r="R84" t="n">
-        <v>6951594</v>
+        <v>6951671</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9125,12 +9125,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9145,22 +9145,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122172652</v>
+        <v>122178222</v>
       </c>
       <c r="B85" t="n">
-        <v>98115</v>
+        <v>97165</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9173,16 +9173,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220093</v>
+        <v>221945</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477755</v>
+        <v>477540</v>
       </c>
       <c r="R85" t="n">
-        <v>6951671</v>
+        <v>6951594</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9222,12 +9222,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9242,22 +9242,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178243</v>
+        <v>122178244</v>
       </c>
       <c r="B86" t="n">
-        <v>79733</v>
+        <v>79643</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9270,16 +9270,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2080</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9292,7 +9292,7 @@
         <v>477538</v>
       </c>
       <c r="R86" t="n">
-        <v>6951448</v>
+        <v>6951440</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9351,10 +9351,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178244</v>
+        <v>122178238</v>
       </c>
       <c r="B87" t="n">
-        <v>79643</v>
+        <v>94237</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9363,20 +9363,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2080</v>
+        <v>2387</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9389,7 +9389,7 @@
         <v>477538</v>
       </c>
       <c r="R87" t="n">
-        <v>6951440</v>
+        <v>6951456</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9448,10 +9448,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178238</v>
+        <v>122178243</v>
       </c>
       <c r="B88" t="n">
-        <v>94237</v>
+        <v>79733</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9460,20 +9460,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9486,7 +9486,7 @@
         <v>477538</v>
       </c>
       <c r="R88" t="n">
-        <v>6951456</v>
+        <v>6951448</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -3425,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154207</v>
+        <v>122154202</v>
       </c>
       <c r="B26" t="n">
-        <v>74744</v>
+        <v>98115</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3437,20 +3437,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>492</v>
+        <v>220093</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477445</v>
+        <v>477389</v>
       </c>
       <c r="R26" t="n">
-        <v>6951570</v>
+        <v>6951610</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154202</v>
+        <v>122154207</v>
       </c>
       <c r="B27" t="n">
-        <v>98115</v>
+        <v>74744</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3534,20 +3534,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220093</v>
+        <v>492</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477389</v>
+        <v>477445</v>
       </c>
       <c r="R27" t="n">
-        <v>6951610</v>
+        <v>6951570</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154173</v>
+        <v>122154203</v>
       </c>
       <c r="B28" t="n">
-        <v>78652</v>
+        <v>90813</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3635,16 +3635,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477825</v>
+        <v>477381</v>
       </c>
       <c r="R28" t="n">
-        <v>6951660</v>
+        <v>6951610</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154203</v>
+        <v>122154173</v>
       </c>
       <c r="B31" t="n">
-        <v>90813</v>
+        <v>78652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3926,16 +3926,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477381</v>
+        <v>477825</v>
       </c>
       <c r="R31" t="n">
-        <v>6951610</v>
+        <v>6951660</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4201,10 +4201,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154189</v>
+        <v>122154171</v>
       </c>
       <c r="B34" t="n">
-        <v>74745</v>
+        <v>79733</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4217,16 +4217,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477405</v>
+        <v>477875</v>
       </c>
       <c r="R34" t="n">
-        <v>6951731</v>
+        <v>6951643</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4298,10 +4298,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154195</v>
+        <v>122154216</v>
       </c>
       <c r="B35" t="n">
-        <v>74745</v>
+        <v>74753</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4314,16 +4314,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477495</v>
+        <v>477457</v>
       </c>
       <c r="R35" t="n">
-        <v>6951727</v>
+        <v>6951419</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154171</v>
+        <v>122154189</v>
       </c>
       <c r="B36" t="n">
-        <v>79733</v>
+        <v>74745</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4411,16 +4411,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477875</v>
+        <v>477405</v>
       </c>
       <c r="R36" t="n">
-        <v>6951643</v>
+        <v>6951731</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154216</v>
+        <v>122154195</v>
       </c>
       <c r="B37" t="n">
-        <v>74753</v>
+        <v>74745</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4508,16 +4508,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477457</v>
+        <v>477495</v>
       </c>
       <c r="R37" t="n">
-        <v>6951419</v>
+        <v>6951727</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154208</v>
+        <v>122154186</v>
       </c>
       <c r="B46" t="n">
-        <v>79734</v>
+        <v>5173</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,20 +5378,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>100526</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477462</v>
+        <v>477370</v>
       </c>
       <c r="R46" t="n">
-        <v>6951484</v>
+        <v>6951711</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154186</v>
+        <v>122154208</v>
       </c>
       <c r="B47" t="n">
-        <v>5173</v>
+        <v>79734</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5475,20 +5475,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>2081</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477370</v>
+        <v>477462</v>
       </c>
       <c r="R47" t="n">
-        <v>6951711</v>
+        <v>6951484</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154210</v>
+        <v>122154201</v>
       </c>
       <c r="B49" t="n">
-        <v>79733</v>
+        <v>74745</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5677,16 +5677,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477464</v>
+        <v>477404</v>
       </c>
       <c r="R49" t="n">
-        <v>6951483</v>
+        <v>6951629</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154201</v>
+        <v>122154211</v>
       </c>
       <c r="B50" t="n">
-        <v>74745</v>
+        <v>90757</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5774,16 +5774,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477404</v>
+        <v>477448</v>
       </c>
       <c r="R50" t="n">
-        <v>6951629</v>
+        <v>6951476</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5855,10 +5855,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154211</v>
+        <v>122154210</v>
       </c>
       <c r="B51" t="n">
-        <v>90757</v>
+        <v>79733</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5871,16 +5871,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477448</v>
+        <v>477464</v>
       </c>
       <c r="R51" t="n">
-        <v>6951476</v>
+        <v>6951483</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6635,10 +6635,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154161</v>
+        <v>122154218</v>
       </c>
       <c r="B59" t="n">
-        <v>79734</v>
+        <v>98115</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6647,20 +6647,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>220093</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477944</v>
+        <v>477479</v>
       </c>
       <c r="R59" t="n">
-        <v>6951693</v>
+        <v>6951442</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6732,10 +6732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154218</v>
+        <v>122154161</v>
       </c>
       <c r="B60" t="n">
-        <v>98115</v>
+        <v>79734</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6744,20 +6744,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477479</v>
+        <v>477944</v>
       </c>
       <c r="R60" t="n">
-        <v>6951442</v>
+        <v>6951693</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -9060,10 +9060,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122172652</v>
+        <v>122178222</v>
       </c>
       <c r="B84" t="n">
-        <v>98115</v>
+        <v>97165</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9076,16 +9076,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220093</v>
+        <v>221945</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9095,10 +9095,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477755</v>
+        <v>477540</v>
       </c>
       <c r="R84" t="n">
-        <v>6951671</v>
+        <v>6951594</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9125,12 +9125,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9145,22 +9145,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122178222</v>
+        <v>122172652</v>
       </c>
       <c r="B85" t="n">
-        <v>97165</v>
+        <v>98115</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9173,16 +9173,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477540</v>
+        <v>477755</v>
       </c>
       <c r="R85" t="n">
-        <v>6951594</v>
+        <v>6951671</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9222,12 +9222,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9242,22 +9242,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178244</v>
+        <v>122178243</v>
       </c>
       <c r="B86" t="n">
-        <v>79643</v>
+        <v>79733</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9270,16 +9270,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2080</v>
+        <v>6458</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9292,7 +9292,7 @@
         <v>477538</v>
       </c>
       <c r="R86" t="n">
-        <v>6951440</v>
+        <v>6951448</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9351,10 +9351,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178238</v>
+        <v>122178244</v>
       </c>
       <c r="B87" t="n">
-        <v>94237</v>
+        <v>79643</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9363,20 +9363,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2387</v>
+        <v>2080</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9389,7 +9389,7 @@
         <v>477538</v>
       </c>
       <c r="R87" t="n">
-        <v>6951456</v>
+        <v>6951440</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9448,10 +9448,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178243</v>
+        <v>122178238</v>
       </c>
       <c r="B88" t="n">
-        <v>79733</v>
+        <v>94237</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9460,20 +9460,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9486,7 +9486,7 @@
         <v>477538</v>
       </c>
       <c r="R88" t="n">
-        <v>6951448</v>
+        <v>6951456</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154175</v>
+        <v>122154225</v>
       </c>
       <c r="B19" t="n">
-        <v>90809</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2758,16 +2758,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2777,10 +2782,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477793</v>
+        <v>477572</v>
       </c>
       <c r="R19" t="n">
-        <v>6951655</v>
+        <v>6951618</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2839,10 +2844,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154219</v>
+        <v>122154200</v>
       </c>
       <c r="B20" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2855,16 +2860,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2874,10 +2884,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477495</v>
+        <v>477435</v>
       </c>
       <c r="R20" t="n">
-        <v>6951463</v>
+        <v>6951645</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2936,10 +2946,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154224</v>
+        <v>122154197</v>
       </c>
       <c r="B21" t="n">
-        <v>56592</v>
+        <v>79766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2952,16 +2962,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102613</v>
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,10 +2986,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477538</v>
+        <v>477617</v>
       </c>
       <c r="R21" t="n">
-        <v>6951618</v>
+        <v>6951666</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3033,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154192</v>
+        <v>122154219</v>
       </c>
       <c r="B22" t="n">
-        <v>79637</v>
+        <v>79737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3045,20 +3060,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3068,10 +3088,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477446</v>
+        <v>477495</v>
       </c>
       <c r="R22" t="n">
-        <v>6951749</v>
+        <v>6951463</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3130,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154214</v>
+        <v>122154169</v>
       </c>
       <c r="B23" t="n">
-        <v>79733</v>
+        <v>56585</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3146,29 +3166,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>102612</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477421</v>
+        <v>477886</v>
       </c>
       <c r="R23" t="n">
-        <v>6951454</v>
+        <v>6951641</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3227,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154197</v>
+        <v>122154206</v>
       </c>
       <c r="B24" t="n">
-        <v>79762</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3239,20 +3268,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3262,10 +3296,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477617</v>
+        <v>477411</v>
       </c>
       <c r="R24" t="n">
-        <v>6951666</v>
+        <v>6951546</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3324,10 +3358,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154170</v>
+        <v>122154190</v>
       </c>
       <c r="B25" t="n">
-        <v>57490</v>
+        <v>98128</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3340,33 +3374,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>220093</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477882</v>
+        <v>477407</v>
       </c>
       <c r="R25" t="n">
-        <v>6951635</v>
+        <v>6951732</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3425,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154202</v>
+        <v>122154216</v>
       </c>
       <c r="B26" t="n">
-        <v>98115</v>
+        <v>74757</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3437,20 +3472,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>6440</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3460,10 +3500,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477389</v>
+        <v>477457</v>
       </c>
       <c r="R26" t="n">
-        <v>6951610</v>
+        <v>6951419</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3522,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154207</v>
+        <v>122154211</v>
       </c>
       <c r="B27" t="n">
-        <v>74744</v>
+        <v>90770</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3534,20 +3574,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>492</v>
+        <v>112</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3557,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477445</v>
+        <v>477448</v>
       </c>
       <c r="R27" t="n">
-        <v>6951570</v>
+        <v>6951476</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3619,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154203</v>
+        <v>122154173</v>
       </c>
       <c r="B28" t="n">
-        <v>90813</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3635,16 +3680,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3654,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477381</v>
+        <v>477825</v>
       </c>
       <c r="R28" t="n">
-        <v>6951610</v>
+        <v>6951660</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3716,10 +3766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154209</v>
+        <v>122154221</v>
       </c>
       <c r="B29" t="n">
-        <v>79762</v>
+        <v>79738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3728,20 +3778,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>2081</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3751,10 +3806,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477462</v>
+        <v>477477</v>
       </c>
       <c r="R29" t="n">
-        <v>6951485</v>
+        <v>6951466</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3813,10 +3868,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154213</v>
+        <v>122154214</v>
       </c>
       <c r="B30" t="n">
-        <v>79762</v>
+        <v>79737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3825,20 +3880,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3848,10 +3908,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477424</v>
+        <v>477421</v>
       </c>
       <c r="R30" t="n">
-        <v>6951452</v>
+        <v>6951454</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3910,10 +3970,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154173</v>
+        <v>122154187</v>
       </c>
       <c r="B31" t="n">
-        <v>78652</v>
+        <v>5173</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3922,20 +3982,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100526</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3945,10 +4010,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477825</v>
+        <v>477368</v>
       </c>
       <c r="R31" t="n">
-        <v>6951660</v>
+        <v>6951718</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4007,10 +4072,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154225</v>
+        <v>122154224</v>
       </c>
       <c r="B32" t="n">
-        <v>79733</v>
+        <v>56596</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4019,20 +4084,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>102613</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4042,7 +4112,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477572</v>
+        <v>477538</v>
       </c>
       <c r="R32" t="n">
         <v>6951618</v>
@@ -4104,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154204</v>
+        <v>122154201</v>
       </c>
       <c r="B33" t="n">
-        <v>98115</v>
+        <v>74749</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4116,20 +4186,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220093</v>
+        <v>308</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4139,10 +4214,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477373</v>
+        <v>477404</v>
       </c>
       <c r="R33" t="n">
-        <v>6951613</v>
+        <v>6951629</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4201,10 +4276,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154171</v>
+        <v>122154220</v>
       </c>
       <c r="B34" t="n">
-        <v>79733</v>
+        <v>79766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4213,20 +4288,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6462</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4236,10 +4316,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477875</v>
+        <v>477476</v>
       </c>
       <c r="R34" t="n">
-        <v>6951643</v>
+        <v>6951463</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4298,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154216</v>
+        <v>122154177</v>
       </c>
       <c r="B35" t="n">
-        <v>74753</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4314,16 +4394,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4333,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477457</v>
+        <v>477767</v>
       </c>
       <c r="R35" t="n">
-        <v>6951419</v>
+        <v>6951662</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4395,10 +4480,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154189</v>
+        <v>122154215</v>
       </c>
       <c r="B36" t="n">
-        <v>74745</v>
+        <v>56585</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4411,16 +4496,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>102612</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4430,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477405</v>
+        <v>477438</v>
       </c>
       <c r="R36" t="n">
-        <v>6951731</v>
+        <v>6951412</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4492,10 +4582,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154195</v>
+        <v>122154191</v>
       </c>
       <c r="B37" t="n">
-        <v>74745</v>
+        <v>98128</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4504,20 +4594,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>220093</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4527,10 +4622,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477495</v>
+        <v>477424</v>
       </c>
       <c r="R37" t="n">
-        <v>6951727</v>
+        <v>6951736</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4589,10 +4684,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154227</v>
+        <v>122154189</v>
       </c>
       <c r="B38" t="n">
-        <v>79733</v>
+        <v>74749</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4605,16 +4700,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>308</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4624,10 +4724,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477615</v>
+        <v>477405</v>
       </c>
       <c r="R38" t="n">
-        <v>6951614</v>
+        <v>6951731</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4686,10 +4786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154212</v>
+        <v>122154172</v>
       </c>
       <c r="B39" t="n">
-        <v>91204</v>
+        <v>5173</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4698,20 +4798,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>100526</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4721,10 +4826,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477420</v>
+        <v>477879</v>
       </c>
       <c r="R39" t="n">
-        <v>6951455</v>
+        <v>6951648</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4765,7 +4870,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4784,10 +4888,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154191</v>
+        <v>122154217</v>
       </c>
       <c r="B40" t="n">
-        <v>98115</v>
+        <v>57383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4796,33 +4900,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220093</v>
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477424</v>
+        <v>477473</v>
       </c>
       <c r="R40" t="n">
-        <v>6951736</v>
+        <v>6951436</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4881,10 +4994,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154174</v>
+        <v>122154171</v>
       </c>
       <c r="B41" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4899,6 +5012,11 @@
       <c r="E41" t="n">
         <v>6458</v>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -4916,10 +5034,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477833</v>
+        <v>477875</v>
       </c>
       <c r="R41" t="n">
-        <v>6951669</v>
+        <v>6951643</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4978,10 +5096,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122154177</v>
+        <v>122154205</v>
       </c>
       <c r="B42" t="n">
-        <v>78652</v>
+        <v>97178</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4990,20 +5108,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221945</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5013,10 +5136,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477767</v>
+        <v>477367</v>
       </c>
       <c r="R42" t="n">
-        <v>6951662</v>
+        <v>6951594</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5075,10 +5198,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154220</v>
+        <v>122154160</v>
       </c>
       <c r="B43" t="n">
-        <v>79762</v>
+        <v>98141</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5091,16 +5214,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>219790</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5110,10 +5238,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477476</v>
+        <v>477847</v>
       </c>
       <c r="R43" t="n">
-        <v>6951463</v>
+        <v>6951679</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5172,10 +5300,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154172</v>
+        <v>122154185</v>
       </c>
       <c r="B44" t="n">
-        <v>5173</v>
+        <v>90844</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5184,20 +5312,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>5432</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5207,10 +5340,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477879</v>
+        <v>477372</v>
       </c>
       <c r="R44" t="n">
-        <v>6951648</v>
+        <v>6951655</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5269,10 +5402,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154187</v>
+        <v>122154195</v>
       </c>
       <c r="B45" t="n">
-        <v>5173</v>
+        <v>74749</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5281,20 +5414,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>308</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5304,10 +5442,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477368</v>
+        <v>477495</v>
       </c>
       <c r="R45" t="n">
-        <v>6951718</v>
+        <v>6951727</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5366,10 +5504,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154186</v>
+        <v>122154161</v>
       </c>
       <c r="B46" t="n">
-        <v>5173</v>
+        <v>79738</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5378,20 +5516,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>2081</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5401,10 +5544,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477370</v>
+        <v>477944</v>
       </c>
       <c r="R46" t="n">
-        <v>6951711</v>
+        <v>6951693</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5463,10 +5606,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154208</v>
+        <v>122154213</v>
       </c>
       <c r="B47" t="n">
-        <v>79734</v>
+        <v>79766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5475,20 +5618,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6462</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5498,10 +5646,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477462</v>
+        <v>477424</v>
       </c>
       <c r="R47" t="n">
-        <v>6951484</v>
+        <v>6951452</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5560,10 +5708,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154217</v>
+        <v>122154186</v>
       </c>
       <c r="B48" t="n">
-        <v>57379</v>
+        <v>5173</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5572,37 +5720,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>100526</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477473</v>
+        <v>477370</v>
       </c>
       <c r="R48" t="n">
-        <v>6951436</v>
+        <v>6951711</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5661,10 +5810,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154201</v>
+        <v>122154209</v>
       </c>
       <c r="B49" t="n">
-        <v>74745</v>
+        <v>79766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5673,20 +5822,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>308</v>
+        <v>6462</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5696,10 +5850,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477404</v>
+        <v>477462</v>
       </c>
       <c r="R49" t="n">
-        <v>6951629</v>
+        <v>6951485</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5758,10 +5912,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154211</v>
+        <v>122154210</v>
       </c>
       <c r="B50" t="n">
-        <v>90757</v>
+        <v>79737</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5774,16 +5928,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>112</v>
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5793,10 +5952,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477448</v>
+        <v>477464</v>
       </c>
       <c r="R50" t="n">
-        <v>6951476</v>
+        <v>6951483</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5855,10 +6014,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154210</v>
+        <v>122154207</v>
       </c>
       <c r="B51" t="n">
-        <v>79733</v>
+        <v>74748</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5867,20 +6026,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>492</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5890,10 +6054,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477464</v>
+        <v>477445</v>
       </c>
       <c r="R51" t="n">
-        <v>6951483</v>
+        <v>6951570</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5952,10 +6116,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154160</v>
+        <v>122154188</v>
       </c>
       <c r="B52" t="n">
-        <v>98128</v>
+        <v>74757</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5964,20 +6128,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>6440</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5987,10 +6156,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477847</v>
+        <v>477377</v>
       </c>
       <c r="R52" t="n">
-        <v>6951679</v>
+        <v>6951731</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6049,10 +6218,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154221</v>
+        <v>122154192</v>
       </c>
       <c r="B53" t="n">
-        <v>79734</v>
+        <v>79641</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6061,20 +6230,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6456</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6084,10 +6258,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477477</v>
+        <v>477446</v>
       </c>
       <c r="R53" t="n">
-        <v>6951466</v>
+        <v>6951749</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6146,10 +6320,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122154185</v>
+        <v>122154170</v>
       </c>
       <c r="B54" t="n">
-        <v>90831</v>
+        <v>57494</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6158,33 +6332,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>103031</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477372</v>
+        <v>477882</v>
       </c>
       <c r="R54" t="n">
-        <v>6951655</v>
+        <v>6951635</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6243,10 +6426,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122154198</v>
+        <v>122154212</v>
       </c>
       <c r="B55" t="n">
-        <v>79733</v>
+        <v>91217</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6259,16 +6442,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6040186</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6278,10 +6461,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477617</v>
+        <v>477420</v>
       </c>
       <c r="R55" t="n">
-        <v>6951666</v>
+        <v>6951455</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6322,6 +6505,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6340,10 +6524,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122154206</v>
+        <v>122154218</v>
       </c>
       <c r="B56" t="n">
-        <v>78652</v>
+        <v>98128</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6352,20 +6536,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220093</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6375,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477411</v>
+        <v>477479</v>
       </c>
       <c r="R56" t="n">
-        <v>6951546</v>
+        <v>6951442</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6437,10 +6626,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122154169</v>
+        <v>122154204</v>
       </c>
       <c r="B57" t="n">
-        <v>56581</v>
+        <v>98128</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6449,37 +6638,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>220093</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477886</v>
+        <v>477373</v>
       </c>
       <c r="R57" t="n">
-        <v>6951641</v>
+        <v>6951613</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6538,10 +6728,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122154188</v>
+        <v>122154175</v>
       </c>
       <c r="B58" t="n">
-        <v>74753</v>
+        <v>90822</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6554,16 +6744,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>1108</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6573,10 +6768,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477377</v>
+        <v>477793</v>
       </c>
       <c r="R58" t="n">
-        <v>6951731</v>
+        <v>6951655</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6635,10 +6830,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154218</v>
+        <v>122154198</v>
       </c>
       <c r="B59" t="n">
-        <v>98115</v>
+        <v>79737</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6647,20 +6842,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220093</v>
+        <v>6458</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6670,10 +6870,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477479</v>
+        <v>477617</v>
       </c>
       <c r="R59" t="n">
-        <v>6951442</v>
+        <v>6951666</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6732,10 +6932,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154161</v>
+        <v>122154174</v>
       </c>
       <c r="B60" t="n">
-        <v>79734</v>
+        <v>79737</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6748,16 +6948,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6767,10 +6972,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477944</v>
+        <v>477833</v>
       </c>
       <c r="R60" t="n">
-        <v>6951693</v>
+        <v>6951669</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6829,10 +7034,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154215</v>
+        <v>122154227</v>
       </c>
       <c r="B61" t="n">
-        <v>56581</v>
+        <v>79737</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6845,16 +7050,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6864,10 +7074,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477438</v>
+        <v>477615</v>
       </c>
       <c r="R61" t="n">
-        <v>6951412</v>
+        <v>6951614</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6926,10 +7136,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154205</v>
+        <v>122154202</v>
       </c>
       <c r="B62" t="n">
-        <v>97165</v>
+        <v>98128</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6942,16 +7152,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>220093</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6961,10 +7176,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477367</v>
+        <v>477389</v>
       </c>
       <c r="R62" t="n">
-        <v>6951594</v>
+        <v>6951610</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7023,10 +7238,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154200</v>
+        <v>122154208</v>
       </c>
       <c r="B63" t="n">
-        <v>78652</v>
+        <v>79738</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7039,16 +7254,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2081</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7058,10 +7278,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477435</v>
+        <v>477462</v>
       </c>
       <c r="R63" t="n">
-        <v>6951645</v>
+        <v>6951484</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7120,10 +7340,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154190</v>
+        <v>122154203</v>
       </c>
       <c r="B64" t="n">
-        <v>98115</v>
+        <v>90826</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7132,20 +7352,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220093</v>
+        <v>1202</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7155,10 +7380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477407</v>
+        <v>477381</v>
       </c>
       <c r="R64" t="n">
-        <v>6951732</v>
+        <v>6951610</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7217,10 +7442,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178235</v>
+        <v>122178227</v>
       </c>
       <c r="B65" t="n">
-        <v>79241</v>
+        <v>79737</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7233,16 +7458,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6458</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7252,10 +7482,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477573</v>
+        <v>477598</v>
       </c>
       <c r="R65" t="n">
-        <v>6951539</v>
+        <v>6951610</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7314,10 +7544,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178228</v>
+        <v>122178223</v>
       </c>
       <c r="B66" t="n">
-        <v>79733</v>
+        <v>94058</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7326,20 +7556,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2412</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Källmossa</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7349,10 +7584,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477590</v>
+        <v>477540</v>
       </c>
       <c r="R66" t="n">
-        <v>6951600</v>
+        <v>6951613</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7411,10 +7646,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178221</v>
+        <v>122178222</v>
       </c>
       <c r="B67" t="n">
-        <v>79733</v>
+        <v>97178</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7423,20 +7658,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>221945</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477543</v>
+        <v>477540</v>
       </c>
       <c r="R67" t="n">
-        <v>6951588</v>
+        <v>6951594</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7508,10 +7748,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178246</v>
+        <v>122178243</v>
       </c>
       <c r="B68" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7526,6 +7766,11 @@
       <c r="E68" t="n">
         <v>6458</v>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -7543,10 +7788,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477535</v>
+        <v>477538</v>
       </c>
       <c r="R68" t="n">
-        <v>6951442</v>
+        <v>6951448</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7605,10 +7850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178247</v>
+        <v>122178245</v>
       </c>
       <c r="B69" t="n">
-        <v>79733</v>
+        <v>74757</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7621,16 +7866,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6440</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7640,10 +7890,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477540</v>
+        <v>477542</v>
       </c>
       <c r="R69" t="n">
-        <v>6951433</v>
+        <v>6951443</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7702,10 +7952,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178223</v>
+        <v>122178247</v>
       </c>
       <c r="B70" t="n">
-        <v>94045</v>
+        <v>79737</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7714,20 +7964,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2412</v>
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7740,7 +7995,7 @@
         <v>477540</v>
       </c>
       <c r="R70" t="n">
-        <v>6951613</v>
+        <v>6951433</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7799,10 +8054,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178236</v>
+        <v>122178220</v>
       </c>
       <c r="B71" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7815,16 +8070,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7834,10 +8094,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477559</v>
+        <v>477556</v>
       </c>
       <c r="R71" t="n">
-        <v>6951532</v>
+        <v>6951549</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7896,10 +8156,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178229</v>
+        <v>122178231</v>
       </c>
       <c r="B72" t="n">
-        <v>79769</v>
+        <v>79737</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7908,20 +8168,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7931,10 +8196,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477587</v>
+        <v>477585</v>
       </c>
       <c r="R72" t="n">
-        <v>6951569</v>
+        <v>6951573</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7993,10 +8258,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178237</v>
+        <v>122172654</v>
       </c>
       <c r="B73" t="n">
-        <v>79733</v>
+        <v>97178</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8005,20 +8270,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>221945</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8028,10 +8298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477518</v>
+        <v>477639</v>
       </c>
       <c r="R73" t="n">
-        <v>6951490</v>
+        <v>6951706</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8058,12 +8328,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8078,22 +8348,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122172640</v>
+        <v>122172653</v>
       </c>
       <c r="B74" t="n">
-        <v>79733</v>
+        <v>90844</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8106,16 +8376,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8125,10 +8400,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477949</v>
+        <v>477642</v>
       </c>
       <c r="R74" t="n">
-        <v>6951706</v>
+        <v>6951702</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8187,10 +8462,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178242</v>
+        <v>122178237</v>
       </c>
       <c r="B75" t="n">
-        <v>74753</v>
+        <v>79737</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8203,16 +8478,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6458</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8222,10 +8502,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477534</v>
+        <v>477518</v>
       </c>
       <c r="R75" t="n">
-        <v>6951448</v>
+        <v>6951490</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8284,10 +8564,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122178245</v>
+        <v>122178225</v>
       </c>
       <c r="B76" t="n">
-        <v>74753</v>
+        <v>97178</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8296,20 +8576,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6440</v>
+        <v>221945</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8319,10 +8604,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477542</v>
+        <v>477580</v>
       </c>
       <c r="R76" t="n">
-        <v>6951443</v>
+        <v>6951617</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8381,10 +8666,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122172654</v>
+        <v>122172640</v>
       </c>
       <c r="B77" t="n">
-        <v>97165</v>
+        <v>79737</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8393,20 +8678,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>6458</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8416,7 +8706,7 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477639</v>
+        <v>477949</v>
       </c>
       <c r="R77" t="n">
         <v>6951706</v>
@@ -8478,10 +8768,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122178227</v>
+        <v>122178242</v>
       </c>
       <c r="B78" t="n">
-        <v>79733</v>
+        <v>74757</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8494,16 +8784,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6440</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8513,10 +8808,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477598</v>
+        <v>477534</v>
       </c>
       <c r="R78" t="n">
-        <v>6951610</v>
+        <v>6951448</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8575,10 +8870,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122178231</v>
+        <v>122178234</v>
       </c>
       <c r="B79" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8593,6 +8888,11 @@
       <c r="E79" t="n">
         <v>6458</v>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -8610,10 +8910,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477585</v>
+        <v>477584</v>
       </c>
       <c r="R79" t="n">
-        <v>6951573</v>
+        <v>6951542</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8672,10 +8972,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122178226</v>
+        <v>122178221</v>
       </c>
       <c r="B80" t="n">
-        <v>74745</v>
+        <v>79737</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8688,16 +8988,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>308</v>
+        <v>6458</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8707,10 +9012,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477581</v>
+        <v>477543</v>
       </c>
       <c r="R80" t="n">
-        <v>6951614</v>
+        <v>6951588</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8769,10 +9074,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122178234</v>
+        <v>122172652</v>
       </c>
       <c r="B81" t="n">
-        <v>79733</v>
+        <v>98128</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8781,20 +9086,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220093</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8804,10 +9114,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477584</v>
+        <v>477755</v>
       </c>
       <c r="R81" t="n">
-        <v>6951542</v>
+        <v>6951671</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8834,12 +9144,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8854,22 +9164,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122178220</v>
+        <v>122178246</v>
       </c>
       <c r="B82" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8884,6 +9194,11 @@
       <c r="E82" t="n">
         <v>6458</v>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -8901,10 +9216,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477556</v>
+        <v>477535</v>
       </c>
       <c r="R82" t="n">
-        <v>6951549</v>
+        <v>6951442</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8963,10 +9278,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122178225</v>
+        <v>122178235</v>
       </c>
       <c r="B83" t="n">
-        <v>97165</v>
+        <v>79245</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8975,20 +9290,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>229821</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8998,10 +9318,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477580</v>
+        <v>477573</v>
       </c>
       <c r="R83" t="n">
-        <v>6951617</v>
+        <v>6951539</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9060,10 +9380,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122178222</v>
+        <v>122178236</v>
       </c>
       <c r="B84" t="n">
-        <v>97165</v>
+        <v>78656</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9072,20 +9392,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9095,10 +9420,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477540</v>
+        <v>477559</v>
       </c>
       <c r="R84" t="n">
-        <v>6951594</v>
+        <v>6951532</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9157,10 +9482,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122172652</v>
+        <v>122178232</v>
       </c>
       <c r="B85" t="n">
-        <v>98115</v>
+        <v>79737</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9169,20 +9494,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220093</v>
+        <v>6458</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9192,10 +9522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477755</v>
+        <v>477570</v>
       </c>
       <c r="R85" t="n">
-        <v>6951671</v>
+        <v>6951563</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9222,12 +9552,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9242,22 +9572,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178243</v>
+        <v>122178226</v>
       </c>
       <c r="B86" t="n">
-        <v>79733</v>
+        <v>74749</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9270,16 +9600,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>308</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9289,10 +9624,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477538</v>
+        <v>477581</v>
       </c>
       <c r="R86" t="n">
-        <v>6951448</v>
+        <v>6951614</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9351,10 +9686,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178244</v>
+        <v>122178238</v>
       </c>
       <c r="B87" t="n">
-        <v>79643</v>
+        <v>94250</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9363,20 +9698,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2080</v>
+        <v>2387</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9389,7 +9729,7 @@
         <v>477538</v>
       </c>
       <c r="R87" t="n">
-        <v>6951440</v>
+        <v>6951456</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9448,10 +9788,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178238</v>
+        <v>122178244</v>
       </c>
       <c r="B88" t="n">
-        <v>94237</v>
+        <v>79647</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9460,20 +9800,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2387</v>
+        <v>2080</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Skorpgelélav</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9486,7 +9831,7 @@
         <v>477538</v>
       </c>
       <c r="R88" t="n">
-        <v>6951456</v>
+        <v>6951440</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9545,10 +9890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122172653</v>
+        <v>122178224</v>
       </c>
       <c r="B89" t="n">
-        <v>90831</v>
+        <v>94250</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9557,20 +9902,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>2387</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9580,10 +9930,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477642</v>
+        <v>477572</v>
       </c>
       <c r="R89" t="n">
-        <v>6951702</v>
+        <v>6951626</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9610,12 +9960,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9630,22 +9980,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122178232</v>
+        <v>122178228</v>
       </c>
       <c r="B90" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9660,6 +10010,11 @@
       <c r="E90" t="n">
         <v>6458</v>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -9677,10 +10032,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477570</v>
+        <v>477590</v>
       </c>
       <c r="R90" t="n">
-        <v>6951563</v>
+        <v>6951600</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9739,10 +10094,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122178224</v>
+        <v>122178229</v>
       </c>
       <c r="B91" t="n">
-        <v>94237</v>
+        <v>79773</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9755,16 +10110,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2387</v>
+        <v>6464</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9774,10 +10134,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>477572</v>
+        <v>477587</v>
       </c>
       <c r="R91" t="n">
-        <v>6951626</v>
+        <v>6951569</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -2742,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154225</v>
+        <v>122154220</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
+        <v>79766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,25 +2754,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477572</v>
+        <v>477476</v>
       </c>
       <c r="R19" t="n">
-        <v>6951618</v>
+        <v>6951463</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122154200</v>
+        <v>122154172</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2856,25 +2856,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477435</v>
+        <v>477879</v>
       </c>
       <c r="R20" t="n">
-        <v>6951645</v>
+        <v>6951648</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2946,10 +2946,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122154197</v>
+        <v>122154190</v>
       </c>
       <c r="B21" t="n">
-        <v>79766</v>
+        <v>98141</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2962,21 +2962,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>220093</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477617</v>
+        <v>477407</v>
       </c>
       <c r="R21" t="n">
-        <v>6951666</v>
+        <v>6951732</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122154219</v>
+        <v>122154177</v>
       </c>
       <c r="B22" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477495</v>
+        <v>477767</v>
       </c>
       <c r="R22" t="n">
-        <v>6951463</v>
+        <v>6951662</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122154169</v>
+        <v>122154207</v>
       </c>
       <c r="B23" t="n">
-        <v>56585</v>
+        <v>74748</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3162,42 +3162,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>492</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477886</v>
+        <v>477445</v>
       </c>
       <c r="R23" t="n">
-        <v>6951641</v>
+        <v>6951570</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3256,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122154206</v>
+        <v>122154221</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3272,21 +3268,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3296,10 +3292,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477411</v>
+        <v>477477</v>
       </c>
       <c r="R24" t="n">
-        <v>6951546</v>
+        <v>6951466</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122154190</v>
+        <v>122154202</v>
       </c>
       <c r="B25" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3398,10 +3394,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477407</v>
+        <v>477389</v>
       </c>
       <c r="R25" t="n">
-        <v>6951732</v>
+        <v>6951610</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3460,10 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154216</v>
+        <v>122154219</v>
       </c>
       <c r="B26" t="n">
-        <v>74757</v>
+        <v>79737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,21 +3472,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3500,10 +3496,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477457</v>
+        <v>477495</v>
       </c>
       <c r="R26" t="n">
-        <v>6951419</v>
+        <v>6951463</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3562,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154211</v>
+        <v>122154197</v>
       </c>
       <c r="B27" t="n">
-        <v>90770</v>
+        <v>79766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3574,25 +3570,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477448</v>
+        <v>477617</v>
       </c>
       <c r="R27" t="n">
-        <v>6951476</v>
+        <v>6951666</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3664,10 +3660,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154173</v>
+        <v>122154209</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>79766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3676,25 +3672,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477825</v>
+        <v>477462</v>
       </c>
       <c r="R28" t="n">
-        <v>6951660</v>
+        <v>6951485</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3766,10 +3762,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154221</v>
+        <v>122154224</v>
       </c>
       <c r="B29" t="n">
-        <v>79738</v>
+        <v>56596</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3778,25 +3774,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3806,10 +3802,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477477</v>
+        <v>477538</v>
       </c>
       <c r="R29" t="n">
-        <v>6951466</v>
+        <v>6951618</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3868,10 +3864,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154214</v>
+        <v>122154203</v>
       </c>
       <c r="B30" t="n">
-        <v>79737</v>
+        <v>90839</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3884,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3908,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477421</v>
+        <v>477381</v>
       </c>
       <c r="R30" t="n">
-        <v>6951454</v>
+        <v>6951610</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3970,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154187</v>
+        <v>122154211</v>
       </c>
       <c r="B31" t="n">
-        <v>5173</v>
+        <v>90783</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,25 +3978,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4010,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477368</v>
+        <v>477448</v>
       </c>
       <c r="R31" t="n">
-        <v>6951718</v>
+        <v>6951476</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4072,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154224</v>
+        <v>122154171</v>
       </c>
       <c r="B32" t="n">
-        <v>56596</v>
+        <v>79737</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4084,25 +4080,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102613</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4112,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477538</v>
+        <v>477875</v>
       </c>
       <c r="R32" t="n">
-        <v>6951618</v>
+        <v>6951643</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4174,10 +4170,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154201</v>
+        <v>122154188</v>
       </c>
       <c r="B33" t="n">
-        <v>74749</v>
+        <v>74757</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,21 +4186,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4214,10 +4210,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477404</v>
+        <v>477377</v>
       </c>
       <c r="R33" t="n">
-        <v>6951629</v>
+        <v>6951731</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4276,10 +4272,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122154220</v>
+        <v>122154227</v>
       </c>
       <c r="B34" t="n">
-        <v>79766</v>
+        <v>79737</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4288,25 +4284,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4316,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477476</v>
+        <v>477615</v>
       </c>
       <c r="R34" t="n">
-        <v>6951463</v>
+        <v>6951614</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4378,10 +4374,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154177</v>
+        <v>122154217</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4394,34 +4390,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477767</v>
+        <v>477473</v>
       </c>
       <c r="R35" t="n">
-        <v>6951662</v>
+        <v>6951436</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4480,10 +4480,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122154215</v>
+        <v>122154175</v>
       </c>
       <c r="B36" t="n">
-        <v>56585</v>
+        <v>90835</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4496,21 +4496,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477438</v>
+        <v>477793</v>
       </c>
       <c r="R36" t="n">
-        <v>6951412</v>
+        <v>6951655</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154191</v>
+        <v>122154161</v>
       </c>
       <c r="B37" t="n">
-        <v>98128</v>
+        <v>79738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4594,25 +4594,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4622,10 +4622,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477424</v>
+        <v>477944</v>
       </c>
       <c r="R37" t="n">
-        <v>6951736</v>
+        <v>6951693</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154189</v>
+        <v>122154205</v>
       </c>
       <c r="B38" t="n">
-        <v>74749</v>
+        <v>97191</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,25 +4696,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477405</v>
+        <v>477367</v>
       </c>
       <c r="R38" t="n">
-        <v>6951731</v>
+        <v>6951594</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4786,10 +4786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154172</v>
+        <v>122154185</v>
       </c>
       <c r="B39" t="n">
-        <v>5173</v>
+        <v>90857</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,25 +4798,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477879</v>
+        <v>477372</v>
       </c>
       <c r="R39" t="n">
-        <v>6951648</v>
+        <v>6951655</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4888,10 +4888,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122154217</v>
+        <v>122154173</v>
       </c>
       <c r="B40" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4904,38 +4904,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477473</v>
+        <v>477825</v>
       </c>
       <c r="R40" t="n">
-        <v>6951436</v>
+        <v>6951660</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4994,10 +4990,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122154171</v>
+        <v>122154218</v>
       </c>
       <c r="B41" t="n">
-        <v>79737</v>
+        <v>98141</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5006,25 +5002,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5034,10 +5030,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477875</v>
+        <v>477479</v>
       </c>
       <c r="R41" t="n">
-        <v>6951643</v>
+        <v>6951442</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5096,10 +5092,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122154205</v>
+        <v>122154160</v>
       </c>
       <c r="B42" t="n">
-        <v>97178</v>
+        <v>98154</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5112,21 +5108,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5136,10 +5132,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477367</v>
+        <v>477847</v>
       </c>
       <c r="R42" t="n">
-        <v>6951594</v>
+        <v>6951679</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5198,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154160</v>
+        <v>122154192</v>
       </c>
       <c r="B43" t="n">
-        <v>98141</v>
+        <v>79641</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5214,21 +5210,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5238,10 +5234,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477847</v>
+        <v>477446</v>
       </c>
       <c r="R43" t="n">
-        <v>6951679</v>
+        <v>6951749</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5300,10 +5296,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154185</v>
+        <v>122154201</v>
       </c>
       <c r="B44" t="n">
-        <v>90844</v>
+        <v>74749</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5316,21 +5312,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5340,10 +5336,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477372</v>
+        <v>477404</v>
       </c>
       <c r="R44" t="n">
-        <v>6951655</v>
+        <v>6951629</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5402,7 +5398,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154195</v>
+        <v>122154189</v>
       </c>
       <c r="B45" t="n">
         <v>74749</v>
@@ -5442,10 +5438,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477495</v>
+        <v>477405</v>
       </c>
       <c r="R45" t="n">
-        <v>6951727</v>
+        <v>6951731</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5504,10 +5500,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122154161</v>
+        <v>122154210</v>
       </c>
       <c r="B46" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5520,21 +5516,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5544,10 +5540,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477944</v>
+        <v>477464</v>
       </c>
       <c r="R46" t="n">
-        <v>6951693</v>
+        <v>6951483</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5606,10 +5602,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122154213</v>
+        <v>122154198</v>
       </c>
       <c r="B47" t="n">
-        <v>79766</v>
+        <v>79737</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5618,25 +5614,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5646,10 +5642,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477424</v>
+        <v>477617</v>
       </c>
       <c r="R47" t="n">
-        <v>6951452</v>
+        <v>6951666</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5810,10 +5806,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154209</v>
+        <v>122154215</v>
       </c>
       <c r="B49" t="n">
-        <v>79766</v>
+        <v>56585</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5822,25 +5818,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5850,10 +5846,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477462</v>
+        <v>477438</v>
       </c>
       <c r="R49" t="n">
-        <v>6951485</v>
+        <v>6951412</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5912,10 +5908,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154210</v>
+        <v>122154200</v>
       </c>
       <c r="B50" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5928,21 +5924,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5952,10 +5948,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477464</v>
+        <v>477435</v>
       </c>
       <c r="R50" t="n">
-        <v>6951483</v>
+        <v>6951645</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6014,10 +6010,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154207</v>
+        <v>122154212</v>
       </c>
       <c r="B51" t="n">
-        <v>74748</v>
+        <v>91230</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6026,25 +6022,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>492</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Smalskaftslav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6054,10 +6045,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477445</v>
+        <v>477420</v>
       </c>
       <c r="R51" t="n">
-        <v>6951570</v>
+        <v>6951455</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6098,6 +6089,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6116,10 +6108,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154188</v>
+        <v>122154195</v>
       </c>
       <c r="B52" t="n">
-        <v>74757</v>
+        <v>74749</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6132,21 +6124,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6156,10 +6148,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477377</v>
+        <v>477495</v>
       </c>
       <c r="R52" t="n">
-        <v>6951731</v>
+        <v>6951727</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6218,10 +6210,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154192</v>
+        <v>122154191</v>
       </c>
       <c r="B53" t="n">
-        <v>79641</v>
+        <v>98141</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6234,21 +6226,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6456</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6258,10 +6250,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477446</v>
+        <v>477424</v>
       </c>
       <c r="R53" t="n">
-        <v>6951749</v>
+        <v>6951736</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6320,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122154170</v>
+        <v>122154213</v>
       </c>
       <c r="B54" t="n">
-        <v>57494</v>
+        <v>79766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6336,38 +6328,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477882</v>
+        <v>477424</v>
       </c>
       <c r="R54" t="n">
-        <v>6951635</v>
+        <v>6951452</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6426,10 +6414,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122154212</v>
+        <v>122154216</v>
       </c>
       <c r="B55" t="n">
-        <v>91217</v>
+        <v>74757</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6442,16 +6430,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6461,10 +6454,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477420</v>
+        <v>477457</v>
       </c>
       <c r="R55" t="n">
-        <v>6951455</v>
+        <v>6951419</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6505,7 +6498,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6524,10 +6516,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122154218</v>
+        <v>122154208</v>
       </c>
       <c r="B56" t="n">
-        <v>98128</v>
+        <v>79738</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6536,25 +6528,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6564,10 +6556,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477479</v>
+        <v>477462</v>
       </c>
       <c r="R56" t="n">
-        <v>6951442</v>
+        <v>6951484</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6626,10 +6618,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122154204</v>
+        <v>122154225</v>
       </c>
       <c r="B57" t="n">
-        <v>98128</v>
+        <v>79737</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6638,25 +6630,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6666,10 +6658,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477373</v>
+        <v>477572</v>
       </c>
       <c r="R57" t="n">
-        <v>6951613</v>
+        <v>6951618</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6728,10 +6720,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122154175</v>
+        <v>122154214</v>
       </c>
       <c r="B58" t="n">
-        <v>90822</v>
+        <v>79737</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6744,21 +6736,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6768,10 +6760,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477793</v>
+        <v>477421</v>
       </c>
       <c r="R58" t="n">
-        <v>6951655</v>
+        <v>6951454</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6830,7 +6822,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122154198</v>
+        <v>122154174</v>
       </c>
       <c r="B59" t="n">
         <v>79737</v>
@@ -6870,10 +6862,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477617</v>
+        <v>477833</v>
       </c>
       <c r="R59" t="n">
-        <v>6951666</v>
+        <v>6951669</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6932,10 +6924,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122154174</v>
+        <v>122154169</v>
       </c>
       <c r="B60" t="n">
-        <v>79737</v>
+        <v>56585</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6948,34 +6940,38 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477833</v>
+        <v>477886</v>
       </c>
       <c r="R60" t="n">
-        <v>6951669</v>
+        <v>6951641</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,10 +7030,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122154227</v>
+        <v>122154187</v>
       </c>
       <c r="B61" t="n">
-        <v>79737</v>
+        <v>5173</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7046,25 +7042,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7074,10 +7070,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477615</v>
+        <v>477368</v>
       </c>
       <c r="R61" t="n">
-        <v>6951614</v>
+        <v>6951718</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7136,10 +7132,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122154202</v>
+        <v>122154204</v>
       </c>
       <c r="B62" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7176,10 +7172,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477389</v>
+        <v>477373</v>
       </c>
       <c r="R62" t="n">
-        <v>6951610</v>
+        <v>6951613</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7238,10 +7234,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122154208</v>
+        <v>122154206</v>
       </c>
       <c r="B63" t="n">
-        <v>79738</v>
+        <v>78656</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7254,21 +7250,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7278,10 +7274,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477462</v>
+        <v>477411</v>
       </c>
       <c r="R63" t="n">
-        <v>6951484</v>
+        <v>6951546</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7340,10 +7336,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122154203</v>
+        <v>122154170</v>
       </c>
       <c r="B64" t="n">
-        <v>90826</v>
+        <v>57494</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7352,38 +7348,42 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477381</v>
+        <v>477882</v>
       </c>
       <c r="R64" t="n">
-        <v>6951610</v>
+        <v>6951635</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178227</v>
+        <v>122178221</v>
       </c>
       <c r="B65" t="n">
         <v>79737</v>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477598</v>
+        <v>477543</v>
       </c>
       <c r="R65" t="n">
-        <v>6951610</v>
+        <v>6951588</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7547,7 +7547,7 @@
         <v>122178223</v>
       </c>
       <c r="B66" t="n">
-        <v>94058</v>
+        <v>94071</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178222</v>
+        <v>122178225</v>
       </c>
       <c r="B67" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477540</v>
+        <v>477580</v>
       </c>
       <c r="R67" t="n">
-        <v>6951594</v>
+        <v>6951617</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7748,7 +7748,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178243</v>
+        <v>122178231</v>
       </c>
       <c r="B68" t="n">
         <v>79737</v>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477538</v>
+        <v>477585</v>
       </c>
       <c r="R68" t="n">
-        <v>6951448</v>
+        <v>6951573</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178245</v>
+        <v>122178244</v>
       </c>
       <c r="B69" t="n">
-        <v>74757</v>
+        <v>79647</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>2080</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477542</v>
+        <v>477538</v>
       </c>
       <c r="R69" t="n">
-        <v>6951443</v>
+        <v>6951440</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178247</v>
+        <v>122178229</v>
       </c>
       <c r="B70" t="n">
-        <v>79737</v>
+        <v>79773</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7964,25 +7964,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477540</v>
+        <v>477587</v>
       </c>
       <c r="R70" t="n">
-        <v>6951433</v>
+        <v>6951569</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178220</v>
+        <v>122178238</v>
       </c>
       <c r="B71" t="n">
-        <v>79737</v>
+        <v>94263</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8066,25 +8066,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>2387</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477556</v>
+        <v>477538</v>
       </c>
       <c r="R71" t="n">
-        <v>6951549</v>
+        <v>6951456</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8156,7 +8156,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178231</v>
+        <v>122178247</v>
       </c>
       <c r="B72" t="n">
         <v>79737</v>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477585</v>
+        <v>477540</v>
       </c>
       <c r="R72" t="n">
-        <v>6951573</v>
+        <v>6951433</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8258,10 +8258,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122172654</v>
+        <v>122178237</v>
       </c>
       <c r="B73" t="n">
-        <v>97178</v>
+        <v>79737</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8270,25 +8270,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477639</v>
+        <v>477518</v>
       </c>
       <c r="R73" t="n">
-        <v>6951706</v>
+        <v>6951490</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8348,22 +8348,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122172653</v>
+        <v>122178227</v>
       </c>
       <c r="B74" t="n">
-        <v>90844</v>
+        <v>79737</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477642</v>
+        <v>477598</v>
       </c>
       <c r="R74" t="n">
-        <v>6951702</v>
+        <v>6951610</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8430,12 +8430,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8450,22 +8450,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178237</v>
+        <v>122178242</v>
       </c>
       <c r="B75" t="n">
-        <v>79737</v>
+        <v>74757</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8478,21 +8478,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477518</v>
+        <v>477534</v>
       </c>
       <c r="R75" t="n">
-        <v>6951490</v>
+        <v>6951448</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122178225</v>
+        <v>122172652</v>
       </c>
       <c r="B76" t="n">
-        <v>97178</v>
+        <v>98141</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8580,21 +8580,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477580</v>
+        <v>477755</v>
       </c>
       <c r="R76" t="n">
-        <v>6951617</v>
+        <v>6951671</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8654,22 +8654,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122172640</v>
+        <v>122172653</v>
       </c>
       <c r="B77" t="n">
-        <v>79737</v>
+        <v>90857</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8682,21 +8682,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477949</v>
+        <v>477642</v>
       </c>
       <c r="R77" t="n">
-        <v>6951706</v>
+        <v>6951702</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8768,10 +8768,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122178242</v>
+        <v>122178222</v>
       </c>
       <c r="B78" t="n">
-        <v>74757</v>
+        <v>97191</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8780,25 +8780,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477534</v>
+        <v>477540</v>
       </c>
       <c r="R78" t="n">
-        <v>6951448</v>
+        <v>6951594</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122178234</v>
+        <v>122178246</v>
       </c>
       <c r="B79" t="n">
         <v>79737</v>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477584</v>
+        <v>477535</v>
       </c>
       <c r="R79" t="n">
-        <v>6951542</v>
+        <v>6951442</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8972,10 +8972,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122178221</v>
+        <v>122178235</v>
       </c>
       <c r="B80" t="n">
-        <v>79737</v>
+        <v>79245</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477543</v>
+        <v>477573</v>
       </c>
       <c r="R80" t="n">
-        <v>6951588</v>
+        <v>6951539</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122172652</v>
+        <v>122178243</v>
       </c>
       <c r="B81" t="n">
-        <v>98128</v>
+        <v>79737</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9086,25 +9086,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477755</v>
+        <v>477538</v>
       </c>
       <c r="R81" t="n">
-        <v>6951671</v>
+        <v>6951448</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9144,12 +9144,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9164,22 +9164,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122178246</v>
+        <v>122172654</v>
       </c>
       <c r="B82" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9188,25 +9188,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477535</v>
+        <v>477639</v>
       </c>
       <c r="R82" t="n">
-        <v>6951442</v>
+        <v>6951706</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9246,12 +9246,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9266,22 +9266,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122178235</v>
+        <v>122178234</v>
       </c>
       <c r="B83" t="n">
-        <v>79245</v>
+        <v>79737</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9294,21 +9294,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477573</v>
+        <v>477584</v>
       </c>
       <c r="R83" t="n">
-        <v>6951539</v>
+        <v>6951542</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122178236</v>
+        <v>122178232</v>
       </c>
       <c r="B84" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9396,21 +9396,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477559</v>
+        <v>477570</v>
       </c>
       <c r="R84" t="n">
-        <v>6951532</v>
+        <v>6951563</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9482,7 +9482,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122178232</v>
+        <v>122178228</v>
       </c>
       <c r="B85" t="n">
         <v>79737</v>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477570</v>
+        <v>477590</v>
       </c>
       <c r="R85" t="n">
-        <v>6951563</v>
+        <v>6951600</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9584,10 +9584,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122178226</v>
+        <v>122172640</v>
       </c>
       <c r="B86" t="n">
-        <v>74749</v>
+        <v>79737</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477581</v>
+        <v>477949</v>
       </c>
       <c r="R86" t="n">
-        <v>6951614</v>
+        <v>6951706</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9654,12 +9654,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9674,22 +9674,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178238</v>
+        <v>122178220</v>
       </c>
       <c r="B87" t="n">
-        <v>94250</v>
+        <v>79737</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9698,25 +9698,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477538</v>
+        <v>477556</v>
       </c>
       <c r="R87" t="n">
-        <v>6951456</v>
+        <v>6951549</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9788,10 +9788,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178244</v>
+        <v>122178236</v>
       </c>
       <c r="B88" t="n">
-        <v>79647</v>
+        <v>78656</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9804,21 +9804,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2080</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477538</v>
+        <v>477559</v>
       </c>
       <c r="R88" t="n">
-        <v>6951440</v>
+        <v>6951532</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9893,7 +9893,7 @@
         <v>122178224</v>
       </c>
       <c r="B89" t="n">
-        <v>94250</v>
+        <v>94263</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122178228</v>
+        <v>122178226</v>
       </c>
       <c r="B90" t="n">
-        <v>79737</v>
+        <v>74749</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10008,21 +10008,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477590</v>
+        <v>477581</v>
       </c>
       <c r="R90" t="n">
-        <v>6951600</v>
+        <v>6951614</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10094,10 +10094,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122178229</v>
+        <v>122178245</v>
       </c>
       <c r="B91" t="n">
-        <v>79773</v>
+        <v>74757</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10106,25 +10106,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>477587</v>
+        <v>477542</v>
       </c>
       <c r="R91" t="n">
-        <v>6951569</v>
+        <v>6951443</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -3966,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154211</v>
+        <v>122154171</v>
       </c>
       <c r="B31" t="n">
-        <v>90783</v>
+        <v>79737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477448</v>
+        <v>477875</v>
       </c>
       <c r="R31" t="n">
-        <v>6951476</v>
+        <v>6951643</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122154171</v>
+        <v>122154188</v>
       </c>
       <c r="B32" t="n">
-        <v>79737</v>
+        <v>74757</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477875</v>
+        <v>477377</v>
       </c>
       <c r="R32" t="n">
-        <v>6951643</v>
+        <v>6951731</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122154188</v>
+        <v>122154211</v>
       </c>
       <c r="B33" t="n">
-        <v>74757</v>
+        <v>90783</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4186,21 +4186,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477377</v>
+        <v>477448</v>
       </c>
       <c r="R33" t="n">
-        <v>6951731</v>
+        <v>6951476</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122154217</v>
+        <v>122154161</v>
       </c>
       <c r="B35" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4390,38 +4390,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477473</v>
+        <v>477944</v>
       </c>
       <c r="R35" t="n">
-        <v>6951436</v>
+        <v>6951693</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4582,10 +4578,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122154161</v>
+        <v>122154217</v>
       </c>
       <c r="B37" t="n">
-        <v>79738</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4598,34 +4594,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477944</v>
+        <v>477473</v>
       </c>
       <c r="R37" t="n">
-        <v>6951693</v>
+        <v>6951436</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4684,10 +4684,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154205</v>
+        <v>122154185</v>
       </c>
       <c r="B38" t="n">
-        <v>97191</v>
+        <v>90857</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,25 +4696,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477367</v>
+        <v>477372</v>
       </c>
       <c r="R38" t="n">
-        <v>6951594</v>
+        <v>6951655</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4786,10 +4786,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154185</v>
+        <v>122154205</v>
       </c>
       <c r="B39" t="n">
-        <v>90857</v>
+        <v>97191</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,25 +4798,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477372</v>
+        <v>477367</v>
       </c>
       <c r="R39" t="n">
-        <v>6951655</v>
+        <v>6951594</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5194,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122154192</v>
+        <v>122154201</v>
       </c>
       <c r="B43" t="n">
-        <v>79641</v>
+        <v>74749</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5206,25 +5206,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477446</v>
+        <v>477404</v>
       </c>
       <c r="R43" t="n">
-        <v>6951749</v>
+        <v>6951629</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154201</v>
+        <v>122154189</v>
       </c>
       <c r="B44" t="n">
         <v>74749</v>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477404</v>
+        <v>477405</v>
       </c>
       <c r="R44" t="n">
-        <v>6951629</v>
+        <v>6951731</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122154189</v>
+        <v>122154192</v>
       </c>
       <c r="B45" t="n">
-        <v>74749</v>
+        <v>79641</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5410,25 +5410,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477405</v>
+        <v>477446</v>
       </c>
       <c r="R45" t="n">
-        <v>6951731</v>
+        <v>6951749</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154195</v>
+        <v>122154191</v>
       </c>
       <c r="B52" t="n">
-        <v>74749</v>
+        <v>98141</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6120,25 +6120,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>308</v>
+        <v>220093</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477495</v>
+        <v>477424</v>
       </c>
       <c r="R52" t="n">
-        <v>6951727</v>
+        <v>6951736</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6210,10 +6210,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154191</v>
+        <v>122154195</v>
       </c>
       <c r="B53" t="n">
-        <v>98141</v>
+        <v>74749</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,25 +6222,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220093</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477424</v>
+        <v>477495</v>
       </c>
       <c r="R53" t="n">
-        <v>6951736</v>
+        <v>6951727</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -7442,7 +7442,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178221</v>
+        <v>122178234</v>
       </c>
       <c r="B65" t="n">
         <v>79737</v>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477543</v>
+        <v>477584</v>
       </c>
       <c r="R65" t="n">
-        <v>6951588</v>
+        <v>6951542</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7544,10 +7544,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178223</v>
+        <v>122178242</v>
       </c>
       <c r="B66" t="n">
-        <v>94071</v>
+        <v>74757</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7556,25 +7556,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2412</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477540</v>
+        <v>477534</v>
       </c>
       <c r="R66" t="n">
-        <v>6951613</v>
+        <v>6951448</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7646,10 +7646,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178225</v>
+        <v>122178243</v>
       </c>
       <c r="B67" t="n">
-        <v>97191</v>
+        <v>79737</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7658,25 +7658,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477580</v>
+        <v>477538</v>
       </c>
       <c r="R67" t="n">
-        <v>6951617</v>
+        <v>6951448</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178231</v>
+        <v>122178222</v>
       </c>
       <c r="B68" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7760,25 +7760,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477585</v>
+        <v>477540</v>
       </c>
       <c r="R68" t="n">
-        <v>6951573</v>
+        <v>6951594</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122178244</v>
+        <v>122178247</v>
       </c>
       <c r="B69" t="n">
-        <v>79647</v>
+        <v>79737</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2080</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477538</v>
+        <v>477540</v>
       </c>
       <c r="R69" t="n">
-        <v>6951440</v>
+        <v>6951433</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7952,10 +7952,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122178229</v>
+        <v>122178246</v>
       </c>
       <c r="B70" t="n">
-        <v>79773</v>
+        <v>79737</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7964,25 +7964,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477587</v>
+        <v>477535</v>
       </c>
       <c r="R70" t="n">
-        <v>6951569</v>
+        <v>6951442</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122178238</v>
+        <v>122178235</v>
       </c>
       <c r="B71" t="n">
-        <v>94263</v>
+        <v>79245</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8066,25 +8066,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2387</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477538</v>
+        <v>477573</v>
       </c>
       <c r="R71" t="n">
-        <v>6951456</v>
+        <v>6951539</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122178247</v>
+        <v>122172653</v>
       </c>
       <c r="B72" t="n">
-        <v>79737</v>
+        <v>90857</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8172,21 +8172,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477540</v>
+        <v>477642</v>
       </c>
       <c r="R72" t="n">
-        <v>6951433</v>
+        <v>6951702</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8246,22 +8246,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122178237</v>
+        <v>122178229</v>
       </c>
       <c r="B73" t="n">
-        <v>79737</v>
+        <v>79773</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8270,25 +8270,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477518</v>
+        <v>477587</v>
       </c>
       <c r="R73" t="n">
-        <v>6951490</v>
+        <v>6951569</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122178227</v>
+        <v>122172652</v>
       </c>
       <c r="B74" t="n">
-        <v>79737</v>
+        <v>98141</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8372,25 +8372,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477598</v>
+        <v>477755</v>
       </c>
       <c r="R74" t="n">
-        <v>6951610</v>
+        <v>6951671</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8430,12 +8430,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8450,22 +8450,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122178242</v>
+        <v>122172640</v>
       </c>
       <c r="B75" t="n">
-        <v>74757</v>
+        <v>79737</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8478,21 +8478,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477534</v>
+        <v>477949</v>
       </c>
       <c r="R75" t="n">
-        <v>6951448</v>
+        <v>6951706</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8552,22 +8552,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122172652</v>
+        <v>122178228</v>
       </c>
       <c r="B76" t="n">
-        <v>98141</v>
+        <v>79737</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8576,25 +8576,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477755</v>
+        <v>477590</v>
       </c>
       <c r="R76" t="n">
-        <v>6951671</v>
+        <v>6951600</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8654,22 +8654,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122172653</v>
+        <v>122178221</v>
       </c>
       <c r="B77" t="n">
-        <v>90857</v>
+        <v>79737</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8682,21 +8682,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477642</v>
+        <v>477543</v>
       </c>
       <c r="R77" t="n">
-        <v>6951702</v>
+        <v>6951588</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8736,12 +8736,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8756,22 +8756,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122178222</v>
+        <v>122178232</v>
       </c>
       <c r="B78" t="n">
-        <v>97191</v>
+        <v>79737</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8780,25 +8780,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477540</v>
+        <v>477570</v>
       </c>
       <c r="R78" t="n">
-        <v>6951594</v>
+        <v>6951563</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122178246</v>
+        <v>122178225</v>
       </c>
       <c r="B79" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8882,25 +8882,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477535</v>
+        <v>477580</v>
       </c>
       <c r="R79" t="n">
-        <v>6951442</v>
+        <v>6951617</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8972,10 +8972,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122178235</v>
+        <v>122178236</v>
       </c>
       <c r="B80" t="n">
-        <v>79245</v>
+        <v>78656</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477573</v>
+        <v>477559</v>
       </c>
       <c r="R80" t="n">
-        <v>6951539</v>
+        <v>6951532</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9074,7 +9074,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122178243</v>
+        <v>122178237</v>
       </c>
       <c r="B81" t="n">
         <v>79737</v>
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477538</v>
+        <v>477518</v>
       </c>
       <c r="R81" t="n">
-        <v>6951448</v>
+        <v>6951490</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9176,10 +9176,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122172654</v>
+        <v>122178231</v>
       </c>
       <c r="B82" t="n">
-        <v>97191</v>
+        <v>79737</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9188,25 +9188,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477639</v>
+        <v>477585</v>
       </c>
       <c r="R82" t="n">
-        <v>6951706</v>
+        <v>6951573</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9246,12 +9246,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9266,22 +9266,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122178234</v>
+        <v>122178244</v>
       </c>
       <c r="B83" t="n">
-        <v>79737</v>
+        <v>79647</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9294,21 +9294,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>2080</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477584</v>
+        <v>477538</v>
       </c>
       <c r="R83" t="n">
-        <v>6951542</v>
+        <v>6951440</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122178232</v>
+        <v>122178223</v>
       </c>
       <c r="B84" t="n">
-        <v>79737</v>
+        <v>94071</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9392,25 +9392,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>2412</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477570</v>
+        <v>477540</v>
       </c>
       <c r="R84" t="n">
-        <v>6951563</v>
+        <v>6951613</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122178228</v>
+        <v>122172654</v>
       </c>
       <c r="B85" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9494,25 +9494,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477590</v>
+        <v>477639</v>
       </c>
       <c r="R85" t="n">
-        <v>6951600</v>
+        <v>6951706</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9552,12 +9552,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9572,22 +9572,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122172640</v>
+        <v>122178226</v>
       </c>
       <c r="B86" t="n">
-        <v>79737</v>
+        <v>74749</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9600,21 +9600,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477949</v>
+        <v>477581</v>
       </c>
       <c r="R86" t="n">
-        <v>6951706</v>
+        <v>6951614</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9654,12 +9654,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9674,22 +9674,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122178220</v>
+        <v>122178245</v>
       </c>
       <c r="B87" t="n">
-        <v>79737</v>
+        <v>74757</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9702,21 +9702,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477556</v>
+        <v>477542</v>
       </c>
       <c r="R87" t="n">
-        <v>6951549</v>
+        <v>6951443</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9788,10 +9788,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122178236</v>
+        <v>122178224</v>
       </c>
       <c r="B88" t="n">
-        <v>78656</v>
+        <v>94263</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9800,25 +9800,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477559</v>
+        <v>477572</v>
       </c>
       <c r="R88" t="n">
-        <v>6951532</v>
+        <v>6951626</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9890,7 +9890,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122178224</v>
+        <v>122178238</v>
       </c>
       <c r="B89" t="n">
         <v>94263</v>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477572</v>
+        <v>477538</v>
       </c>
       <c r="R89" t="n">
-        <v>6951626</v>
+        <v>6951456</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122178226</v>
+        <v>122178227</v>
       </c>
       <c r="B90" t="n">
-        <v>74749</v>
+        <v>79737</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10008,21 +10008,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477581</v>
+        <v>477598</v>
       </c>
       <c r="R90" t="n">
-        <v>6951614</v>
+        <v>6951610</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10094,10 +10094,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122178245</v>
+        <v>122178220</v>
       </c>
       <c r="B91" t="n">
-        <v>74757</v>
+        <v>79737</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10110,21 +10110,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>477542</v>
+        <v>477556</v>
       </c>
       <c r="R91" t="n">
-        <v>6951443</v>
+        <v>6951549</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10194,6 +10194,2626 @@
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125671901</v>
+      </c>
+      <c r="B92" t="n">
+        <v>80064</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>477440</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6951449</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>125657638</v>
+      </c>
+      <c r="B93" t="n">
+        <v>56828</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>477427</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6951523</v>
+      </c>
+      <c r="S93" t="n">
+        <v>50</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>125670788</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>477403</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6951670</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>125657704</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91737</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>760</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>477483</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6951493</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>125657633</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>477455</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6951481</v>
+      </c>
+      <c r="S96" t="n">
+        <v>50</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>125657637</v>
+      </c>
+      <c r="B97" t="n">
+        <v>56828</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>477459</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6951572</v>
+      </c>
+      <c r="S97" t="n">
+        <v>50</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>125671881</v>
+      </c>
+      <c r="B98" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>477440</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6951449</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>125663252</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>477408</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6951545</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>125657630</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>477442</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6951549</v>
+      </c>
+      <c r="S100" t="n">
+        <v>50</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>125657636</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57738</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>477560</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6951544</v>
+      </c>
+      <c r="S101" t="n">
+        <v>50</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>125670523</v>
+      </c>
+      <c r="B102" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>477385</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6951687</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>125657635</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57480</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>477530</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6951481</v>
+      </c>
+      <c r="S103" t="n">
+        <v>50</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>125670934</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91184</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>477391</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6951629</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>125657705</v>
+      </c>
+      <c r="B105" t="n">
+        <v>88512</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>510</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>477545</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6951453</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>125666595</v>
+      </c>
+      <c r="B106" t="n">
+        <v>91184</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>477423</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6951648</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>125666274</v>
+      </c>
+      <c r="B107" t="n">
+        <v>75025</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>477409</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6951634</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>125663151</v>
+      </c>
+      <c r="B108" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>477420</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6951546</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>125657631</v>
+      </c>
+      <c r="B109" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>477569</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6951502</v>
+      </c>
+      <c r="S109" t="n">
+        <v>50</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>125666433</v>
+      </c>
+      <c r="B110" t="n">
+        <v>82737</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>477416</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6951641</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>125669436</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>477482</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6951702</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>125671631</v>
+      </c>
+      <c r="B112" t="n">
+        <v>80029</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>477425</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6951524</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>125668481</v>
+      </c>
+      <c r="B113" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>477500</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6951693</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>125657634</v>
+      </c>
+      <c r="B114" t="n">
+        <v>57480</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>477644</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6951563</v>
+      </c>
+      <c r="S114" t="n">
+        <v>50</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12357,10 +12357,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125669436</v>
+        <v>125671631</v>
       </c>
       <c r="B111" t="n">
-        <v>57635</v>
+        <v>80029</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12373,39 +12373,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>477482</v>
+        <v>477425</v>
       </c>
       <c r="R111" t="n">
-        <v>6951702</v>
+        <v>6951524</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12437,7 +12432,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12447,7 +12442,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12474,10 +12469,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125671631</v>
+        <v>125669436</v>
       </c>
       <c r="B112" t="n">
-        <v>80029</v>
+        <v>57635</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12490,34 +12485,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>477425</v>
+        <v>477482</v>
       </c>
       <c r="R112" t="n">
-        <v>6951524</v>
+        <v>6951702</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12549,7 +12549,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD112" t="b">

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -11727,10 +11727,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125671881</v>
+        <v>125670788</v>
       </c>
       <c r="B106" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11738,34 +11738,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>477440</v>
+        <v>477403</v>
       </c>
       <c r="R106" t="n">
-        <v>6951449</v>
+        <v>6951670</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11797,7 +11802,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11807,7 +11812,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11834,10 +11839,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125670788</v>
+        <v>125671881</v>
       </c>
       <c r="B107" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11845,39 +11850,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477403</v>
+        <v>477440</v>
       </c>
       <c r="R107" t="n">
-        <v>6951670</v>
+        <v>6951449</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -10306,7 +10306,7 @@
         <v>125670523</v>
       </c>
       <c r="B93" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125657634</v>
+        <v>125657636</v>
       </c>
       <c r="B94" t="n">
-        <v>57493</v>
+        <v>57755</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10421,16 +10421,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>102621</v>
+        <v>103031</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10438,16 +10438,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10461,10 +10457,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>477644</v>
+        <v>477560</v>
       </c>
       <c r="R94" t="n">
-        <v>6951563</v>
+        <v>6951544</v>
       </c>
       <c r="S94" t="n">
         <v>50</v>
@@ -10491,12 +10487,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10523,10 +10519,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125657630</v>
+        <v>125657705</v>
       </c>
       <c r="B95" t="n">
-        <v>57651</v>
+        <v>88633</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10534,53 +10530,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>477442</v>
+        <v>477545</v>
       </c>
       <c r="R95" t="n">
-        <v>6951549</v>
+        <v>6951453</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10604,12 +10584,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10629,34 +10609,34 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125657636</v>
+        <v>125657638</v>
       </c>
       <c r="B96" t="n">
-        <v>57755</v>
+        <v>56834</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10664,12 +10644,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -10683,10 +10667,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>477560</v>
+        <v>477427</v>
       </c>
       <c r="R96" t="n">
-        <v>6951544</v>
+        <v>6951523</v>
       </c>
       <c r="S96" t="n">
         <v>50</v>
@@ -10745,10 +10729,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125657638</v>
+        <v>125663151</v>
       </c>
       <c r="B97" t="n">
-        <v>56834</v>
+        <v>57651</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10756,16 +10740,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10773,36 +10757,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>477427</v>
+        <v>477420</v>
       </c>
       <c r="R97" t="n">
-        <v>6951523</v>
+        <v>6951546</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10826,12 +10799,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10846,57 +10829,57 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125657705</v>
+        <v>125671901</v>
       </c>
       <c r="B98" t="n">
-        <v>88626</v>
+        <v>80106</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>477545</v>
+        <v>477440</v>
       </c>
       <c r="R98" t="n">
-        <v>6951453</v>
+        <v>6951449</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10923,12 +10906,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10943,22 +10936,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125657633</v>
+        <v>125671631</v>
       </c>
       <c r="B99" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10966,53 +10959,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>477455</v>
+        <v>477425</v>
       </c>
       <c r="R99" t="n">
-        <v>6951481</v>
+        <v>6951524</v>
       </c>
       <c r="S99" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11036,12 +11013,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11056,22 +11043,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125663151</v>
+        <v>125657637</v>
       </c>
       <c r="B100" t="n">
-        <v>57651</v>
+        <v>56834</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11079,16 +11066,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11096,25 +11083,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>477420</v>
+        <v>477459</v>
       </c>
       <c r="R100" t="n">
-        <v>6951546</v>
+        <v>6951572</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11138,22 +11136,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11168,76 +11156,60 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125657635</v>
+        <v>125670934</v>
       </c>
       <c r="B101" t="n">
-        <v>57493</v>
+        <v>91245</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>102621</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>477530</v>
+        <v>477391</v>
       </c>
       <c r="R101" t="n">
-        <v>6951481</v>
+        <v>6951629</v>
       </c>
       <c r="S101" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11261,12 +11233,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11281,44 +11263,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125671901</v>
+        <v>125671881</v>
       </c>
       <c r="B102" t="n">
-        <v>80106</v>
+        <v>80070</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11363,7 +11345,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11373,7 +11355,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11400,10 +11382,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125671631</v>
+        <v>125670788</v>
       </c>
       <c r="B103" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11411,34 +11393,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477425</v>
+        <v>477403</v>
       </c>
       <c r="R103" t="n">
-        <v>6951524</v>
+        <v>6951670</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11470,7 +11457,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11480,7 +11467,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11507,64 +11494,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125657637</v>
+        <v>125657704</v>
       </c>
       <c r="B104" t="n">
-        <v>56834</v>
+        <v>91798</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>760</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477459</v>
+        <v>477483</v>
       </c>
       <c r="R104" t="n">
-        <v>6951572</v>
+        <v>6951493</v>
       </c>
       <c r="S104" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11588,12 +11559,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11613,17 +11584,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125670934</v>
+        <v>125669436</v>
       </c>
       <c r="B105" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11631,34 +11602,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477391</v>
+        <v>477482</v>
       </c>
       <c r="R105" t="n">
-        <v>6951629</v>
+        <v>6951702</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11690,7 +11666,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11700,7 +11676,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11727,7 +11703,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125670788</v>
+        <v>125663252</v>
       </c>
       <c r="B106" t="n">
         <v>57651</v>
@@ -11767,10 +11743,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>477403</v>
+        <v>477408</v>
       </c>
       <c r="R106" t="n">
-        <v>6951670</v>
+        <v>6951545</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11802,7 +11778,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11812,7 +11788,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11839,10 +11815,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125671881</v>
+        <v>125668481</v>
       </c>
       <c r="B107" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11850,21 +11826,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11874,10 +11850,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477440</v>
+        <v>477500</v>
       </c>
       <c r="R107" t="n">
-        <v>6951449</v>
+        <v>6951693</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11909,7 +11885,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11919,7 +11895,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11946,45 +11922,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125657704</v>
+        <v>125666595</v>
       </c>
       <c r="B108" t="n">
-        <v>91791</v>
+        <v>91245</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>760</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>477483</v>
+        <v>477423</v>
       </c>
       <c r="R108" t="n">
-        <v>6951493</v>
+        <v>6951648</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12011,12 +11987,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12031,22 +12017,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125669436</v>
+        <v>125666274</v>
       </c>
       <c r="B109" t="n">
-        <v>57651</v>
+        <v>75066</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12054,39 +12040,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>477482</v>
+        <v>477409</v>
       </c>
       <c r="R109" t="n">
-        <v>6951702</v>
+        <v>6951634</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12118,7 +12099,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12128,7 +12109,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12155,10 +12136,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125663252</v>
+        <v>125757747</v>
       </c>
       <c r="B110" t="n">
-        <v>57651</v>
+        <v>75066</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12166,39 +12147,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>477408</v>
+        <v>477462</v>
       </c>
       <c r="R110" t="n">
-        <v>6951545</v>
+        <v>6951615</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12228,19 +12204,9 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>15:53</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12267,10 +12233,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125666595</v>
+        <v>125757748</v>
       </c>
       <c r="B111" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12278,34 +12244,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>477423</v>
+        <v>477491</v>
       </c>
       <c r="R111" t="n">
-        <v>6951648</v>
+        <v>6951708</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12335,19 +12306,14 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>17:41</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>17:41</t>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12374,10 +12340,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125668481</v>
+        <v>125757749</v>
       </c>
       <c r="B112" t="n">
-        <v>78967</v>
+        <v>91245</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12385,34 +12351,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>477500</v>
+        <v>477486</v>
       </c>
       <c r="R112" t="n">
-        <v>6951693</v>
+        <v>6951644</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12442,19 +12408,9 @@
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>18:50</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>18:50</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12481,7 +12437,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125657631</v>
+        <v>125657630</v>
       </c>
       <c r="B113" t="n">
         <v>57651</v>
@@ -12532,10 +12488,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477569</v>
+        <v>477442</v>
       </c>
       <c r="R113" t="n">
-        <v>6951502</v>
+        <v>6951549</v>
       </c>
       <c r="S113" t="n">
         <v>50</v>
@@ -12562,12 +12518,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12594,48 +12550,64 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125666274</v>
+        <v>125657634</v>
       </c>
       <c r="B114" t="n">
-        <v>75066</v>
+        <v>57493</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6440</v>
+        <v>102621</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477409</v>
+        <v>477644</v>
       </c>
       <c r="R114" t="n">
-        <v>6951634</v>
+        <v>6951563</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12659,22 +12631,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>17:33</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>17:33</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12689,22 +12651,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125757747</v>
+        <v>125657633</v>
       </c>
       <c r="B115" t="n">
-        <v>75066</v>
+        <v>57651</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12712,37 +12674,53 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Storstensjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477462</v>
+        <v>477455</v>
       </c>
       <c r="R115" t="n">
-        <v>6951615</v>
+        <v>6951481</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12766,12 +12744,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12786,39 +12764,39 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125757748</v>
+        <v>125657635</v>
       </c>
       <c r="B116" t="n">
-        <v>57651</v>
+        <v>57493</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12826,25 +12804,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Storstensjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477491</v>
+        <v>477530</v>
       </c>
       <c r="R116" t="n">
-        <v>6951708</v>
+        <v>6951481</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12868,17 +12857,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12893,22 +12877,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125757749</v>
+        <v>125657631</v>
       </c>
       <c r="B117" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12916,37 +12900,53 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Storstensjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>477486</v>
+        <v>477569</v>
       </c>
       <c r="R117" t="n">
-        <v>6951644</v>
+        <v>6951502</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12970,12 +12970,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12990,12 +12990,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -11275,10 +11275,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125671881</v>
+        <v>125670788</v>
       </c>
       <c r="B102" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11286,34 +11286,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477440</v>
+        <v>477403</v>
       </c>
       <c r="R102" t="n">
-        <v>6951449</v>
+        <v>6951670</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11345,7 +11350,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11355,7 +11360,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11382,10 +11387,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125670788</v>
+        <v>125671881</v>
       </c>
       <c r="B103" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11393,39 +11398,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477403</v>
+        <v>477440</v>
       </c>
       <c r="R103" t="n">
-        <v>6951670</v>
+        <v>6951449</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57651</v>
+        <v>57493</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B116" t="n">
-        <v>57493</v>
+        <v>57651</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -10199,7 +10199,7 @@
         <v>125666433</v>
       </c>
       <c r="B92" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>125670523</v>
       </c>
       <c r="B93" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>125657705</v>
       </c>
       <c r="B95" t="n">
-        <v>88633</v>
+        <v>88637</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>125671901</v>
       </c>
       <c r="B98" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>125671631</v>
       </c>
       <c r="B99" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>125670934</v>
       </c>
       <c r="B101" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11275,10 +11275,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125670788</v>
+        <v>125671881</v>
       </c>
       <c r="B102" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11286,39 +11286,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477403</v>
+        <v>477440</v>
       </c>
       <c r="R102" t="n">
-        <v>6951670</v>
+        <v>6951449</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11350,7 +11345,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11360,7 +11355,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11387,10 +11382,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125671881</v>
+        <v>125670788</v>
       </c>
       <c r="B103" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11398,34 +11393,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477440</v>
+        <v>477403</v>
       </c>
       <c r="R103" t="n">
-        <v>6951449</v>
+        <v>6951670</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11494,45 +11494,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125657704</v>
+        <v>125669436</v>
       </c>
       <c r="B104" t="n">
-        <v>91798</v>
+        <v>57651</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477483</v>
+        <v>477482</v>
       </c>
       <c r="R104" t="n">
-        <v>6951493</v>
+        <v>6951702</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11559,12 +11564,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11579,62 +11594,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125669436</v>
+        <v>125657704</v>
       </c>
       <c r="B105" t="n">
-        <v>57651</v>
+        <v>91802</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477482</v>
+        <v>477483</v>
       </c>
       <c r="R105" t="n">
-        <v>6951702</v>
+        <v>6951493</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11661,22 +11671,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11691,12 +11691,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11818,7 +11818,7 @@
         <v>125668481</v>
       </c>
       <c r="B107" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>125666595</v>
       </c>
       <c r="B108" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>125666274</v>
       </c>
       <c r="B109" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>125757747</v>
       </c>
       <c r="B110" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>125757749</v>
       </c>
       <c r="B112" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B115" t="n">
-        <v>57493</v>
+        <v>57651</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B116" t="n">
-        <v>57651</v>
+        <v>57493</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -11494,50 +11494,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125669436</v>
+        <v>125657704</v>
       </c>
       <c r="B104" t="n">
-        <v>57651</v>
+        <v>91802</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477482</v>
+        <v>477483</v>
       </c>
       <c r="R104" t="n">
-        <v>6951702</v>
+        <v>6951493</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11564,22 +11559,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11594,57 +11579,62 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125657704</v>
+        <v>125669436</v>
       </c>
       <c r="B105" t="n">
-        <v>91802</v>
+        <v>57651</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477483</v>
+        <v>477482</v>
       </c>
       <c r="R105" t="n">
-        <v>6951493</v>
+        <v>6951702</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11671,12 +11661,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11691,12 +11691,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -10199,7 +10199,7 @@
         <v>125666433</v>
       </c>
       <c r="B92" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>125670523</v>
       </c>
       <c r="B93" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>125657705</v>
       </c>
       <c r="B95" t="n">
-        <v>88637</v>
+        <v>88641</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>125671901</v>
       </c>
       <c r="B98" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>125671631</v>
       </c>
       <c r="B99" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>125670934</v>
       </c>
       <c r="B101" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>125671881</v>
       </c>
       <c r="B102" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>125657704</v>
       </c>
       <c r="B104" t="n">
-        <v>91802</v>
+        <v>91806</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>125668481</v>
       </c>
       <c r="B107" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>125666595</v>
       </c>
       <c r="B108" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>125757749</v>
       </c>
       <c r="B112" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -11815,10 +11815,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125668481</v>
+        <v>125666595</v>
       </c>
       <c r="B107" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11826,21 +11826,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11850,10 +11850,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477500</v>
+        <v>477423</v>
       </c>
       <c r="R107" t="n">
-        <v>6951693</v>
+        <v>6951648</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11922,10 +11922,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125666595</v>
+        <v>125668481</v>
       </c>
       <c r="B108" t="n">
-        <v>91250</v>
+        <v>78972</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>477423</v>
+        <v>477500</v>
       </c>
       <c r="R108" t="n">
-        <v>6951648</v>
+        <v>6951693</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57651</v>
+        <v>57493</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B116" t="n">
-        <v>57493</v>
+        <v>57651</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -11275,10 +11275,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125671881</v>
+        <v>125670788</v>
       </c>
       <c r="B102" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11286,34 +11286,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477440</v>
+        <v>477403</v>
       </c>
       <c r="R102" t="n">
-        <v>6951449</v>
+        <v>6951670</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11345,7 +11350,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11355,7 +11360,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11382,10 +11387,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125670788</v>
+        <v>125671881</v>
       </c>
       <c r="B103" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11393,39 +11398,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477403</v>
+        <v>477440</v>
       </c>
       <c r="R103" t="n">
-        <v>6951670</v>
+        <v>6951449</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B115" t="n">
-        <v>57493</v>
+        <v>57651</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B116" t="n">
-        <v>57651</v>
+        <v>57493</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -11275,10 +11275,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125670788</v>
+        <v>125671881</v>
       </c>
       <c r="B102" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11286,39 +11286,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477403</v>
+        <v>477440</v>
       </c>
       <c r="R102" t="n">
-        <v>6951670</v>
+        <v>6951449</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11350,7 +11345,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11360,7 +11355,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11387,10 +11382,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125671881</v>
+        <v>125670788</v>
       </c>
       <c r="B103" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11398,34 +11393,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477440</v>
+        <v>477403</v>
       </c>
       <c r="R103" t="n">
-        <v>6951449</v>
+        <v>6951670</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57651</v>
+        <v>57493</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B116" t="n">
-        <v>57493</v>
+        <v>57651</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -10199,7 +10199,7 @@
         <v>125666433</v>
       </c>
       <c r="B92" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>125670523</v>
       </c>
       <c r="B93" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>125657636</v>
       </c>
       <c r="B94" t="n">
-        <v>57755</v>
+        <v>57756</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10519,10 +10519,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125657705</v>
+        <v>125657638</v>
       </c>
       <c r="B95" t="n">
-        <v>88641</v>
+        <v>56835</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10530,37 +10530,53 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>477545</v>
+        <v>477427</v>
       </c>
       <c r="R95" t="n">
-        <v>6951453</v>
+        <v>6951523</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10584,12 +10600,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10609,17 +10625,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125657638</v>
+        <v>125657705</v>
       </c>
       <c r="B96" t="n">
-        <v>56834</v>
+        <v>88643</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10627,53 +10643,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>477427</v>
+        <v>477545</v>
       </c>
       <c r="R96" t="n">
-        <v>6951523</v>
+        <v>6951453</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10697,12 +10697,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10732,7 +10732,7 @@
         <v>125663151</v>
       </c>
       <c r="B97" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>125671901</v>
       </c>
       <c r="B98" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>125671631</v>
       </c>
       <c r="B99" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>125657637</v>
       </c>
       <c r="B100" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>125670934</v>
       </c>
       <c r="B101" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11275,10 +11275,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125671881</v>
+        <v>125670788</v>
       </c>
       <c r="B102" t="n">
-        <v>80075</v>
+        <v>57652</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11286,34 +11286,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477440</v>
+        <v>477403</v>
       </c>
       <c r="R102" t="n">
-        <v>6951449</v>
+        <v>6951670</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11345,7 +11350,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11355,7 +11360,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11382,10 +11387,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125670788</v>
+        <v>125671881</v>
       </c>
       <c r="B103" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11393,39 +11398,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477403</v>
+        <v>477440</v>
       </c>
       <c r="R103" t="n">
-        <v>6951670</v>
+        <v>6951449</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11497,7 +11497,7 @@
         <v>125657704</v>
       </c>
       <c r="B104" t="n">
-        <v>91806</v>
+        <v>91808</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>125669436</v>
       </c>
       <c r="B105" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>125663252</v>
       </c>
       <c r="B106" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11815,10 +11815,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125666595</v>
+        <v>125668481</v>
       </c>
       <c r="B107" t="n">
-        <v>91250</v>
+        <v>78973</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11826,21 +11826,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11850,10 +11850,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477423</v>
+        <v>477500</v>
       </c>
       <c r="R107" t="n">
-        <v>6951648</v>
+        <v>6951693</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11922,10 +11922,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125668481</v>
+        <v>125666595</v>
       </c>
       <c r="B108" t="n">
-        <v>78972</v>
+        <v>91252</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11933,21 +11933,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11957,10 +11957,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>477500</v>
+        <v>477423</v>
       </c>
       <c r="R108" t="n">
-        <v>6951693</v>
+        <v>6951648</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12032,7 +12032,7 @@
         <v>125666274</v>
       </c>
       <c r="B109" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>125757747</v>
       </c>
       <c r="B110" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>125757748</v>
       </c>
       <c r="B111" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>125757749</v>
       </c>
       <c r="B112" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>125657630</v>
       </c>
       <c r="B113" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>125657634</v>
       </c>
       <c r="B114" t="n">
-        <v>57493</v>
+        <v>57494</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B115" t="n">
-        <v>57493</v>
+        <v>57652</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B116" t="n">
-        <v>57651</v>
+        <v>57494</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>
@@ -12892,7 +12892,7 @@
         <v>125657631</v>
       </c>
       <c r="B117" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57652</v>
+        <v>57494</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B116" t="n">
-        <v>57494</v>
+        <v>57652</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -10306,7 +10306,7 @@
         <v>125670523</v>
       </c>
       <c r="B93" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10519,10 +10519,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125657638</v>
+        <v>125657705</v>
       </c>
       <c r="B95" t="n">
-        <v>56835</v>
+        <v>88645</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10530,53 +10530,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>477427</v>
+        <v>477545</v>
       </c>
       <c r="R95" t="n">
-        <v>6951523</v>
+        <v>6951453</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10600,12 +10584,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10625,17 +10609,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125657705</v>
+        <v>125657638</v>
       </c>
       <c r="B96" t="n">
-        <v>88643</v>
+        <v>56835</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10643,37 +10627,53 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>477545</v>
+        <v>477427</v>
       </c>
       <c r="R96" t="n">
-        <v>6951453</v>
+        <v>6951523</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10697,12 +10697,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11171,7 +11171,7 @@
         <v>125670934</v>
       </c>
       <c r="B101" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11275,10 +11275,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125670788</v>
+        <v>125671881</v>
       </c>
       <c r="B102" t="n">
-        <v>57652</v>
+        <v>80076</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11286,39 +11286,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477403</v>
+        <v>477440</v>
       </c>
       <c r="R102" t="n">
-        <v>6951670</v>
+        <v>6951449</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11350,7 +11345,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11360,7 +11355,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11387,10 +11382,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125671881</v>
+        <v>125670788</v>
       </c>
       <c r="B103" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11398,34 +11393,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477440</v>
+        <v>477403</v>
       </c>
       <c r="R103" t="n">
-        <v>6951449</v>
+        <v>6951670</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11494,45 +11494,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125657704</v>
+        <v>125669436</v>
       </c>
       <c r="B104" t="n">
-        <v>91808</v>
+        <v>57652</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477483</v>
+        <v>477482</v>
       </c>
       <c r="R104" t="n">
-        <v>6951493</v>
+        <v>6951702</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11559,12 +11564,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11579,62 +11594,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125669436</v>
+        <v>125657704</v>
       </c>
       <c r="B105" t="n">
-        <v>57652</v>
+        <v>91810</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477482</v>
+        <v>477483</v>
       </c>
       <c r="R105" t="n">
-        <v>6951702</v>
+        <v>6951493</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11661,22 +11671,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11691,12 +11691,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11925,7 +11925,7 @@
         <v>125666595</v>
       </c>
       <c r="B108" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>125757749</v>
       </c>
       <c r="B112" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12437,27 +12437,27 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125657630</v>
+        <v>125657634</v>
       </c>
       <c r="B113" t="n">
-        <v>57652</v>
+        <v>57494</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12488,10 +12488,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477442</v>
+        <v>477644</v>
       </c>
       <c r="R113" t="n">
-        <v>6951549</v>
+        <v>6951563</v>
       </c>
       <c r="S113" t="n">
         <v>50</v>
@@ -12518,12 +12518,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12550,27 +12550,27 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125657634</v>
+        <v>125657630</v>
       </c>
       <c r="B114" t="n">
-        <v>57494</v>
+        <v>57652</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477644</v>
+        <v>477442</v>
       </c>
       <c r="R114" t="n">
-        <v>6951563</v>
+        <v>6951549</v>
       </c>
       <c r="S114" t="n">
         <v>50</v>
@@ -12631,12 +12631,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B115" t="n">
-        <v>57494</v>
+        <v>57652</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B116" t="n">
-        <v>57652</v>
+        <v>57494</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -10306,7 +10306,7 @@
         <v>125670523</v>
       </c>
       <c r="B93" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10519,10 +10519,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125657705</v>
+        <v>125657638</v>
       </c>
       <c r="B95" t="n">
-        <v>88645</v>
+        <v>56835</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10530,37 +10530,53 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>477545</v>
+        <v>477427</v>
       </c>
       <c r="R95" t="n">
-        <v>6951453</v>
+        <v>6951523</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10584,12 +10600,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10609,17 +10625,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125657638</v>
+        <v>125657705</v>
       </c>
       <c r="B96" t="n">
-        <v>56835</v>
+        <v>88647</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10627,53 +10643,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>477427</v>
+        <v>477545</v>
       </c>
       <c r="R96" t="n">
-        <v>6951523</v>
+        <v>6951453</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10697,12 +10697,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11171,7 +11171,7 @@
         <v>125670934</v>
       </c>
       <c r="B101" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11275,10 +11275,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125671881</v>
+        <v>125670788</v>
       </c>
       <c r="B102" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11286,34 +11286,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477440</v>
+        <v>477403</v>
       </c>
       <c r="R102" t="n">
-        <v>6951449</v>
+        <v>6951670</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11345,7 +11350,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11355,7 +11360,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11382,10 +11387,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125670788</v>
+        <v>125671881</v>
       </c>
       <c r="B103" t="n">
-        <v>57652</v>
+        <v>80076</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11393,39 +11398,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477403</v>
+        <v>477440</v>
       </c>
       <c r="R103" t="n">
-        <v>6951670</v>
+        <v>6951449</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11609,7 +11609,7 @@
         <v>125657704</v>
       </c>
       <c r="B105" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>125666595</v>
       </c>
       <c r="B108" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>125757749</v>
       </c>
       <c r="B112" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12437,27 +12437,27 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125657634</v>
+        <v>125657630</v>
       </c>
       <c r="B113" t="n">
-        <v>57494</v>
+        <v>57652</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12488,10 +12488,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477644</v>
+        <v>477442</v>
       </c>
       <c r="R113" t="n">
-        <v>6951563</v>
+        <v>6951549</v>
       </c>
       <c r="S113" t="n">
         <v>50</v>
@@ -12518,12 +12518,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12550,27 +12550,27 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125657630</v>
+        <v>125657634</v>
       </c>
       <c r="B114" t="n">
-        <v>57652</v>
+        <v>57494</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477442</v>
+        <v>477644</v>
       </c>
       <c r="R114" t="n">
-        <v>6951549</v>
+        <v>6951563</v>
       </c>
       <c r="S114" t="n">
         <v>50</v>
@@ -12631,12 +12631,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -10199,7 +10199,7 @@
         <v>125666433</v>
       </c>
       <c r="B92" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>125670523</v>
       </c>
       <c r="B93" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>125657636</v>
       </c>
       <c r="B94" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10519,10 +10519,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125657638</v>
+        <v>125657705</v>
       </c>
       <c r="B95" t="n">
-        <v>56835</v>
+        <v>88651</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10530,53 +10530,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>477427</v>
+        <v>477545</v>
       </c>
       <c r="R95" t="n">
-        <v>6951523</v>
+        <v>6951453</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10600,12 +10584,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10625,17 +10609,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125657705</v>
+        <v>125657638</v>
       </c>
       <c r="B96" t="n">
-        <v>88647</v>
+        <v>56839</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10643,37 +10627,53 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>477545</v>
+        <v>477427</v>
       </c>
       <c r="R96" t="n">
-        <v>6951453</v>
+        <v>6951523</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10697,12 +10697,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10732,7 +10732,7 @@
         <v>125663151</v>
       </c>
       <c r="B97" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>125671901</v>
       </c>
       <c r="B98" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>125671631</v>
       </c>
       <c r="B99" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>125657637</v>
       </c>
       <c r="B100" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>125670934</v>
       </c>
       <c r="B101" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11275,10 +11275,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125670788</v>
+        <v>125671881</v>
       </c>
       <c r="B102" t="n">
-        <v>57652</v>
+        <v>80080</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11286,39 +11286,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477403</v>
+        <v>477440</v>
       </c>
       <c r="R102" t="n">
-        <v>6951670</v>
+        <v>6951449</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11350,7 +11345,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11360,7 +11355,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11387,10 +11382,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125671881</v>
+        <v>125670788</v>
       </c>
       <c r="B103" t="n">
-        <v>80076</v>
+        <v>57656</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11398,34 +11393,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477440</v>
+        <v>477403</v>
       </c>
       <c r="R103" t="n">
-        <v>6951449</v>
+        <v>6951670</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11497,7 +11497,7 @@
         <v>125669436</v>
       </c>
       <c r="B104" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>125657704</v>
       </c>
       <c r="B105" t="n">
-        <v>91812</v>
+        <v>91816</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>125663252</v>
       </c>
       <c r="B106" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>125668481</v>
       </c>
       <c r="B107" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>125666595</v>
       </c>
       <c r="B108" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>125666274</v>
       </c>
       <c r="B109" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>125757747</v>
       </c>
       <c r="B110" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>125757748</v>
       </c>
       <c r="B111" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>125757749</v>
       </c>
       <c r="B112" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>125657630</v>
       </c>
       <c r="B113" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>125657634</v>
       </c>
       <c r="B114" t="n">
-        <v>57494</v>
+        <v>57498</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57652</v>
+        <v>57498</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B116" t="n">
-        <v>57494</v>
+        <v>57656</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>
@@ -12892,7 +12892,7 @@
         <v>125657631</v>
       </c>
       <c r="B117" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -11494,50 +11494,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125669436</v>
+        <v>125657704</v>
       </c>
       <c r="B104" t="n">
-        <v>57656</v>
+        <v>91816</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477482</v>
+        <v>477483</v>
       </c>
       <c r="R104" t="n">
-        <v>6951702</v>
+        <v>6951493</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11564,22 +11559,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11594,57 +11579,62 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125657704</v>
+        <v>125669436</v>
       </c>
       <c r="B105" t="n">
-        <v>91816</v>
+        <v>57656</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477483</v>
+        <v>477482</v>
       </c>
       <c r="R105" t="n">
-        <v>6951493</v>
+        <v>6951702</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11671,12 +11661,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11691,12 +11691,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B115" t="n">
-        <v>57498</v>
+        <v>57656</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B116" t="n">
-        <v>57656</v>
+        <v>57498</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12437,27 +12437,27 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125657630</v>
+        <v>125657634</v>
       </c>
       <c r="B113" t="n">
-        <v>57656</v>
+        <v>57498</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12488,10 +12488,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477442</v>
+        <v>477644</v>
       </c>
       <c r="R113" t="n">
-        <v>6951549</v>
+        <v>6951563</v>
       </c>
       <c r="S113" t="n">
         <v>50</v>
@@ -12518,12 +12518,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12550,27 +12550,27 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125657634</v>
+        <v>125657630</v>
       </c>
       <c r="B114" t="n">
-        <v>57498</v>
+        <v>57656</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477644</v>
+        <v>477442</v>
       </c>
       <c r="R114" t="n">
-        <v>6951563</v>
+        <v>6951549</v>
       </c>
       <c r="S114" t="n">
         <v>50</v>
@@ -12631,12 +12631,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12440,7 +12440,7 @@
         <v>125657634</v>
       </c>
       <c r="B113" t="n">
-        <v>57498</v>
+        <v>57499</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>125657630</v>
       </c>
       <c r="B114" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12663,27 +12663,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125657633</v>
+        <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57656</v>
+        <v>57499</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12700,7 +12700,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477455</v>
+        <v>477530</v>
       </c>
       <c r="R115" t="n">
         <v>6951481</v>
@@ -12776,27 +12776,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125657635</v>
+        <v>125657633</v>
       </c>
       <c r="B116" t="n">
-        <v>57498</v>
+        <v>57657</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477530</v>
+        <v>477455</v>
       </c>
       <c r="R116" t="n">
         <v>6951481</v>
@@ -12892,7 +12892,7 @@
         <v>125657631</v>
       </c>
       <c r="B117" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12437,27 +12437,27 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125657634</v>
+        <v>125657630</v>
       </c>
       <c r="B113" t="n">
-        <v>57499</v>
+        <v>57657</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12488,10 +12488,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477644</v>
+        <v>477442</v>
       </c>
       <c r="R113" t="n">
-        <v>6951563</v>
+        <v>6951549</v>
       </c>
       <c r="S113" t="n">
         <v>50</v>
@@ -12518,12 +12518,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12550,27 +12550,27 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125657630</v>
+        <v>125657634</v>
       </c>
       <c r="B114" t="n">
-        <v>57657</v>
+        <v>57499</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477442</v>
+        <v>477644</v>
       </c>
       <c r="R114" t="n">
-        <v>6951549</v>
+        <v>6951563</v>
       </c>
       <c r="S114" t="n">
         <v>50</v>
@@ -12631,12 +12631,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13000,6 +13000,515 @@
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129875243</v>
+      </c>
+      <c r="B118" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>477625</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6951553</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129875244</v>
+      </c>
+      <c r="B119" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>477584</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6951573</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129875247</v>
+      </c>
+      <c r="B120" t="n">
+        <v>98801</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>477516</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6951462</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129875245</v>
+      </c>
+      <c r="B121" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>477568</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6951562</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129875246</v>
+      </c>
+      <c r="B122" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>477517</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6951486</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -13207,7 +13207,7 @@
         <v>129875247</v>
       </c>
       <c r="B120" t="n">
-        <v>98801</v>
+        <v>98811</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -13005,7 +13005,7 @@
         <v>129875243</v>
       </c>
       <c r="B118" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>129875244</v>
       </c>
       <c r="B119" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>129875247</v>
       </c>
       <c r="B120" t="n">
-        <v>98811</v>
+        <v>98815</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>129875245</v>
       </c>
       <c r="B121" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>129875246</v>
       </c>
       <c r="B122" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -13005,7 +13005,7 @@
         <v>129875243</v>
       </c>
       <c r="B118" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>129875244</v>
       </c>
       <c r="B119" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>129875247</v>
       </c>
       <c r="B120" t="n">
-        <v>98815</v>
+        <v>98818</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>129875245</v>
       </c>
       <c r="B121" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>129875246</v>
       </c>
       <c r="B122" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -13005,7 +13005,7 @@
         <v>129875243</v>
       </c>
       <c r="B118" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>129875244</v>
       </c>
       <c r="B119" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>129875247</v>
       </c>
       <c r="B120" t="n">
-        <v>98818</v>
+        <v>98819</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>129875245</v>
       </c>
       <c r="B121" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>129875246</v>
       </c>
       <c r="B122" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -13005,7 +13005,7 @@
         <v>129875243</v>
       </c>
       <c r="B118" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>129875244</v>
       </c>
       <c r="B119" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>129875247</v>
       </c>
       <c r="B120" t="n">
-        <v>98819</v>
+        <v>98836</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>129875245</v>
       </c>
       <c r="B121" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>129875246</v>
       </c>
       <c r="B122" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -13207,7 +13207,7 @@
         <v>129875247</v>
       </c>
       <c r="B120" t="n">
-        <v>98852</v>
+        <v>98854</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12553,7 +12553,7 @@
         <v>125657634</v>
       </c>
       <c r="B114" t="n">
-        <v>57499</v>
+        <v>57667</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57499</v>
+        <v>57667</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>129875243</v>
       </c>
       <c r="B118" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>129875244</v>
       </c>
       <c r="B119" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>129875247</v>
       </c>
       <c r="B120" t="n">
-        <v>98854</v>
+        <v>98941</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>129875245</v>
       </c>
       <c r="B121" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>129875246</v>
       </c>
       <c r="B122" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12553,7 +12553,7 @@
         <v>125657634</v>
       </c>
       <c r="B114" t="n">
-        <v>57667</v>
+        <v>57693</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57667</v>
+        <v>57693</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12553,7 +12553,7 @@
         <v>125657634</v>
       </c>
       <c r="B114" t="n">
-        <v>57693</v>
+        <v>57695</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57693</v>
+        <v>57695</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -12553,7 +12553,7 @@
         <v>125657634</v>
       </c>
       <c r="B114" t="n">
-        <v>57695</v>
+        <v>57703</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>125657635</v>
       </c>
       <c r="B115" t="n">
-        <v>57695</v>
+        <v>57703</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY128"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7892,48 +7892,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>103969177</v>
+        <v>134550625</v>
       </c>
       <c r="B74" t="n">
-        <v>79583</v>
+        <v>80488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Storstensjön, Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477548</v>
+        <v>477791</v>
       </c>
       <c r="R74" t="n">
-        <v>6951437</v>
+        <v>6951621</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7957,22 +7957,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7983,35 +7983,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AS74" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>103969161</v>
+        <v>103969177</v>
       </c>
       <c r="B75" t="n">
-        <v>80461</v>
+        <v>79583</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8019,21 +8010,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8043,10 +8034,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477549</v>
+        <v>477548</v>
       </c>
       <c r="R75" t="n">
-        <v>6951436</v>
+        <v>6951437</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8078,7 +8069,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8088,7 +8079,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8124,7 +8115,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122154197</v>
+        <v>103969161</v>
       </c>
       <c r="B76" t="n">
         <v>80461</v>
@@ -8155,17 +8146,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477617</v>
+        <v>477549</v>
       </c>
       <c r="R76" t="n">
-        <v>6951666</v>
+        <v>6951436</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8189,12 +8180,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8205,23 +8206,32 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122154209</v>
+        <v>122154197</v>
       </c>
       <c r="B77" t="n">
         <v>80461</v>
@@ -8256,10 +8266,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477462</v>
+        <v>477617</v>
       </c>
       <c r="R77" t="n">
-        <v>6951485</v>
+        <v>6951666</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8318,7 +8328,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122154213</v>
+        <v>122154209</v>
       </c>
       <c r="B78" t="n">
         <v>80461</v>
@@ -8353,10 +8363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477424</v>
+        <v>477462</v>
       </c>
       <c r="R78" t="n">
-        <v>6951452</v>
+        <v>6951485</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8415,7 +8425,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122154220</v>
+        <v>122154213</v>
       </c>
       <c r="B79" t="n">
         <v>80461</v>
@@ -8450,10 +8460,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477476</v>
+        <v>477424</v>
       </c>
       <c r="R79" t="n">
-        <v>6951463</v>
+        <v>6951452</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8512,10 +8522,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122154196</v>
+        <v>122154220</v>
       </c>
       <c r="B80" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8523,21 +8533,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8547,10 +8557,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477621</v>
+        <v>477476</v>
       </c>
       <c r="R80" t="n">
-        <v>6951670</v>
+        <v>6951463</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8609,10 +8619,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>103969189</v>
+        <v>122154196</v>
       </c>
       <c r="B81" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8620,37 +8630,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477539</v>
+        <v>477621</v>
       </c>
       <c r="R81" t="n">
-        <v>6951435</v>
+        <v>6951670</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8674,22 +8684,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8700,32 +8700,23 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122178229</v>
+        <v>103969189</v>
       </c>
       <c r="B82" t="n">
         <v>80468</v>
@@ -8756,17 +8747,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477587</v>
+        <v>477539</v>
       </c>
       <c r="R82" t="n">
-        <v>6951569</v>
+        <v>6951435</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8790,12 +8781,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8806,23 +8807,32 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125671901</v>
+        <v>122178229</v>
       </c>
       <c r="B83" t="n">
         <v>80468</v>
@@ -8853,17 +8863,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477440</v>
+        <v>477587</v>
       </c>
       <c r="R83" t="n">
-        <v>6951449</v>
+        <v>6951569</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8887,22 +8897,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>20:40</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>20:40</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8917,62 +8917,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>103969196</v>
+        <v>125671901</v>
       </c>
       <c r="B84" t="n">
-        <v>57953</v>
+        <v>80468</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477415</v>
+        <v>477440</v>
       </c>
       <c r="R84" t="n">
-        <v>6951679</v>
+        <v>6951449</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8999,22 +8994,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9025,32 +9020,23 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122154217</v>
+        <v>103969196</v>
       </c>
       <c r="B85" t="n">
         <v>57953</v>
@@ -9078,24 +9064,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477473</v>
+        <v>477415</v>
       </c>
       <c r="R85" t="n">
-        <v>6951436</v>
+        <v>6951679</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9119,12 +9106,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9135,23 +9132,32 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125657630</v>
+        <v>122154217</v>
       </c>
       <c r="B86" t="n">
         <v>57953</v>
@@ -9184,31 +9190,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477442</v>
+        <v>477473</v>
       </c>
       <c r="R86" t="n">
-        <v>6951549</v>
+        <v>6951436</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9232,12 +9226,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9252,19 +9246,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125657631</v>
+        <v>125657630</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -9315,10 +9309,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477569</v>
+        <v>477442</v>
       </c>
       <c r="R87" t="n">
-        <v>6951502</v>
+        <v>6951549</v>
       </c>
       <c r="S87" t="n">
         <v>50</v>
@@ -9345,12 +9339,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9377,7 +9371,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125657633</v>
+        <v>125657631</v>
       </c>
       <c r="B88" t="n">
         <v>57953</v>
@@ -9414,7 +9408,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9428,10 +9422,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477455</v>
+        <v>477569</v>
       </c>
       <c r="R88" t="n">
-        <v>6951481</v>
+        <v>6951502</v>
       </c>
       <c r="S88" t="n">
         <v>50</v>
@@ -9458,12 +9452,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9490,7 +9484,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125663151</v>
+        <v>125657633</v>
       </c>
       <c r="B89" t="n">
         <v>57953</v>
@@ -9518,25 +9512,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477420</v>
+        <v>477455</v>
       </c>
       <c r="R89" t="n">
-        <v>6951546</v>
+        <v>6951481</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9560,22 +9565,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9590,19 +9585,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125663252</v>
+        <v>125663151</v>
       </c>
       <c r="B90" t="n">
         <v>57953</v>
@@ -9642,10 +9637,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477408</v>
+        <v>477420</v>
       </c>
       <c r="R90" t="n">
-        <v>6951545</v>
+        <v>6951546</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9677,7 +9672,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9687,7 +9682,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9714,7 +9709,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125669436</v>
+        <v>125663252</v>
       </c>
       <c r="B91" t="n">
         <v>57953</v>
@@ -9754,10 +9749,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>477482</v>
+        <v>477408</v>
       </c>
       <c r="R91" t="n">
-        <v>6951702</v>
+        <v>6951545</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9789,7 +9784,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9799,7 +9794,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9826,7 +9821,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125670788</v>
+        <v>125669436</v>
       </c>
       <c r="B92" t="n">
         <v>57953</v>
@@ -9866,10 +9861,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>477403</v>
+        <v>477482</v>
       </c>
       <c r="R92" t="n">
-        <v>6951670</v>
+        <v>6951702</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9901,7 +9896,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9911,7 +9906,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9938,7 +9933,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125757748</v>
+        <v>125670788</v>
       </c>
       <c r="B93" t="n">
         <v>57953</v>
@@ -9974,14 +9969,14 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Storstensjön, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>477491</v>
+        <v>477403</v>
       </c>
       <c r="R93" t="n">
-        <v>6951708</v>
+        <v>6951670</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10011,14 +10006,19 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10045,48 +10045,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122154172</v>
+        <v>125757748</v>
       </c>
       <c r="B94" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>477879</v>
+        <v>477491</v>
       </c>
       <c r="R94" t="n">
-        <v>6951648</v>
+        <v>6951708</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10110,12 +10115,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10130,19 +10140,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122154186</v>
+        <v>122154172</v>
       </c>
       <c r="B95" t="n">
         <v>5179</v>
@@ -10177,10 +10187,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>477370</v>
+        <v>477879</v>
       </c>
       <c r="R95" t="n">
-        <v>6951711</v>
+        <v>6951648</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10239,7 +10249,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122154187</v>
+        <v>122154186</v>
       </c>
       <c r="B96" t="n">
         <v>5179</v>
@@ -10274,10 +10284,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>477368</v>
+        <v>477370</v>
       </c>
       <c r="R96" t="n">
-        <v>6951718</v>
+        <v>6951711</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10336,10 +10346,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122154169</v>
+        <v>122154187</v>
       </c>
       <c r="B97" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10347,38 +10357,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>477886</v>
+        <v>477368</v>
       </c>
       <c r="R97" t="n">
-        <v>6951641</v>
+        <v>6951718</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10437,7 +10443,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122154215</v>
+        <v>122154169</v>
       </c>
       <c r="B98" t="n">
         <v>57132</v>
@@ -10465,17 +10471,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>477438</v>
+        <v>477886</v>
       </c>
       <c r="R98" t="n">
-        <v>6951412</v>
+        <v>6951641</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10534,7 +10544,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125657637</v>
+        <v>122154215</v>
       </c>
       <c r="B99" t="n">
         <v>57132</v>
@@ -10562,36 +10572,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>477459</v>
+        <v>477438</v>
       </c>
       <c r="R99" t="n">
-        <v>6951572</v>
+        <v>6951412</v>
       </c>
       <c r="S99" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10615,12 +10609,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10635,19 +10629,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125657638</v>
+        <v>125657637</v>
       </c>
       <c r="B100" t="n">
         <v>57132</v>
@@ -10698,10 +10692,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>477427</v>
+        <v>477459</v>
       </c>
       <c r="R100" t="n">
-        <v>6951523</v>
+        <v>6951572</v>
       </c>
       <c r="S100" t="n">
         <v>50</v>
@@ -10728,12 +10722,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10760,10 +10754,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122154224</v>
+        <v>125657638</v>
       </c>
       <c r="B101" t="n">
-        <v>57144</v>
+        <v>57132</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10771,16 +10765,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -10788,20 +10782,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>477538</v>
+        <v>477427</v>
       </c>
       <c r="R101" t="n">
-        <v>6951618</v>
+        <v>6951523</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10825,12 +10835,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10845,39 +10855,39 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125657634</v>
+        <v>122154224</v>
       </c>
       <c r="B102" t="n">
-        <v>57794</v>
+        <v>57144</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>102621</v>
+        <v>102613</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10885,36 +10895,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477644</v>
+        <v>477538</v>
       </c>
       <c r="R102" t="n">
-        <v>6951563</v>
+        <v>6951618</v>
       </c>
       <c r="S102" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10938,12 +10932,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10958,19 +10952,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125657635</v>
+        <v>125657634</v>
       </c>
       <c r="B103" t="n">
         <v>57794</v>
@@ -11021,10 +11015,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477530</v>
+        <v>477644</v>
       </c>
       <c r="R103" t="n">
-        <v>6951481</v>
+        <v>6951563</v>
       </c>
       <c r="S103" t="n">
         <v>50</v>
@@ -11051,12 +11045,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11083,10 +11077,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122154170</v>
+        <v>125657635</v>
       </c>
       <c r="B104" t="n">
-        <v>58057</v>
+        <v>57794</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11094,16 +11088,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11113,22 +11107,34 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477882</v>
+        <v>477530</v>
       </c>
       <c r="R104" t="n">
-        <v>6951635</v>
+        <v>6951481</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11152,12 +11158,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11172,19 +11178,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125657636</v>
+        <v>122154170</v>
       </c>
       <c r="B105" t="n">
         <v>58057</v>
@@ -11212,32 +11218,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477560</v>
+        <v>477882</v>
       </c>
       <c r="R105" t="n">
-        <v>6951544</v>
+        <v>6951635</v>
       </c>
       <c r="S105" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11261,12 +11259,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11281,39 +11279,39 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122154193</v>
+        <v>125657636</v>
       </c>
       <c r="B106" t="n">
-        <v>5199</v>
+        <v>58057</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11322,19 +11320,31 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>477460</v>
+        <v>477560</v>
       </c>
       <c r="R106" t="n">
-        <v>6951750</v>
+        <v>6951544</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11358,12 +11368,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11378,22 +11388,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>103969202</v>
+        <v>122154193</v>
       </c>
       <c r="B107" t="n">
-        <v>99035</v>
+        <v>5199</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11401,37 +11411,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219790</v>
+        <v>105930</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477499</v>
+        <v>477460</v>
       </c>
       <c r="R107" t="n">
-        <v>6951560</v>
+        <v>6951750</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11455,22 +11465,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11481,32 +11481,23 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>122154160</v>
+        <v>103969202</v>
       </c>
       <c r="B108" t="n">
         <v>99035</v>
@@ -11537,17 +11528,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>477847</v>
+        <v>477499</v>
       </c>
       <c r="R108" t="n">
-        <v>6951679</v>
+        <v>6951560</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11571,12 +11562,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11587,23 +11588,32 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122154164</v>
+        <v>122154160</v>
       </c>
       <c r="B109" t="n">
         <v>99035</v>
@@ -11638,10 +11648,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>477933</v>
+        <v>477847</v>
       </c>
       <c r="R109" t="n">
-        <v>6951709</v>
+        <v>6951679</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11700,10 +11710,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>103969191</v>
+        <v>122154164</v>
       </c>
       <c r="B110" t="n">
-        <v>99456</v>
+        <v>99035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11711,37 +11721,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>477557</v>
+        <v>477933</v>
       </c>
       <c r="R110" t="n">
-        <v>6951591</v>
+        <v>6951709</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11765,22 +11775,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11791,32 +11791,23 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>103969199</v>
+        <v>103969191</v>
       </c>
       <c r="B111" t="n">
         <v>99456</v>
@@ -11847,14 +11838,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>477403</v>
+        <v>477557</v>
       </c>
       <c r="R111" t="n">
-        <v>6951589</v>
+        <v>6951591</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11886,7 +11877,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11896,7 +11887,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11932,10 +11923,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122154190</v>
+        <v>103969199</v>
       </c>
       <c r="B112" t="n">
-        <v>99022</v>
+        <v>99456</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11943,37 +11934,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>477407</v>
+        <v>477403</v>
       </c>
       <c r="R112" t="n">
-        <v>6951732</v>
+        <v>6951589</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11997,12 +11988,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12013,23 +12014,32 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122154191</v>
+        <v>122154190</v>
       </c>
       <c r="B113" t="n">
         <v>99022</v>
@@ -12064,10 +12074,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477424</v>
+        <v>477407</v>
       </c>
       <c r="R113" t="n">
-        <v>6951736</v>
+        <v>6951732</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12126,7 +12136,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122154202</v>
+        <v>122154191</v>
       </c>
       <c r="B114" t="n">
         <v>99022</v>
@@ -12161,10 +12171,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477389</v>
+        <v>477424</v>
       </c>
       <c r="R114" t="n">
-        <v>6951610</v>
+        <v>6951736</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12223,7 +12233,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122154204</v>
+        <v>122154202</v>
       </c>
       <c r="B115" t="n">
         <v>99022</v>
@@ -12258,10 +12268,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477373</v>
+        <v>477389</v>
       </c>
       <c r="R115" t="n">
-        <v>6951613</v>
+        <v>6951610</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12320,7 +12330,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122154218</v>
+        <v>122154204</v>
       </c>
       <c r="B116" t="n">
         <v>99022</v>
@@ -12355,10 +12365,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477479</v>
+        <v>477373</v>
       </c>
       <c r="R116" t="n">
-        <v>6951442</v>
+        <v>6951613</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12417,7 +12427,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122172652</v>
+        <v>122154218</v>
       </c>
       <c r="B117" t="n">
         <v>99022</v>
@@ -12452,10 +12462,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>477755</v>
+        <v>477479</v>
       </c>
       <c r="R117" t="n">
-        <v>6951671</v>
+        <v>6951442</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12502,22 +12512,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129875187</v>
+        <v>122172652</v>
       </c>
       <c r="B118" t="n">
-        <v>97989</v>
+        <v>99022</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12525,41 +12535,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221941</v>
+        <v>220093</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>477586</v>
+        <v>477755</v>
       </c>
       <c r="R118" t="n">
-        <v>6951427</v>
+        <v>6951671</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12583,12 +12589,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12603,26 +12609,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122154205</v>
+        <v>129875187</v>
       </c>
       <c r="B119" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12630,16 +12632,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -12647,20 +12649,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>477367</v>
+        <v>477586</v>
       </c>
       <c r="R119" t="n">
-        <v>6951594</v>
+        <v>6951427</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12684,12 +12690,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12704,19 +12710,23 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122172654</v>
+        <v>122154205</v>
       </c>
       <c r="B120" t="n">
         <v>97983</v>
@@ -12751,10 +12761,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>477639</v>
+        <v>477367</v>
       </c>
       <c r="R120" t="n">
-        <v>6951706</v>
+        <v>6951594</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12801,19 +12811,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122178222</v>
+        <v>122172654</v>
       </c>
       <c r="B121" t="n">
         <v>97983</v>
@@ -12848,10 +12858,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>477540</v>
+        <v>477639</v>
       </c>
       <c r="R121" t="n">
-        <v>6951594</v>
+        <v>6951706</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12878,12 +12888,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12898,19 +12908,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122178225</v>
+        <v>122178222</v>
       </c>
       <c r="B122" t="n">
         <v>97983</v>
@@ -12945,10 +12955,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>477580</v>
+        <v>477540</v>
       </c>
       <c r="R122" t="n">
-        <v>6951617</v>
+        <v>6951594</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13007,10 +13017,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>103969155</v>
+        <v>122178225</v>
       </c>
       <c r="B123" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13018,37 +13028,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>477554</v>
+        <v>477580</v>
       </c>
       <c r="R123" t="n">
-        <v>6951438</v>
+        <v>6951617</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13072,22 +13082,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13098,32 +13098,23 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122178248</v>
+        <v>103969155</v>
       </c>
       <c r="B124" t="n">
         <v>99140</v>
@@ -13154,17 +13145,17 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>477538</v>
+        <v>477554</v>
       </c>
       <c r="R124" t="n">
-        <v>6951419</v>
+        <v>6951438</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13188,12 +13179,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13204,23 +13205,32 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129875247</v>
+        <v>122178248</v>
       </c>
       <c r="B125" t="n">
         <v>99140</v>
@@ -13248,24 +13258,20 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>477516</v>
+        <v>477538</v>
       </c>
       <c r="R125" t="n">
-        <v>6951462</v>
+        <v>6951419</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13289,12 +13295,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13309,23 +13315,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129875248</v>
+        <v>129875247</v>
       </c>
       <c r="B126" t="n">
         <v>99140</v>
@@ -13355,7 +13357,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -13364,10 +13366,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>477509</v>
+        <v>477516</v>
       </c>
       <c r="R126" t="n">
-        <v>6951422</v>
+        <v>6951462</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13430,48 +13432,52 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122178235</v>
+        <v>129875248</v>
       </c>
       <c r="B127" t="n">
-        <v>79917</v>
+        <v>99140</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>477573</v>
+        <v>477509</v>
       </c>
       <c r="R127" t="n">
-        <v>6951539</v>
+        <v>6951422</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13495,12 +13501,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13515,22 +13521,26 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122154212</v>
+        <v>122178235</v>
       </c>
       <c r="B128" t="n">
-        <v>92329</v>
+        <v>79917</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13538,21 +13548,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6040186</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13562,10 +13572,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>477420</v>
+        <v>477573</v>
       </c>
       <c r="R128" t="n">
-        <v>6951455</v>
+        <v>6951539</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -13592,12 +13602,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13606,22 +13616,119 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>122154212</v>
+      </c>
+      <c r="B129" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>477420</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6951455</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
+      <c r="AX129" t="inlineStr">
         <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AY128" t="inlineStr"/>
+      <c r="AY129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122154189</v>
+        <v>134591620</v>
       </c>
       <c r="B3" t="n">
-        <v>83299</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Storstensjön, Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477405</v>
+        <v>477471</v>
       </c>
       <c r="R3" t="n">
-        <v>6951731</v>
+        <v>6951582</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122154195</v>
+        <v>122154189</v>
       </c>
       <c r="B4" t="n">
         <v>83299</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477495</v>
+        <v>477405</v>
       </c>
       <c r="R4" t="n">
-        <v>6951727</v>
+        <v>6951731</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122154201</v>
+        <v>122154195</v>
       </c>
       <c r="B5" t="n">
         <v>83299</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477404</v>
+        <v>477495</v>
       </c>
       <c r="R5" t="n">
-        <v>6951629</v>
+        <v>6951727</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178226</v>
+        <v>122154201</v>
       </c>
       <c r="B6" t="n">
         <v>83299</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477581</v>
+        <v>477404</v>
       </c>
       <c r="R6" t="n">
-        <v>6951614</v>
+        <v>6951629</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122154207</v>
+        <v>122178226</v>
       </c>
       <c r="B7" t="n">
-        <v>83298</v>
+        <v>83299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477445</v>
+        <v>477581</v>
       </c>
       <c r="R7" t="n">
-        <v>6951570</v>
+        <v>6951614</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1245,60 +1245,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125657705</v>
+        <v>122154207</v>
       </c>
       <c r="B8" t="n">
-        <v>89292</v>
+        <v>83298</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477545</v>
+        <v>477445</v>
       </c>
       <c r="R8" t="n">
-        <v>6951453</v>
+        <v>6951570</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1342,7 +1342,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125657704</v>
+        <v>125657705</v>
       </c>
       <c r="B9" t="n">
-        <v>92509</v>
+        <v>89292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477483</v>
+        <v>477545</v>
       </c>
       <c r="R9" t="n">
-        <v>6951493</v>
+        <v>6951453</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,48 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122154175</v>
+        <v>125657704</v>
       </c>
       <c r="B10" t="n">
-        <v>91905</v>
+        <v>92509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477793</v>
+        <v>477483</v>
       </c>
       <c r="R10" t="n">
-        <v>6951655</v>
+        <v>6951493</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1536,7 +1536,7 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122154203</v>
+        <v>122154175</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477381</v>
+        <v>477793</v>
       </c>
       <c r="R11" t="n">
-        <v>6951610</v>
+        <v>6951655</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125670523</v>
+        <v>122154203</v>
       </c>
       <c r="B12" t="n">
         <v>91909</v>
@@ -1676,17 +1676,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477385</v>
+        <v>477381</v>
       </c>
       <c r="R12" t="n">
-        <v>6951687</v>
+        <v>6951610</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1710,22 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>20:01</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>20:01</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1740,22 +1730,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125666433</v>
+        <v>125670523</v>
       </c>
       <c r="B13" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477416</v>
+        <v>477385</v>
       </c>
       <c r="R13" t="n">
-        <v>6951641</v>
+        <v>6951687</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1822,7 +1812,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1832,7 +1822,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103969193</v>
+        <v>125666433</v>
       </c>
       <c r="B14" t="n">
-        <v>80342</v>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,34 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2080</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477537</v>
+        <v>477416</v>
       </c>
       <c r="R14" t="n">
-        <v>6951437</v>
+        <v>6951641</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1924,22 +1914,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1950,37 +1940,23 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122178244</v>
+        <v>103969193</v>
       </c>
       <c r="B15" t="n">
         <v>80342</v>
@@ -2011,17 +1987,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477538</v>
+        <v>477537</v>
       </c>
       <c r="R15" t="n">
-        <v>6951440</v>
+        <v>6951437</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2045,12 +2021,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2061,26 +2047,40 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122154161</v>
+        <v>122178244</v>
       </c>
       <c r="B16" t="n">
-        <v>80433</v>
+        <v>80342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2088,21 +2088,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477944</v>
+        <v>477538</v>
       </c>
       <c r="R16" t="n">
-        <v>6951693</v>
+        <v>6951440</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2162,19 +2162,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122154208</v>
+        <v>122154161</v>
       </c>
       <c r="B17" t="n">
         <v>80433</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477462</v>
+        <v>477944</v>
       </c>
       <c r="R17" t="n">
-        <v>6951484</v>
+        <v>6951693</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2271,7 +2271,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122154221</v>
+        <v>122154208</v>
       </c>
       <c r="B18" t="n">
         <v>80433</v>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477477</v>
+        <v>477462</v>
       </c>
       <c r="R18" t="n">
-        <v>6951466</v>
+        <v>6951484</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125671631</v>
+        <v>122154221</v>
       </c>
       <c r="B19" t="n">
         <v>80433</v>
@@ -2399,17 +2399,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477425</v>
+        <v>477477</v>
       </c>
       <c r="R19" t="n">
-        <v>6951524</v>
+        <v>6951466</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2433,22 +2433,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>20:33</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>20:33</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2463,60 +2453,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178224</v>
+        <v>125671631</v>
       </c>
       <c r="B20" t="n">
-        <v>95962</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2387</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477572</v>
+        <v>477425</v>
       </c>
       <c r="R20" t="n">
-        <v>6951626</v>
+        <v>6951524</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2540,12 +2530,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2560,19 +2560,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178238</v>
+        <v>122178224</v>
       </c>
       <c r="B21" t="n">
         <v>95962</v>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477538</v>
+        <v>477572</v>
       </c>
       <c r="R21" t="n">
-        <v>6951456</v>
+        <v>6951626</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178223</v>
+        <v>122178238</v>
       </c>
       <c r="B22" t="n">
-        <v>95769</v>
+        <v>95962</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2680,21 +2680,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2412</v>
+        <v>2387</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477540</v>
+        <v>477538</v>
       </c>
       <c r="R22" t="n">
-        <v>6951613</v>
+        <v>6951456</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2766,10 +2766,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103969200</v>
+        <v>122178223</v>
       </c>
       <c r="B23" t="n">
-        <v>96338</v>
+        <v>95769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2777,37 +2777,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>2412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477518</v>
+        <v>477540</v>
       </c>
       <c r="R23" t="n">
-        <v>6951458</v>
+        <v>6951613</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2831,22 +2831,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2857,35 +2847,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103969215</v>
+        <v>103969200</v>
       </c>
       <c r="B24" t="n">
-        <v>96350</v>
+        <v>96338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,34 +2874,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477540</v>
+        <v>477518</v>
       </c>
       <c r="R24" t="n">
-        <v>6951626</v>
+        <v>6951458</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,7 +2933,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2962,7 +2943,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2998,10 +2979,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122172638</v>
+        <v>103969215</v>
       </c>
       <c r="B25" t="n">
-        <v>91680</v>
+        <v>96350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,37 +2990,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3215</v>
+        <v>2813</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477836</v>
+        <v>477540</v>
       </c>
       <c r="R25" t="n">
-        <v>6951703</v>
+        <v>6951626</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3063,12 +3044,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3079,48 +3070,57 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122154163</v>
+        <v>122172638</v>
       </c>
       <c r="B26" t="n">
-        <v>79327</v>
+        <v>91680</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477928</v>
+        <v>477836</v>
       </c>
       <c r="R26" t="n">
-        <v>6951710</v>
+        <v>6951703</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3180,19 +3180,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122154173</v>
+        <v>122154163</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477825</v>
+        <v>477928</v>
       </c>
       <c r="R27" t="n">
-        <v>6951660</v>
+        <v>6951710</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122154177</v>
+        <v>122154173</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477767</v>
+        <v>477825</v>
       </c>
       <c r="R28" t="n">
-        <v>6951662</v>
+        <v>6951660</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3386,7 +3386,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122154194</v>
+        <v>122154177</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477461</v>
+        <v>477767</v>
       </c>
       <c r="R29" t="n">
-        <v>6951754</v>
+        <v>6951662</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122154200</v>
+        <v>122154194</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477435</v>
+        <v>477461</v>
       </c>
       <c r="R30" t="n">
-        <v>6951645</v>
+        <v>6951754</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122154206</v>
+        <v>122154200</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477411</v>
+        <v>477435</v>
       </c>
       <c r="R31" t="n">
-        <v>6951546</v>
+        <v>6951645</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178236</v>
+        <v>122154206</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477559</v>
+        <v>477411</v>
       </c>
       <c r="R32" t="n">
-        <v>6951532</v>
+        <v>6951546</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,19 +3762,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178249</v>
+        <v>122178236</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477540</v>
+        <v>477559</v>
       </c>
       <c r="R33" t="n">
-        <v>6951422</v>
+        <v>6951532</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3871,7 +3871,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125668481</v>
+        <v>122178249</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -3902,17 +3902,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477500</v>
+        <v>477540</v>
       </c>
       <c r="R34" t="n">
-        <v>6951693</v>
+        <v>6951422</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3936,22 +3936,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>18:50</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>18:50</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3966,57 +3956,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103969194</v>
+        <v>125668481</v>
       </c>
       <c r="B35" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477520</v>
+        <v>477500</v>
       </c>
       <c r="R35" t="n">
-        <v>6951430</v>
+        <v>6951693</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4043,22 +4033,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4069,73 +4059,64 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103969213</v>
+        <v>134589951</v>
       </c>
       <c r="B36" t="n">
-        <v>83307</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477408</v>
+        <v>477586</v>
       </c>
       <c r="R36" t="n">
-        <v>6951605</v>
+        <v>6951666</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4159,22 +4140,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4185,32 +4166,23 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122107872</v>
+        <v>103969194</v>
       </c>
       <c r="B37" t="n">
         <v>83307</v>
@@ -4241,17 +4213,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477979</v>
+        <v>477520</v>
       </c>
       <c r="R37" t="n">
-        <v>6951730</v>
+        <v>6951430</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4275,12 +4247,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4291,23 +4273,32 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122154188</v>
+        <v>103969213</v>
       </c>
       <c r="B38" t="n">
         <v>83307</v>
@@ -4338,17 +4329,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477377</v>
+        <v>477408</v>
       </c>
       <c r="R38" t="n">
-        <v>6951731</v>
+        <v>6951605</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4372,12 +4363,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4388,23 +4389,32 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122154216</v>
+        <v>122107872</v>
       </c>
       <c r="B39" t="n">
         <v>83307</v>
@@ -4439,10 +4449,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477457</v>
+        <v>477979</v>
       </c>
       <c r="R39" t="n">
-        <v>6951419</v>
+        <v>6951730</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4469,12 +4479,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4489,19 +4499,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178242</v>
+        <v>122154188</v>
       </c>
       <c r="B40" t="n">
         <v>83307</v>
@@ -4536,10 +4546,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477534</v>
+        <v>477377</v>
       </c>
       <c r="R40" t="n">
-        <v>6951448</v>
+        <v>6951731</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4566,12 +4576,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4586,19 +4596,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178245</v>
+        <v>122154216</v>
       </c>
       <c r="B41" t="n">
         <v>83307</v>
@@ -4633,10 +4643,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477542</v>
+        <v>477457</v>
       </c>
       <c r="R41" t="n">
-        <v>6951443</v>
+        <v>6951419</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4663,12 +4673,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4683,19 +4693,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125666274</v>
+        <v>122178242</v>
       </c>
       <c r="B42" t="n">
         <v>83307</v>
@@ -4726,17 +4736,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477409</v>
+        <v>477534</v>
       </c>
       <c r="R42" t="n">
-        <v>6951634</v>
+        <v>6951448</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4760,22 +4770,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:33</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:33</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4790,19 +4790,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125757747</v>
+        <v>122178245</v>
       </c>
       <c r="B43" t="n">
         <v>83307</v>
@@ -4833,17 +4833,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storstensjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477462</v>
+        <v>477542</v>
       </c>
       <c r="R43" t="n">
-        <v>6951615</v>
+        <v>6951443</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4867,12 +4867,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4887,60 +4887,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122154192</v>
+        <v>125666274</v>
       </c>
       <c r="B44" t="n">
-        <v>80336</v>
+        <v>83307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>477446</v>
+        <v>477409</v>
       </c>
       <c r="R44" t="n">
-        <v>6951749</v>
+        <v>6951634</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4964,12 +4964,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4984,22 +4994,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103969154</v>
+        <v>125757747</v>
       </c>
       <c r="B45" t="n">
-        <v>80432</v>
+        <v>83307</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5007,34 +5017,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>477567</v>
+        <v>477462</v>
       </c>
       <c r="R45" t="n">
-        <v>6951571</v>
+        <v>6951615</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5061,22 +5071,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5087,73 +5087,64 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AS45" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>103969203</v>
+        <v>122154192</v>
       </c>
       <c r="B46" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>477373</v>
+        <v>477446</v>
       </c>
       <c r="R46" t="n">
-        <v>6951587</v>
+        <v>6951749</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5177,22 +5168,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5203,32 +5184,23 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103969216</v>
+        <v>103969154</v>
       </c>
       <c r="B47" t="n">
         <v>80432</v>
@@ -5259,14 +5231,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>477554</v>
+        <v>477567</v>
       </c>
       <c r="R47" t="n">
-        <v>6951436</v>
+        <v>6951571</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5298,7 +5270,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5308,7 +5280,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5344,7 +5316,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122154162</v>
+        <v>103969203</v>
       </c>
       <c r="B48" t="n">
         <v>80432</v>
@@ -5375,17 +5347,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>477943</v>
+        <v>477373</v>
       </c>
       <c r="R48" t="n">
-        <v>6951705</v>
+        <v>6951587</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5409,12 +5381,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5425,23 +5407,32 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122154171</v>
+        <v>103969216</v>
       </c>
       <c r="B49" t="n">
         <v>80432</v>
@@ -5472,17 +5463,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>477875</v>
+        <v>477554</v>
       </c>
       <c r="R49" t="n">
-        <v>6951643</v>
+        <v>6951436</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5506,12 +5497,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5522,23 +5523,32 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122154174</v>
+        <v>122154162</v>
       </c>
       <c r="B50" t="n">
         <v>80432</v>
@@ -5573,10 +5583,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>477833</v>
+        <v>477943</v>
       </c>
       <c r="R50" t="n">
-        <v>6951669</v>
+        <v>6951705</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5635,7 +5645,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122154198</v>
+        <v>122154171</v>
       </c>
       <c r="B51" t="n">
         <v>80432</v>
@@ -5670,10 +5680,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>477617</v>
+        <v>477875</v>
       </c>
       <c r="R51" t="n">
-        <v>6951666</v>
+        <v>6951643</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5732,7 +5742,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122154210</v>
+        <v>122154174</v>
       </c>
       <c r="B52" t="n">
         <v>80432</v>
@@ -5767,10 +5777,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>477464</v>
+        <v>477833</v>
       </c>
       <c r="R52" t="n">
-        <v>6951483</v>
+        <v>6951669</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5829,7 +5839,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122154214</v>
+        <v>122154198</v>
       </c>
       <c r="B53" t="n">
         <v>80432</v>
@@ -5864,10 +5874,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477421</v>
+        <v>477617</v>
       </c>
       <c r="R53" t="n">
-        <v>6951454</v>
+        <v>6951666</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5926,7 +5936,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122154219</v>
+        <v>122154210</v>
       </c>
       <c r="B54" t="n">
         <v>80432</v>
@@ -5961,10 +5971,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>477495</v>
+        <v>477464</v>
       </c>
       <c r="R54" t="n">
-        <v>6951463</v>
+        <v>6951483</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6023,7 +6033,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122154225</v>
+        <v>122154214</v>
       </c>
       <c r="B55" t="n">
         <v>80432</v>
@@ -6058,10 +6068,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>477572</v>
+        <v>477421</v>
       </c>
       <c r="R55" t="n">
-        <v>6951618</v>
+        <v>6951454</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6120,7 +6130,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122154227</v>
+        <v>122154219</v>
       </c>
       <c r="B56" t="n">
         <v>80432</v>
@@ -6155,10 +6165,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477615</v>
+        <v>477495</v>
       </c>
       <c r="R56" t="n">
-        <v>6951614</v>
+        <v>6951463</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6217,7 +6227,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122172640</v>
+        <v>122154225</v>
       </c>
       <c r="B57" t="n">
         <v>80432</v>
@@ -6252,10 +6262,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477949</v>
+        <v>477572</v>
       </c>
       <c r="R57" t="n">
-        <v>6951706</v>
+        <v>6951618</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6302,19 +6312,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122178220</v>
+        <v>122154227</v>
       </c>
       <c r="B58" t="n">
         <v>80432</v>
@@ -6349,10 +6359,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477556</v>
+        <v>477615</v>
       </c>
       <c r="R58" t="n">
-        <v>6951549</v>
+        <v>6951614</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6379,12 +6389,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6399,19 +6409,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122178221</v>
+        <v>122172640</v>
       </c>
       <c r="B59" t="n">
         <v>80432</v>
@@ -6446,10 +6456,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477543</v>
+        <v>477949</v>
       </c>
       <c r="R59" t="n">
-        <v>6951588</v>
+        <v>6951706</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6476,12 +6486,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6496,19 +6506,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122178227</v>
+        <v>122178220</v>
       </c>
       <c r="B60" t="n">
         <v>80432</v>
@@ -6543,10 +6553,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>477598</v>
+        <v>477556</v>
       </c>
       <c r="R60" t="n">
-        <v>6951610</v>
+        <v>6951549</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6605,7 +6615,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122178228</v>
+        <v>122178221</v>
       </c>
       <c r="B61" t="n">
         <v>80432</v>
@@ -6640,10 +6650,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>477590</v>
+        <v>477543</v>
       </c>
       <c r="R61" t="n">
-        <v>6951600</v>
+        <v>6951588</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6702,7 +6712,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122178231</v>
+        <v>122178227</v>
       </c>
       <c r="B62" t="n">
         <v>80432</v>
@@ -6737,10 +6747,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>477585</v>
+        <v>477598</v>
       </c>
       <c r="R62" t="n">
-        <v>6951573</v>
+        <v>6951610</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6799,7 +6809,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122178232</v>
+        <v>122178228</v>
       </c>
       <c r="B63" t="n">
         <v>80432</v>
@@ -6834,10 +6844,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477570</v>
+        <v>477590</v>
       </c>
       <c r="R63" t="n">
-        <v>6951563</v>
+        <v>6951600</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6896,7 +6906,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122178234</v>
+        <v>122178231</v>
       </c>
       <c r="B64" t="n">
         <v>80432</v>
@@ -6931,10 +6941,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>477584</v>
+        <v>477585</v>
       </c>
       <c r="R64" t="n">
-        <v>6951542</v>
+        <v>6951573</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6993,7 +7003,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122178237</v>
+        <v>122178232</v>
       </c>
       <c r="B65" t="n">
         <v>80432</v>
@@ -7028,10 +7038,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>477518</v>
+        <v>477570</v>
       </c>
       <c r="R65" t="n">
-        <v>6951490</v>
+        <v>6951563</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7090,7 +7100,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122178243</v>
+        <v>122178234</v>
       </c>
       <c r="B66" t="n">
         <v>80432</v>
@@ -7125,10 +7135,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>477538</v>
+        <v>477584</v>
       </c>
       <c r="R66" t="n">
-        <v>6951448</v>
+        <v>6951542</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7187,7 +7197,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122178246</v>
+        <v>122178237</v>
       </c>
       <c r="B67" t="n">
         <v>80432</v>
@@ -7222,10 +7232,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>477535</v>
+        <v>477518</v>
       </c>
       <c r="R67" t="n">
-        <v>6951442</v>
+        <v>6951490</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7284,7 +7294,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122178247</v>
+        <v>122178243</v>
       </c>
       <c r="B68" t="n">
         <v>80432</v>
@@ -7319,10 +7329,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477540</v>
+        <v>477538</v>
       </c>
       <c r="R68" t="n">
-        <v>6951433</v>
+        <v>6951448</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7381,7 +7391,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125671881</v>
+        <v>122178246</v>
       </c>
       <c r="B69" t="n">
         <v>80432</v>
@@ -7412,17 +7422,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>477440</v>
+        <v>477535</v>
       </c>
       <c r="R69" t="n">
-        <v>6951449</v>
+        <v>6951442</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7446,22 +7456,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>20:39</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>20:39</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7476,19 +7476,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129875243</v>
+        <v>122178247</v>
       </c>
       <c r="B70" t="n">
         <v>80432</v>
@@ -7519,17 +7519,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477625</v>
+        <v>477540</v>
       </c>
       <c r="R70" t="n">
-        <v>6951553</v>
+        <v>6951433</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7573,23 +7573,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129875244</v>
+        <v>125671881</v>
       </c>
       <c r="B71" t="n">
         <v>80432</v>
@@ -7620,14 +7616,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477584</v>
+        <v>477440</v>
       </c>
       <c r="R71" t="n">
-        <v>6951573</v>
+        <v>6951449</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7654,12 +7650,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,23 +7680,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129875245</v>
+        <v>129875243</v>
       </c>
       <c r="B72" t="n">
         <v>80432</v>
@@ -7725,10 +7727,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477568</v>
+        <v>477625</v>
       </c>
       <c r="R72" t="n">
-        <v>6951562</v>
+        <v>6951553</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7791,7 +7793,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129875246</v>
+        <v>129875244</v>
       </c>
       <c r="B73" t="n">
         <v>80432</v>
@@ -7826,10 +7828,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>477517</v>
+        <v>477584</v>
       </c>
       <c r="R73" t="n">
-        <v>6951486</v>
+        <v>6951573</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7892,10 +7894,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134550625</v>
+        <v>129875245</v>
       </c>
       <c r="B74" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7923,17 +7925,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Storstensjön, Storstensjön, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477791</v>
+        <v>477568</v>
       </c>
       <c r="R74" t="n">
-        <v>6951621</v>
+        <v>6951562</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7957,22 +7959,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>19:07</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7987,57 +7979,61 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>103969177</v>
+        <v>129875246</v>
       </c>
       <c r="B75" t="n">
-        <v>79583</v>
+        <v>80432</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477548</v>
+        <v>477517</v>
       </c>
       <c r="R75" t="n">
-        <v>6951437</v>
+        <v>6951486</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8064,22 +8060,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:03</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:03</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8090,73 +8076,68 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>103969161</v>
+        <v>134550625</v>
       </c>
       <c r="B76" t="n">
-        <v>80461</v>
+        <v>80488</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Storstensjön, Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>477549</v>
+        <v>477791</v>
       </c>
       <c r="R76" t="n">
-        <v>6951436</v>
+        <v>6951621</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8180,22 +8161,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8206,35 +8187,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122154197</v>
+        <v>103969177</v>
       </c>
       <c r="B77" t="n">
-        <v>80461</v>
+        <v>79583</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,37 +8214,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>477617</v>
+        <v>477548</v>
       </c>
       <c r="R77" t="n">
-        <v>6951666</v>
+        <v>6951437</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8296,12 +8268,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8312,23 +8294,32 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122154209</v>
+        <v>103969161</v>
       </c>
       <c r="B78" t="n">
         <v>80461</v>
@@ -8359,17 +8350,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>477462</v>
+        <v>477549</v>
       </c>
       <c r="R78" t="n">
-        <v>6951485</v>
+        <v>6951436</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8393,12 +8384,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8409,23 +8410,32 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122154213</v>
+        <v>122154197</v>
       </c>
       <c r="B79" t="n">
         <v>80461</v>
@@ -8460,10 +8470,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>477424</v>
+        <v>477617</v>
       </c>
       <c r="R79" t="n">
-        <v>6951452</v>
+        <v>6951666</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8522,7 +8532,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122154220</v>
+        <v>122154209</v>
       </c>
       <c r="B80" t="n">
         <v>80461</v>
@@ -8557,10 +8567,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>477476</v>
+        <v>477462</v>
       </c>
       <c r="R80" t="n">
-        <v>6951463</v>
+        <v>6951485</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8619,10 +8629,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122154196</v>
+        <v>122154213</v>
       </c>
       <c r="B81" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8630,21 +8640,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8654,10 +8664,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>477621</v>
+        <v>477424</v>
       </c>
       <c r="R81" t="n">
-        <v>6951670</v>
+        <v>6951452</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8716,10 +8726,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>103969189</v>
+        <v>122154220</v>
       </c>
       <c r="B82" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8727,37 +8737,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>477539</v>
+        <v>477476</v>
       </c>
       <c r="R82" t="n">
-        <v>6951435</v>
+        <v>6951463</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8781,22 +8791,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8807,35 +8807,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122178229</v>
+        <v>122154196</v>
       </c>
       <c r="B83" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,21 +8834,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8867,10 +8858,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>477587</v>
+        <v>477621</v>
       </c>
       <c r="R83" t="n">
-        <v>6951569</v>
+        <v>6951670</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8897,12 +8888,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8917,19 +8908,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125671901</v>
+        <v>103969189</v>
       </c>
       <c r="B84" t="n">
         <v>80468</v>
@@ -8960,14 +8951,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>477440</v>
+        <v>477539</v>
       </c>
       <c r="R84" t="n">
-        <v>6951449</v>
+        <v>6951435</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8994,22 +8985,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9020,69 +9011,73 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>103969196</v>
+        <v>122178229</v>
       </c>
       <c r="B85" t="n">
-        <v>57953</v>
+        <v>80468</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>477415</v>
+        <v>477587</v>
       </c>
       <c r="R85" t="n">
-        <v>6951679</v>
+        <v>6951569</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9106,22 +9101,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9132,77 +9117,64 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122154217</v>
+        <v>125671901</v>
       </c>
       <c r="B86" t="n">
-        <v>57953</v>
+        <v>80468</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477473</v>
+        <v>477440</v>
       </c>
       <c r="R86" t="n">
-        <v>6951436</v>
+        <v>6951449</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9226,12 +9198,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9246,19 +9228,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125657630</v>
+        <v>103969196</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -9286,36 +9268,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477442</v>
+        <v>477415</v>
       </c>
       <c r="R87" t="n">
-        <v>6951549</v>
+        <v>6951679</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9339,12 +9310,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9355,23 +9336,32 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125657631</v>
+        <v>122154217</v>
       </c>
       <c r="B88" t="n">
         <v>57953</v>
@@ -9404,31 +9394,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477569</v>
+        <v>477473</v>
       </c>
       <c r="R88" t="n">
-        <v>6951502</v>
+        <v>6951436</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9452,12 +9430,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9472,19 +9450,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125657633</v>
+        <v>125657630</v>
       </c>
       <c r="B89" t="n">
         <v>57953</v>
@@ -9521,7 +9499,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9535,10 +9513,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>477455</v>
+        <v>477442</v>
       </c>
       <c r="R89" t="n">
-        <v>6951481</v>
+        <v>6951549</v>
       </c>
       <c r="S89" t="n">
         <v>50</v>
@@ -9565,12 +9543,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9597,7 +9575,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125663151</v>
+        <v>125657631</v>
       </c>
       <c r="B90" t="n">
         <v>57953</v>
@@ -9625,25 +9603,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>477420</v>
+        <v>477569</v>
       </c>
       <c r="R90" t="n">
-        <v>6951546</v>
+        <v>6951502</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9667,22 +9656,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9697,19 +9676,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125663252</v>
+        <v>125657633</v>
       </c>
       <c r="B91" t="n">
         <v>57953</v>
@@ -9737,25 +9716,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>477408</v>
+        <v>477455</v>
       </c>
       <c r="R91" t="n">
-        <v>6951545</v>
+        <v>6951481</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9779,22 +9769,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9809,19 +9789,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125669436</v>
+        <v>125663151</v>
       </c>
       <c r="B92" t="n">
         <v>57953</v>
@@ -9861,10 +9841,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>477482</v>
+        <v>477420</v>
       </c>
       <c r="R92" t="n">
-        <v>6951702</v>
+        <v>6951546</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9896,7 +9876,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9906,7 +9886,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9933,7 +9913,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125670788</v>
+        <v>125663252</v>
       </c>
       <c r="B93" t="n">
         <v>57953</v>
@@ -9973,10 +9953,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>477403</v>
+        <v>477408</v>
       </c>
       <c r="R93" t="n">
-        <v>6951670</v>
+        <v>6951545</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10008,7 +9988,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10018,7 +9998,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10045,7 +10025,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125757748</v>
+        <v>125669436</v>
       </c>
       <c r="B94" t="n">
         <v>57953</v>
@@ -10081,14 +10061,14 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Storstensjön, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>477491</v>
+        <v>477482</v>
       </c>
       <c r="R94" t="n">
-        <v>6951708</v>
+        <v>6951702</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10118,14 +10098,19 @@
           <t>2025-06-03</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10152,48 +10137,53 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122154172</v>
+        <v>125670788</v>
       </c>
       <c r="B95" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>477879</v>
+        <v>477403</v>
       </c>
       <c r="R95" t="n">
-        <v>6951648</v>
+        <v>6951670</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10217,12 +10207,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10237,60 +10237,65 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122154186</v>
+        <v>125757748</v>
       </c>
       <c r="B96" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>477370</v>
+        <v>477491</v>
       </c>
       <c r="R96" t="n">
-        <v>6951711</v>
+        <v>6951708</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10314,12 +10319,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10334,60 +10344,65 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122154187</v>
+        <v>134592592</v>
       </c>
       <c r="B97" t="n">
-        <v>5179</v>
+        <v>57975</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Storstensjön, Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>477368</v>
+        <v>477445</v>
       </c>
       <c r="R97" t="n">
-        <v>6951718</v>
+        <v>6951715</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10411,12 +10426,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10431,39 +10451,39 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122154169</v>
+        <v>134592666</v>
       </c>
       <c r="B98" t="n">
-        <v>57132</v>
+        <v>57975</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10471,24 +10491,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>477886</v>
+        <v>477463</v>
       </c>
       <c r="R98" t="n">
-        <v>6951641</v>
+        <v>6951738</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10512,12 +10528,27 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10532,22 +10563,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122154215</v>
+        <v>122154172</v>
       </c>
       <c r="B99" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10555,21 +10586,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10579,10 +10610,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>477438</v>
+        <v>477879</v>
       </c>
       <c r="R99" t="n">
-        <v>6951412</v>
+        <v>6951648</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10641,10 +10672,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125657637</v>
+        <v>122154186</v>
       </c>
       <c r="B100" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10652,53 +10683,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>477459</v>
+        <v>477370</v>
       </c>
       <c r="R100" t="n">
-        <v>6951572</v>
+        <v>6951711</v>
       </c>
       <c r="S100" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10722,12 +10737,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10742,22 +10757,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125657638</v>
+        <v>122154187</v>
       </c>
       <c r="B101" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,53 +10780,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>477427</v>
+        <v>477368</v>
       </c>
       <c r="R101" t="n">
-        <v>6951523</v>
+        <v>6951718</v>
       </c>
       <c r="S101" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10835,12 +10834,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10855,22 +10854,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122154224</v>
+        <v>122154169</v>
       </c>
       <c r="B102" t="n">
-        <v>57144</v>
+        <v>57132</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10878,16 +10877,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10895,17 +10894,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477538</v>
+        <v>477886</v>
       </c>
       <c r="R102" t="n">
-        <v>6951618</v>
+        <v>6951641</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10964,27 +10967,27 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125657634</v>
+        <v>122154215</v>
       </c>
       <c r="B103" t="n">
-        <v>57794</v>
+        <v>57132</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>102621</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -10992,36 +10995,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477644</v>
+        <v>477438</v>
       </c>
       <c r="R103" t="n">
-        <v>6951563</v>
+        <v>6951412</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11045,12 +11032,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11065,39 +11052,39 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125657635</v>
+        <v>125657637</v>
       </c>
       <c r="B104" t="n">
-        <v>57794</v>
+        <v>57132</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102621</v>
+        <v>102612</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11128,10 +11115,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477530</v>
+        <v>477459</v>
       </c>
       <c r="R104" t="n">
-        <v>6951481</v>
+        <v>6951572</v>
       </c>
       <c r="S104" t="n">
         <v>50</v>
@@ -11158,12 +11145,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11190,27 +11177,27 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122154170</v>
+        <v>125657638</v>
       </c>
       <c r="B105" t="n">
-        <v>58057</v>
+        <v>57132</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11220,22 +11207,34 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477882</v>
+        <v>477427</v>
       </c>
       <c r="R105" t="n">
-        <v>6951635</v>
+        <v>6951523</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11259,12 +11258,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11279,39 +11278,39 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125657636</v>
+        <v>122154224</v>
       </c>
       <c r="B106" t="n">
-        <v>58057</v>
+        <v>57144</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11320,31 +11319,19 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>477560</v>
+        <v>477538</v>
       </c>
       <c r="R106" t="n">
-        <v>6951544</v>
+        <v>6951618</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11368,12 +11355,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11388,39 +11375,39 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122154193</v>
+        <v>125657634</v>
       </c>
       <c r="B107" t="n">
-        <v>5199</v>
+        <v>57794</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>105930</v>
+        <v>102621</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11428,20 +11415,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477460</v>
+        <v>477644</v>
       </c>
       <c r="R107" t="n">
-        <v>6951750</v>
+        <v>6951563</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11465,12 +11468,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11485,60 +11488,76 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>103969202</v>
+        <v>125657635</v>
       </c>
       <c r="B108" t="n">
-        <v>99035</v>
+        <v>57794</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219790</v>
+        <v>102621</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>477499</v>
+        <v>477530</v>
       </c>
       <c r="R108" t="n">
-        <v>6951560</v>
+        <v>6951481</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11562,22 +11581,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11588,70 +11597,65 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122154160</v>
+        <v>122154170</v>
       </c>
       <c r="B109" t="n">
-        <v>99035</v>
+        <v>58057</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>477847</v>
+        <v>477882</v>
       </c>
       <c r="R109" t="n">
-        <v>6951679</v>
+        <v>6951635</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11710,48 +11714,60 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122154164</v>
+        <v>125657636</v>
       </c>
       <c r="B110" t="n">
-        <v>99035</v>
+        <v>58057</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>477933</v>
+        <v>477560</v>
       </c>
       <c r="R110" t="n">
-        <v>6951709</v>
+        <v>6951544</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11775,12 +11791,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11795,22 +11811,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>103969191</v>
+        <v>122154193</v>
       </c>
       <c r="B111" t="n">
-        <v>99456</v>
+        <v>5199</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11818,37 +11834,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219880</v>
+        <v>105930</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>477557</v>
+        <v>477460</v>
       </c>
       <c r="R111" t="n">
-        <v>6951591</v>
+        <v>6951750</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11872,22 +11888,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11898,35 +11904,26 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>103969199</v>
+        <v>103969202</v>
       </c>
       <c r="B112" t="n">
-        <v>99456</v>
+        <v>99035</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11934,34 +11931,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>477403</v>
+        <v>477499</v>
       </c>
       <c r="R112" t="n">
-        <v>6951589</v>
+        <v>6951560</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11993,7 +11990,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12003,7 +12000,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12039,10 +12036,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122154190</v>
+        <v>122154160</v>
       </c>
       <c r="B113" t="n">
-        <v>99022</v>
+        <v>99035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12050,21 +12047,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12074,10 +12071,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477407</v>
+        <v>477847</v>
       </c>
       <c r="R113" t="n">
-        <v>6951732</v>
+        <v>6951679</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12136,10 +12133,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122154191</v>
+        <v>122154164</v>
       </c>
       <c r="B114" t="n">
-        <v>99022</v>
+        <v>99035</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12147,21 +12144,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12171,10 +12168,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477424</v>
+        <v>477933</v>
       </c>
       <c r="R114" t="n">
-        <v>6951736</v>
+        <v>6951709</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12233,10 +12230,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122154202</v>
+        <v>103969191</v>
       </c>
       <c r="B115" t="n">
-        <v>99022</v>
+        <v>99456</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12244,37 +12241,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477389</v>
+        <v>477557</v>
       </c>
       <c r="R115" t="n">
-        <v>6951610</v>
+        <v>6951591</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12298,12 +12295,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12314,26 +12321,35 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122154204</v>
+        <v>103969199</v>
       </c>
       <c r="B116" t="n">
-        <v>99022</v>
+        <v>99456</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12341,37 +12357,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477373</v>
+        <v>477403</v>
       </c>
       <c r="R116" t="n">
-        <v>6951613</v>
+        <v>6951589</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12395,12 +12411,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12411,23 +12437,32 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122154218</v>
+        <v>122154190</v>
       </c>
       <c r="B117" t="n">
         <v>99022</v>
@@ -12462,10 +12497,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>477479</v>
+        <v>477407</v>
       </c>
       <c r="R117" t="n">
-        <v>6951442</v>
+        <v>6951732</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12524,7 +12559,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122172652</v>
+        <v>122154191</v>
       </c>
       <c r="B118" t="n">
         <v>99022</v>
@@ -12559,10 +12594,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>477755</v>
+        <v>477424</v>
       </c>
       <c r="R118" t="n">
-        <v>6951671</v>
+        <v>6951736</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12609,22 +12644,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129875187</v>
+        <v>122154202</v>
       </c>
       <c r="B119" t="n">
-        <v>97989</v>
+        <v>99022</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12632,41 +12667,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221941</v>
+        <v>220093</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>477586</v>
+        <v>477389</v>
       </c>
       <c r="R119" t="n">
-        <v>6951427</v>
+        <v>6951610</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12690,12 +12721,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12710,26 +12741,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122154205</v>
+        <v>122154204</v>
       </c>
       <c r="B120" t="n">
-        <v>97983</v>
+        <v>99022</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12737,21 +12764,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12761,10 +12788,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>477367</v>
+        <v>477373</v>
       </c>
       <c r="R120" t="n">
-        <v>6951594</v>
+        <v>6951613</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12823,10 +12850,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122172654</v>
+        <v>122154218</v>
       </c>
       <c r="B121" t="n">
-        <v>97983</v>
+        <v>99022</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12834,21 +12861,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12858,10 +12885,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>477639</v>
+        <v>477479</v>
       </c>
       <c r="R121" t="n">
-        <v>6951706</v>
+        <v>6951442</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12908,22 +12935,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122178222</v>
+        <v>122172652</v>
       </c>
       <c r="B122" t="n">
-        <v>97983</v>
+        <v>99022</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12931,21 +12958,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12955,10 +12982,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>477540</v>
+        <v>477755</v>
       </c>
       <c r="R122" t="n">
-        <v>6951594</v>
+        <v>6951671</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12985,12 +13012,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13005,22 +13032,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122178225</v>
+        <v>129875187</v>
       </c>
       <c r="B123" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13028,16 +13055,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13045,20 +13072,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>477580</v>
+        <v>477586</v>
       </c>
       <c r="R123" t="n">
-        <v>6951617</v>
+        <v>6951427</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13082,12 +13113,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13102,22 +13133,26 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>103969155</v>
+        <v>122154205</v>
       </c>
       <c r="B124" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13125,37 +13160,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>477554</v>
+        <v>477367</v>
       </c>
       <c r="R124" t="n">
-        <v>6951438</v>
+        <v>6951594</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13179,22 +13214,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13205,35 +13230,26 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122178248</v>
+        <v>122172654</v>
       </c>
       <c r="B125" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13241,21 +13257,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13265,10 +13281,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>477538</v>
+        <v>477639</v>
       </c>
       <c r="R125" t="n">
-        <v>6951419</v>
+        <v>6951706</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13295,12 +13311,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13315,22 +13331,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129875247</v>
+        <v>122178222</v>
       </c>
       <c r="B126" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13338,41 +13354,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>477516</v>
+        <v>477540</v>
       </c>
       <c r="R126" t="n">
-        <v>6951462</v>
+        <v>6951594</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13396,12 +13408,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13416,26 +13428,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129875248</v>
+        <v>122178225</v>
       </c>
       <c r="B127" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13443,41 +13451,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>477509</v>
+        <v>477580</v>
       </c>
       <c r="R127" t="n">
-        <v>6951422</v>
+        <v>6951617</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13501,12 +13505,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13521,64 +13525,60 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122178235</v>
+        <v>103969155</v>
       </c>
       <c r="B128" t="n">
-        <v>79917</v>
+        <v>99140</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>477573</v>
+        <v>477554</v>
       </c>
       <c r="R128" t="n">
-        <v>6951539</v>
+        <v>6951438</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13602,12 +13602,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13618,48 +13628,57 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122154212</v>
+        <v>122178248</v>
       </c>
       <c r="B129" t="n">
-        <v>92329</v>
+        <v>99140</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6040186</v>
+        <v>221952</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13669,10 +13688,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>477420</v>
+        <v>477538</v>
       </c>
       <c r="R129" t="n">
-        <v>6951455</v>
+        <v>6951419</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13699,12 +13718,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13713,22 +13732,533 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129875247</v>
+      </c>
+      <c r="B130" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>477516</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6951462</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129875248</v>
+      </c>
+      <c r="B131" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>477509</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6951422</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>134590533</v>
+      </c>
+      <c r="B132" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>477586</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6951537</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>122178235</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>477573</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6951539</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>122154212</v>
+      </c>
+      <c r="B134" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>477420</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6951455</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
+      <c r="AX134" t="inlineStr">
         <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AY129" t="inlineStr"/>
+      <c r="AY134" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AY132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10356,53 +10356,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134592592</v>
+        <v>122154172</v>
       </c>
       <c r="B97" t="n">
-        <v>57975</v>
+        <v>5179</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Storstensjön, Storstensjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>477445</v>
+        <v>477879</v>
       </c>
       <c r="R97" t="n">
-        <v>6951715</v>
+        <v>6951648</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10426,17 +10421,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10451,60 +10441,60 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134592666</v>
+        <v>122154186</v>
       </c>
       <c r="B98" t="n">
-        <v>57975</v>
+        <v>5179</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>477463</v>
+        <v>477370</v>
       </c>
       <c r="R98" t="n">
-        <v>6951738</v>
+        <v>6951711</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10528,27 +10518,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10563,19 +10538,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122154172</v>
+        <v>122154187</v>
       </c>
       <c r="B99" t="n">
         <v>5179</v>
@@ -10610,10 +10585,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>477879</v>
+        <v>477368</v>
       </c>
       <c r="R99" t="n">
-        <v>6951648</v>
+        <v>6951718</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10672,10 +10647,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122154186</v>
+        <v>122154169</v>
       </c>
       <c r="B100" t="n">
-        <v>5179</v>
+        <v>57132</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10683,34 +10658,38 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>477370</v>
+        <v>477886</v>
       </c>
       <c r="R100" t="n">
-        <v>6951711</v>
+        <v>6951641</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10769,10 +10748,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122154187</v>
+        <v>122154215</v>
       </c>
       <c r="B101" t="n">
-        <v>5179</v>
+        <v>57132</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10780,21 +10759,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10804,10 +10783,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>477368</v>
+        <v>477438</v>
       </c>
       <c r="R101" t="n">
-        <v>6951718</v>
+        <v>6951412</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10866,7 +10845,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122154169</v>
+        <v>125657637</v>
       </c>
       <c r="B102" t="n">
         <v>57132</v>
@@ -10899,19 +10878,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477886</v>
+        <v>477459</v>
       </c>
       <c r="R102" t="n">
-        <v>6951641</v>
+        <v>6951572</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10935,12 +10926,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10955,19 +10946,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122154215</v>
+        <v>125657638</v>
       </c>
       <c r="B103" t="n">
         <v>57132</v>
@@ -10995,20 +10986,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477438</v>
+        <v>477427</v>
       </c>
       <c r="R103" t="n">
-        <v>6951412</v>
+        <v>6951523</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11032,12 +11039,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11052,22 +11059,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125657637</v>
+        <v>122154224</v>
       </c>
       <c r="B104" t="n">
-        <v>57132</v>
+        <v>57144</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11075,16 +11082,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11092,36 +11099,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477459</v>
+        <v>477538</v>
       </c>
       <c r="R104" t="n">
-        <v>6951572</v>
+        <v>6951618</v>
       </c>
       <c r="S104" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11145,12 +11136,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11165,39 +11156,39 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125657638</v>
+        <v>125657634</v>
       </c>
       <c r="B105" t="n">
-        <v>57132</v>
+        <v>57794</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>102621</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11228,10 +11219,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477427</v>
+        <v>477644</v>
       </c>
       <c r="R105" t="n">
-        <v>6951523</v>
+        <v>6951563</v>
       </c>
       <c r="S105" t="n">
         <v>50</v>
@@ -11258,12 +11249,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11290,27 +11281,27 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122154224</v>
+        <v>125657635</v>
       </c>
       <c r="B106" t="n">
-        <v>57144</v>
+        <v>57794</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>102613</v>
+        <v>102621</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11318,20 +11309,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>477538</v>
+        <v>477530</v>
       </c>
       <c r="R106" t="n">
-        <v>6951618</v>
+        <v>6951481</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11355,12 +11362,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11375,22 +11382,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125657634</v>
+        <v>122154170</v>
       </c>
       <c r="B107" t="n">
-        <v>57794</v>
+        <v>58057</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11398,16 +11405,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102621</v>
+        <v>103031</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11417,34 +11424,22 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477644</v>
+        <v>477882</v>
       </c>
       <c r="R107" t="n">
-        <v>6951563</v>
+        <v>6951635</v>
       </c>
       <c r="S107" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11468,12 +11463,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11488,22 +11483,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125657635</v>
+        <v>125657636</v>
       </c>
       <c r="B108" t="n">
-        <v>57794</v>
+        <v>58057</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11511,16 +11506,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>102621</v>
+        <v>103031</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11528,16 +11523,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -11551,10 +11542,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>477530</v>
+        <v>477560</v>
       </c>
       <c r="R108" t="n">
-        <v>6951481</v>
+        <v>6951544</v>
       </c>
       <c r="S108" t="n">
         <v>50</v>
@@ -11613,27 +11604,27 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122154170</v>
+        <v>122154193</v>
       </c>
       <c r="B109" t="n">
-        <v>58057</v>
+        <v>5199</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103031</v>
+        <v>105930</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -11641,21 +11632,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>477882</v>
+        <v>477460</v>
       </c>
       <c r="R109" t="n">
-        <v>6951635</v>
+        <v>6951750</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11714,60 +11701,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125657636</v>
+        <v>103969202</v>
       </c>
       <c r="B110" t="n">
-        <v>58057</v>
+        <v>99035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>219790</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>477560</v>
+        <v>477499</v>
       </c>
       <c r="R110" t="n">
-        <v>6951544</v>
+        <v>6951560</v>
       </c>
       <c r="S110" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11791,12 +11766,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11807,26 +11792,35 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122154193</v>
+        <v>122154160</v>
       </c>
       <c r="B111" t="n">
-        <v>5199</v>
+        <v>99035</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11834,21 +11828,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>105930</v>
+        <v>219790</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11858,10 +11852,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>477460</v>
+        <v>477847</v>
       </c>
       <c r="R111" t="n">
-        <v>6951750</v>
+        <v>6951679</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11920,7 +11914,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>103969202</v>
+        <v>122154164</v>
       </c>
       <c r="B112" t="n">
         <v>99035</v>
@@ -11951,17 +11945,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>477499</v>
+        <v>477933</v>
       </c>
       <c r="R112" t="n">
-        <v>6951560</v>
+        <v>6951709</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11985,22 +11979,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12011,35 +11995,26 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122154160</v>
+        <v>103969191</v>
       </c>
       <c r="B113" t="n">
-        <v>99035</v>
+        <v>99456</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12047,37 +12022,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477847</v>
+        <v>477557</v>
       </c>
       <c r="R113" t="n">
-        <v>6951679</v>
+        <v>6951591</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12101,12 +12076,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12117,26 +12102,35 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122154164</v>
+        <v>103969199</v>
       </c>
       <c r="B114" t="n">
-        <v>99035</v>
+        <v>99456</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12144,37 +12138,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477933</v>
+        <v>477403</v>
       </c>
       <c r="R114" t="n">
-        <v>6951709</v>
+        <v>6951589</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12198,12 +12192,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12214,26 +12218,35 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>103969191</v>
+        <v>122154190</v>
       </c>
       <c r="B115" t="n">
-        <v>99456</v>
+        <v>99022</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12241,37 +12254,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219880</v>
+        <v>220093</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477557</v>
+        <v>477407</v>
       </c>
       <c r="R115" t="n">
-        <v>6951591</v>
+        <v>6951732</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12295,22 +12308,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12321,35 +12324,26 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>103969199</v>
+        <v>122154191</v>
       </c>
       <c r="B116" t="n">
-        <v>99456</v>
+        <v>99022</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12357,37 +12351,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219880</v>
+        <v>220093</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477403</v>
+        <v>477424</v>
       </c>
       <c r="R116" t="n">
-        <v>6951589</v>
+        <v>6951736</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12411,22 +12405,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12437,32 +12421,23 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122154190</v>
+        <v>122154202</v>
       </c>
       <c r="B117" t="n">
         <v>99022</v>
@@ -12497,10 +12472,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>477407</v>
+        <v>477389</v>
       </c>
       <c r="R117" t="n">
-        <v>6951732</v>
+        <v>6951610</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12559,7 +12534,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122154191</v>
+        <v>122154204</v>
       </c>
       <c r="B118" t="n">
         <v>99022</v>
@@ -12594,10 +12569,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>477424</v>
+        <v>477373</v>
       </c>
       <c r="R118" t="n">
-        <v>6951736</v>
+        <v>6951613</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12656,7 +12631,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122154202</v>
+        <v>122154218</v>
       </c>
       <c r="B119" t="n">
         <v>99022</v>
@@ -12691,10 +12666,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>477389</v>
+        <v>477479</v>
       </c>
       <c r="R119" t="n">
-        <v>6951610</v>
+        <v>6951442</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12753,7 +12728,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122154204</v>
+        <v>122172652</v>
       </c>
       <c r="B120" t="n">
         <v>99022</v>
@@ -12788,10 +12763,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>477373</v>
+        <v>477755</v>
       </c>
       <c r="R120" t="n">
-        <v>6951613</v>
+        <v>6951671</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12838,22 +12813,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122154218</v>
+        <v>129875187</v>
       </c>
       <c r="B121" t="n">
-        <v>99022</v>
+        <v>97989</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12861,37 +12836,41 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220093</v>
+        <v>221941</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>477479</v>
+        <v>477586</v>
       </c>
       <c r="R121" t="n">
-        <v>6951442</v>
+        <v>6951427</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12915,12 +12894,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12935,22 +12914,26 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122172652</v>
+        <v>122154205</v>
       </c>
       <c r="B122" t="n">
-        <v>99022</v>
+        <v>97983</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12958,21 +12941,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220093</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12982,10 +12965,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>477755</v>
+        <v>477367</v>
       </c>
       <c r="R122" t="n">
-        <v>6951671</v>
+        <v>6951594</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13032,22 +13015,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129875187</v>
+        <v>122172654</v>
       </c>
       <c r="B123" t="n">
-        <v>97989</v>
+        <v>97983</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13055,16 +13038,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13072,24 +13055,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>477586</v>
+        <v>477639</v>
       </c>
       <c r="R123" t="n">
-        <v>6951427</v>
+        <v>6951706</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13113,12 +13092,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13133,23 +13112,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122154205</v>
+        <v>122178222</v>
       </c>
       <c r="B124" t="n">
         <v>97983</v>
@@ -13184,7 +13159,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>477367</v>
+        <v>477540</v>
       </c>
       <c r="R124" t="n">
         <v>6951594</v>
@@ -13214,12 +13189,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13234,19 +13209,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122172654</v>
+        <v>122178225</v>
       </c>
       <c r="B125" t="n">
         <v>97983</v>
@@ -13281,10 +13256,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>477639</v>
+        <v>477580</v>
       </c>
       <c r="R125" t="n">
-        <v>6951706</v>
+        <v>6951617</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13311,12 +13286,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13331,22 +13306,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122178222</v>
+        <v>103969155</v>
       </c>
       <c r="B126" t="n">
-        <v>97983</v>
+        <v>99140</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13354,37 +13329,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>477540</v>
+        <v>477554</v>
       </c>
       <c r="R126" t="n">
-        <v>6951594</v>
+        <v>6951438</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13408,12 +13383,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13424,26 +13409,35 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122178225</v>
+        <v>122178248</v>
       </c>
       <c r="B127" t="n">
-        <v>97983</v>
+        <v>99140</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13451,21 +13445,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13475,10 +13469,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>477580</v>
+        <v>477538</v>
       </c>
       <c r="R127" t="n">
-        <v>6951617</v>
+        <v>6951419</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13537,7 +13531,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>103969155</v>
+        <v>129875247</v>
       </c>
       <c r="B128" t="n">
         <v>99140</v>
@@ -13565,17 +13559,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>477554</v>
+        <v>477516</v>
       </c>
       <c r="R128" t="n">
-        <v>6951438</v>
+        <v>6951462</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13602,22 +13600,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13628,32 +13616,27 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122178248</v>
+        <v>129875248</v>
       </c>
       <c r="B129" t="n">
         <v>99140</v>
@@ -13681,20 +13664,24 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>477538</v>
+        <v>477509</v>
       </c>
       <c r="R129" t="n">
-        <v>6951419</v>
+        <v>6951422</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13718,12 +13705,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13738,22 +13725,26 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129875247</v>
+        <v>134590533</v>
       </c>
       <c r="B130" t="n">
-        <v>99140</v>
+        <v>103907</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13761,38 +13752,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>223284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>477516</v>
+        <v>477586</v>
       </c>
       <c r="R130" t="n">
-        <v>6951462</v>
+        <v>6951537</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13819,12 +13806,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13839,68 +13836,60 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129875248</v>
+        <v>122178235</v>
       </c>
       <c r="B131" t="n">
-        <v>99140</v>
+        <v>79917</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221952</v>
+        <v>229821</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>477509</v>
+        <v>477573</v>
       </c>
       <c r="R131" t="n">
-        <v>6951422</v>
+        <v>6951539</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13924,12 +13913,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13944,64 +13933,60 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134590533</v>
+        <v>122154212</v>
       </c>
       <c r="B132" t="n">
-        <v>103907</v>
+        <v>92329</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>223284</v>
+        <v>6040186</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>477586</v>
+        <v>477420</v>
       </c>
       <c r="R132" t="n">
-        <v>6951537</v>
+        <v>6951455</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14025,22 +14010,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14049,216 +14024,22 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>122178235</v>
-      </c>
-      <c r="B133" t="n">
-        <v>79917</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q133" t="n">
-        <v>477573</v>
-      </c>
-      <c r="R133" t="n">
-        <v>6951539</v>
-      </c>
-      <c r="S133" t="n">
-        <v>5</v>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AD133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT133" t="inlineStr"/>
-      <c r="AW133" t="inlineStr">
-        <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>122154212</v>
-      </c>
-      <c r="B134" t="n">
-        <v>92329</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q134" t="n">
-        <v>477420</v>
-      </c>
-      <c r="R134" t="n">
-        <v>6951455</v>
-      </c>
-      <c r="S134" t="n">
-        <v>5</v>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AD134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF134" t="inlineStr"/>
-      <c r="AG134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT134" t="inlineStr"/>
-      <c r="AW134" t="inlineStr">
-        <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY132"/>
+  <dimension ref="A1:AY134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10356,48 +10356,53 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122154172</v>
+        <v>134592592</v>
       </c>
       <c r="B97" t="n">
-        <v>5179</v>
+        <v>57975</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Storstensjön, Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>477879</v>
+        <v>477445</v>
       </c>
       <c r="R97" t="n">
-        <v>6951648</v>
+        <v>6951715</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10421,12 +10426,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10441,60 +10451,60 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122154186</v>
+        <v>134592666</v>
       </c>
       <c r="B98" t="n">
-        <v>5179</v>
+        <v>57975</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>477370</v>
+        <v>477463</v>
       </c>
       <c r="R98" t="n">
-        <v>6951711</v>
+        <v>6951738</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10518,12 +10528,27 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10538,19 +10563,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122154187</v>
+        <v>122154172</v>
       </c>
       <c r="B99" t="n">
         <v>5179</v>
@@ -10585,10 +10610,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>477368</v>
+        <v>477879</v>
       </c>
       <c r="R99" t="n">
-        <v>6951718</v>
+        <v>6951648</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10647,10 +10672,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122154169</v>
+        <v>122154186</v>
       </c>
       <c r="B100" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10658,38 +10683,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>477886</v>
+        <v>477370</v>
       </c>
       <c r="R100" t="n">
-        <v>6951641</v>
+        <v>6951711</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10748,10 +10769,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122154215</v>
+        <v>122154187</v>
       </c>
       <c r="B101" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10759,21 +10780,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10783,10 +10804,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>477438</v>
+        <v>477368</v>
       </c>
       <c r="R101" t="n">
-        <v>6951412</v>
+        <v>6951718</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10845,7 +10866,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125657637</v>
+        <v>122154169</v>
       </c>
       <c r="B102" t="n">
         <v>57132</v>
@@ -10878,31 +10899,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477459</v>
+        <v>477886</v>
       </c>
       <c r="R102" t="n">
-        <v>6951572</v>
+        <v>6951641</v>
       </c>
       <c r="S102" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10926,12 +10935,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10946,19 +10955,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125657638</v>
+        <v>122154215</v>
       </c>
       <c r="B103" t="n">
         <v>57132</v>
@@ -10986,36 +10995,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477427</v>
+        <v>477438</v>
       </c>
       <c r="R103" t="n">
-        <v>6951523</v>
+        <v>6951412</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11039,12 +11032,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11059,22 +11052,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122154224</v>
+        <v>125657637</v>
       </c>
       <c r="B104" t="n">
-        <v>57144</v>
+        <v>57132</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11082,16 +11075,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11099,20 +11092,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477538</v>
+        <v>477459</v>
       </c>
       <c r="R104" t="n">
-        <v>6951618</v>
+        <v>6951572</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11136,12 +11145,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11156,39 +11165,39 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125657634</v>
+        <v>125657638</v>
       </c>
       <c r="B105" t="n">
-        <v>57794</v>
+        <v>57132</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102621</v>
+        <v>102612</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11219,10 +11228,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477644</v>
+        <v>477427</v>
       </c>
       <c r="R105" t="n">
-        <v>6951563</v>
+        <v>6951523</v>
       </c>
       <c r="S105" t="n">
         <v>50</v>
@@ -11249,12 +11258,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11281,27 +11290,27 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125657635</v>
+        <v>122154224</v>
       </c>
       <c r="B106" t="n">
-        <v>57794</v>
+        <v>57144</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>102621</v>
+        <v>102613</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11309,36 +11318,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>477530</v>
+        <v>477538</v>
       </c>
       <c r="R106" t="n">
-        <v>6951481</v>
+        <v>6951618</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11362,12 +11355,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11382,22 +11375,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122154170</v>
+        <v>125657634</v>
       </c>
       <c r="B107" t="n">
-        <v>58057</v>
+        <v>57794</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11405,16 +11398,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11424,22 +11417,34 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477882</v>
+        <v>477644</v>
       </c>
       <c r="R107" t="n">
-        <v>6951635</v>
+        <v>6951563</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11463,12 +11468,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11483,22 +11488,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125657636</v>
+        <v>125657635</v>
       </c>
       <c r="B108" t="n">
-        <v>58057</v>
+        <v>57794</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11506,16 +11511,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11523,12 +11528,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -11542,10 +11551,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>477560</v>
+        <v>477530</v>
       </c>
       <c r="R108" t="n">
-        <v>6951544</v>
+        <v>6951481</v>
       </c>
       <c r="S108" t="n">
         <v>50</v>
@@ -11604,27 +11613,27 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122154193</v>
+        <v>122154170</v>
       </c>
       <c r="B109" t="n">
-        <v>5199</v>
+        <v>58057</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -11632,17 +11641,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>477460</v>
+        <v>477882</v>
       </c>
       <c r="R109" t="n">
-        <v>6951750</v>
+        <v>6951635</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11701,48 +11714,60 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>103969202</v>
+        <v>125657636</v>
       </c>
       <c r="B110" t="n">
-        <v>99035</v>
+        <v>58057</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>477499</v>
+        <v>477560</v>
       </c>
       <c r="R110" t="n">
-        <v>6951560</v>
+        <v>6951544</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11766,22 +11791,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11792,35 +11807,26 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122154160</v>
+        <v>122154193</v>
       </c>
       <c r="B111" t="n">
-        <v>99035</v>
+        <v>5199</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11828,21 +11834,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219790</v>
+        <v>105930</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11852,10 +11858,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>477847</v>
+        <v>477460</v>
       </c>
       <c r="R111" t="n">
-        <v>6951679</v>
+        <v>6951750</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11914,7 +11920,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122154164</v>
+        <v>103969202</v>
       </c>
       <c r="B112" t="n">
         <v>99035</v>
@@ -11945,17 +11951,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>477933</v>
+        <v>477499</v>
       </c>
       <c r="R112" t="n">
-        <v>6951709</v>
+        <v>6951560</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11979,12 +11985,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11995,26 +12011,35 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>103969191</v>
+        <v>122154160</v>
       </c>
       <c r="B113" t="n">
-        <v>99456</v>
+        <v>99035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12022,37 +12047,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477557</v>
+        <v>477847</v>
       </c>
       <c r="R113" t="n">
-        <v>6951591</v>
+        <v>6951679</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12076,22 +12101,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12102,35 +12117,26 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AS113" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>103969199</v>
+        <v>122154164</v>
       </c>
       <c r="B114" t="n">
-        <v>99456</v>
+        <v>99035</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12138,37 +12144,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477403</v>
+        <v>477933</v>
       </c>
       <c r="R114" t="n">
-        <v>6951589</v>
+        <v>6951709</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12192,22 +12198,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12218,35 +12214,26 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122154190</v>
+        <v>103969191</v>
       </c>
       <c r="B115" t="n">
-        <v>99022</v>
+        <v>99456</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12254,37 +12241,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477407</v>
+        <v>477557</v>
       </c>
       <c r="R115" t="n">
-        <v>6951732</v>
+        <v>6951591</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12308,12 +12295,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12324,26 +12321,35 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122154191</v>
+        <v>103969199</v>
       </c>
       <c r="B116" t="n">
-        <v>99022</v>
+        <v>99456</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12351,37 +12357,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477424</v>
+        <v>477403</v>
       </c>
       <c r="R116" t="n">
-        <v>6951736</v>
+        <v>6951589</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12405,12 +12411,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12421,23 +12437,32 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122154202</v>
+        <v>122154190</v>
       </c>
       <c r="B117" t="n">
         <v>99022</v>
@@ -12472,10 +12497,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>477389</v>
+        <v>477407</v>
       </c>
       <c r="R117" t="n">
-        <v>6951610</v>
+        <v>6951732</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12534,7 +12559,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122154204</v>
+        <v>122154191</v>
       </c>
       <c r="B118" t="n">
         <v>99022</v>
@@ -12569,10 +12594,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>477373</v>
+        <v>477424</v>
       </c>
       <c r="R118" t="n">
-        <v>6951613</v>
+        <v>6951736</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12631,7 +12656,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122154218</v>
+        <v>122154202</v>
       </c>
       <c r="B119" t="n">
         <v>99022</v>
@@ -12666,10 +12691,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>477479</v>
+        <v>477389</v>
       </c>
       <c r="R119" t="n">
-        <v>6951442</v>
+        <v>6951610</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12728,7 +12753,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122172652</v>
+        <v>122154204</v>
       </c>
       <c r="B120" t="n">
         <v>99022</v>
@@ -12763,10 +12788,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>477755</v>
+        <v>477373</v>
       </c>
       <c r="R120" t="n">
-        <v>6951671</v>
+        <v>6951613</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12813,22 +12838,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129875187</v>
+        <v>122154218</v>
       </c>
       <c r="B121" t="n">
-        <v>97989</v>
+        <v>99022</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,41 +12861,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221941</v>
+        <v>220093</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>477586</v>
+        <v>477479</v>
       </c>
       <c r="R121" t="n">
-        <v>6951427</v>
+        <v>6951442</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12894,12 +12915,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12914,26 +12935,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122154205</v>
+        <v>122172652</v>
       </c>
       <c r="B122" t="n">
-        <v>97983</v>
+        <v>99022</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12941,21 +12958,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12965,10 +12982,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>477367</v>
+        <v>477755</v>
       </c>
       <c r="R122" t="n">
-        <v>6951594</v>
+        <v>6951671</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13015,22 +13032,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122172654</v>
+        <v>129875187</v>
       </c>
       <c r="B123" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13038,16 +13055,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13055,20 +13072,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>477639</v>
+        <v>477586</v>
       </c>
       <c r="R123" t="n">
-        <v>6951706</v>
+        <v>6951427</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13092,12 +13113,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13112,19 +13133,23 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122178222</v>
+        <v>122154205</v>
       </c>
       <c r="B124" t="n">
         <v>97983</v>
@@ -13159,7 +13184,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>477540</v>
+        <v>477367</v>
       </c>
       <c r="R124" t="n">
         <v>6951594</v>
@@ -13189,12 +13214,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13209,19 +13234,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122178225</v>
+        <v>122172654</v>
       </c>
       <c r="B125" t="n">
         <v>97983</v>
@@ -13256,10 +13281,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>477580</v>
+        <v>477639</v>
       </c>
       <c r="R125" t="n">
-        <v>6951617</v>
+        <v>6951706</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13286,12 +13311,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13306,22 +13331,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>103969155</v>
+        <v>122178222</v>
       </c>
       <c r="B126" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13329,37 +13354,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>477554</v>
+        <v>477540</v>
       </c>
       <c r="R126" t="n">
-        <v>6951438</v>
+        <v>6951594</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13383,22 +13408,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13409,35 +13424,26 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122178248</v>
+        <v>122178225</v>
       </c>
       <c r="B127" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13445,21 +13451,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13469,10 +13475,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>477538</v>
+        <v>477580</v>
       </c>
       <c r="R127" t="n">
-        <v>6951419</v>
+        <v>6951617</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13531,7 +13537,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129875247</v>
+        <v>103969155</v>
       </c>
       <c r="B128" t="n">
         <v>99140</v>
@@ -13559,21 +13565,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>477516</v>
+        <v>477554</v>
       </c>
       <c r="R128" t="n">
-        <v>6951462</v>
+        <v>6951438</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13600,12 +13602,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13616,27 +13628,32 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129875248</v>
+        <v>122178248</v>
       </c>
       <c r="B129" t="n">
         <v>99140</v>
@@ -13664,24 +13681,20 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>477509</v>
+        <v>477538</v>
       </c>
       <c r="R129" t="n">
-        <v>6951422</v>
+        <v>6951419</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13705,12 +13718,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13725,26 +13738,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134590533</v>
+        <v>129875247</v>
       </c>
       <c r="B130" t="n">
-        <v>103907</v>
+        <v>99140</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13752,34 +13761,38 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>223284</v>
+        <v>221952</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>477586</v>
+        <v>477516</v>
       </c>
       <c r="R130" t="n">
-        <v>6951537</v>
+        <v>6951462</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13806,22 +13819,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13836,60 +13839,68 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122178235</v>
+        <v>129875248</v>
       </c>
       <c r="B131" t="n">
-        <v>79917</v>
+        <v>99140</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>477573</v>
+        <v>477509</v>
       </c>
       <c r="R131" t="n">
-        <v>6951539</v>
+        <v>6951422</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13913,12 +13924,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13933,60 +13944,64 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122154212</v>
+        <v>134590533</v>
       </c>
       <c r="B132" t="n">
-        <v>92329</v>
+        <v>103907</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6040186</v>
+        <v>223284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>477420</v>
+        <v>477586</v>
       </c>
       <c r="R132" t="n">
-        <v>6951455</v>
+        <v>6951537</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14010,12 +14025,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14024,22 +14049,216 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>122178235</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>477573</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6951539</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>122154212</v>
+      </c>
+      <c r="B134" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>477420</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6951455</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
+      <c r="AX134" t="inlineStr">
         <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AY132" t="inlineStr"/>
+      <c r="AY134" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AZ134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154211</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134591620</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154189</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154201</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178226</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154207</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657705</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657704</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154175</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154203</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670523</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125666433</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969193</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2171,6 +2246,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178244</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154161</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154208</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2462,6 +2552,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154221</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2569,6 +2664,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671631</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2666,6 +2766,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178224</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2763,6 +2868,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178238</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2860,6 +2970,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178223</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2976,6 +3091,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969200</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3092,6 +3212,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969215</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3189,6 +3314,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122172638</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3286,6 +3416,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154163</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3383,6 +3518,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154173</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3480,6 +3620,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154177</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3577,6 +3722,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154194</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3674,6 +3824,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154200</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3771,6 +3926,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154206</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3868,6 +4028,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178236</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3965,6 +4130,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178249</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4072,6 +4242,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125668481</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4179,6 +4354,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134589951</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4295,6 +4475,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969194</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4411,6 +4596,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969213</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4508,6 +4698,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122107872</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4605,6 +4800,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154188</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4702,6 +4902,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154216</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4799,6 +5004,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178242</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4896,6 +5106,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178245</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5003,6 +5218,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125666274</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5100,6 +5320,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125757747</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5197,6 +5422,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154192</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5313,6 +5543,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969154</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5429,6 +5664,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969203</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5545,6 +5785,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969216</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5642,6 +5887,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154162</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5739,6 +5989,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154171</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5836,6 +6091,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154174</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5933,6 +6193,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154198</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6030,6 +6295,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154210</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6127,6 +6397,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154214</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6224,6 +6499,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154219</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6321,6 +6601,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154225</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6418,6 +6703,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154227</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6515,6 +6805,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122172640</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6612,6 +6907,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178220</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6709,6 +7009,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178221</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6806,6 +7111,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178227</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6903,6 +7213,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178228</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7000,6 +7315,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178231</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7097,6 +7417,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178232</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7194,6 +7519,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178234</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7291,6 +7621,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178237</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7388,6 +7723,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178243</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7485,6 +7825,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178246</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7582,6 +7927,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178247</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7689,6 +8039,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671881</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7790,6 +8145,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875243</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7891,6 +8251,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875244</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7992,6 +8357,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875245</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8093,6 +8463,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875246</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8200,6 +8575,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134550625</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8316,6 +8696,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969177</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8432,6 +8817,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969161</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8529,6 +8919,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154197</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8626,6 +9021,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154209</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8723,6 +9123,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154213</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8820,6 +9225,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154220</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8917,6 +9327,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154196</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9033,6 +9448,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969189</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9130,6 +9550,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178229</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9237,6 +9662,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125671901</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9358,6 +9788,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969196</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9459,6 +9894,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154217</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9572,6 +10012,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657630</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9685,6 +10130,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657631</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9798,6 +10248,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657633</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9910,6 +10365,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125663151</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10022,6 +10482,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125663252</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10134,6 +10599,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125669436</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10246,6 +10716,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125670788</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10353,6 +10828,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125757748</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10460,6 +10940,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134592592</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10572,6 +11057,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134592666</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10669,6 +11159,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154172</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10766,6 +11261,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154186</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10863,6 +11363,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154187</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10964,6 +11469,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154169</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11061,6 +11571,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154215</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11174,6 +11689,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657637</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11287,6 +11807,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657638</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11384,6 +11909,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154224</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11497,6 +12027,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657634</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11610,6 +12145,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657635</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11711,6 +12251,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154170</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11820,6 +12365,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657636</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11917,6 +12467,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154193</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12033,6 +12588,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969202</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12130,6 +12690,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154160</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12227,6 +12792,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154164</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12343,6 +12913,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969191</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12459,6 +13034,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969199</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12556,6 +13136,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154190</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12653,6 +13238,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154191</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12750,6 +13340,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154202</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12847,6 +13442,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154204</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12944,6 +13544,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154218</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13041,6 +13646,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122172652</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13146,6 +13756,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875187</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13243,6 +13858,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154205</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13340,6 +13960,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122172654</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13437,6 +14062,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178222</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13534,6 +14164,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178225</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13650,6 +14285,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969155</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13747,6 +14387,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178248</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13852,6 +14497,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875247</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13957,6 +14607,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875248</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14064,6 +14719,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590533</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14161,6 +14821,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178235</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14259,8 +14924,148 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ134"/>
+  <dimension ref="A1:AZ132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10836,53 +10836,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134592592</v>
+        <v>122154172</v>
       </c>
       <c r="B97" t="n">
-        <v>57975</v>
+        <v>5179</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Storstensjön, Storstensjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>477445</v>
+        <v>477879</v>
       </c>
       <c r="R97" t="n">
-        <v>6951715</v>
+        <v>6951648</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10906,17 +10901,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10931,65 +10921,65 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134592592</t>
+          <t>https://artportalen.se/Sighting/122154172</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134592666</v>
+        <v>122154186</v>
       </c>
       <c r="B98" t="n">
-        <v>57975</v>
+        <v>5179</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kläppsjön, Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>477463</v>
+        <v>477370</v>
       </c>
       <c r="R98" t="n">
-        <v>6951738</v>
+        <v>6951711</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11013,27 +11003,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11048,24 +11023,24 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134592666</t>
+          <t>https://artportalen.se/Sighting/122154186</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122154172</v>
+        <v>122154187</v>
       </c>
       <c r="B99" t="n">
         <v>5179</v>
@@ -11100,10 +11075,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>477879</v>
+        <v>477368</v>
       </c>
       <c r="R99" t="n">
-        <v>6951648</v>
+        <v>6951718</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11161,16 +11136,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154172</t>
+          <t>https://artportalen.se/Sighting/122154187</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122154186</v>
+        <v>122154169</v>
       </c>
       <c r="B100" t="n">
-        <v>5179</v>
+        <v>57132</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11178,34 +11153,38 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>477370</v>
+        <v>477886</v>
       </c>
       <c r="R100" t="n">
-        <v>6951711</v>
+        <v>6951641</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11263,16 +11242,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154186</t>
+          <t>https://artportalen.se/Sighting/122154169</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122154187</v>
+        <v>122154215</v>
       </c>
       <c r="B101" t="n">
-        <v>5179</v>
+        <v>57132</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11280,21 +11259,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11304,10 +11283,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>477368</v>
+        <v>477438</v>
       </c>
       <c r="R101" t="n">
-        <v>6951718</v>
+        <v>6951412</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11365,13 +11344,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154187</t>
+          <t>https://artportalen.se/Sighting/122154215</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122154169</v>
+        <v>125657637</v>
       </c>
       <c r="B102" t="n">
         <v>57132</v>
@@ -11404,19 +11383,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477886</v>
+        <v>477459</v>
       </c>
       <c r="R102" t="n">
-        <v>6951641</v>
+        <v>6951572</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11440,12 +11431,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11460,24 +11451,24 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154169</t>
+          <t>https://artportalen.se/Sighting/125657637</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122154215</v>
+        <v>125657638</v>
       </c>
       <c r="B103" t="n">
         <v>57132</v>
@@ -11505,20 +11496,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477438</v>
+        <v>477427</v>
       </c>
       <c r="R103" t="n">
-        <v>6951412</v>
+        <v>6951523</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11542,12 +11549,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11562,27 +11569,27 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154215</t>
+          <t>https://artportalen.se/Sighting/125657638</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125657637</v>
+        <v>122154224</v>
       </c>
       <c r="B104" t="n">
-        <v>57132</v>
+        <v>57144</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11590,16 +11597,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11607,36 +11614,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477459</v>
+        <v>477538</v>
       </c>
       <c r="R104" t="n">
-        <v>6951572</v>
+        <v>6951618</v>
       </c>
       <c r="S104" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11660,12 +11651,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11680,44 +11671,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657637</t>
+          <t>https://artportalen.se/Sighting/122154224</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125657638</v>
+        <v>125657634</v>
       </c>
       <c r="B105" t="n">
-        <v>57132</v>
+        <v>57794</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>102621</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11748,10 +11739,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477427</v>
+        <v>477644</v>
       </c>
       <c r="R105" t="n">
-        <v>6951523</v>
+        <v>6951563</v>
       </c>
       <c r="S105" t="n">
         <v>50</v>
@@ -11778,12 +11769,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11809,33 +11800,33 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657638</t>
+          <t>https://artportalen.se/Sighting/125657634</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>122154224</v>
+        <v>125657635</v>
       </c>
       <c r="B106" t="n">
-        <v>57144</v>
+        <v>57794</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>102613</v>
+        <v>102621</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11843,20 +11834,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>477538</v>
+        <v>477530</v>
       </c>
       <c r="R106" t="n">
-        <v>6951618</v>
+        <v>6951481</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11880,12 +11887,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11900,27 +11907,27 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154224</t>
+          <t>https://artportalen.se/Sighting/125657635</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125657634</v>
+        <v>122154170</v>
       </c>
       <c r="B107" t="n">
-        <v>57794</v>
+        <v>58057</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11928,16 +11935,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102621</v>
+        <v>103031</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11947,34 +11954,22 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477644</v>
+        <v>477882</v>
       </c>
       <c r="R107" t="n">
-        <v>6951563</v>
+        <v>6951635</v>
       </c>
       <c r="S107" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11998,12 +11993,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12018,27 +12013,27 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657634</t>
+          <t>https://artportalen.se/Sighting/122154170</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125657635</v>
+        <v>125657636</v>
       </c>
       <c r="B108" t="n">
-        <v>57794</v>
+        <v>58057</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12046,16 +12041,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>102621</v>
+        <v>103031</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12063,16 +12058,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -12086,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>477530</v>
+        <v>477560</v>
       </c>
       <c r="R108" t="n">
-        <v>6951481</v>
+        <v>6951544</v>
       </c>
       <c r="S108" t="n">
         <v>50</v>
@@ -12147,33 +12138,33 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657635</t>
+          <t>https://artportalen.se/Sighting/125657636</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122154170</v>
+        <v>122154193</v>
       </c>
       <c r="B109" t="n">
-        <v>58057</v>
+        <v>5199</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103031</v>
+        <v>105930</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12181,21 +12172,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>477882</v>
+        <v>477460</v>
       </c>
       <c r="R109" t="n">
-        <v>6951635</v>
+        <v>6951750</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12253,66 +12240,54 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154170</t>
+          <t>https://artportalen.se/Sighting/122154193</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125657636</v>
+        <v>103969202</v>
       </c>
       <c r="B110" t="n">
-        <v>58057</v>
+        <v>99035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>219790</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>477560</v>
+        <v>477499</v>
       </c>
       <c r="R110" t="n">
-        <v>6951544</v>
+        <v>6951560</v>
       </c>
       <c r="S110" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12336,12 +12311,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12352,31 +12337,40 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657636</t>
+          <t>https://artportalen.se/Sighting/103969202</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122154193</v>
+        <v>122154160</v>
       </c>
       <c r="B111" t="n">
-        <v>5199</v>
+        <v>99035</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12384,21 +12378,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>105930</v>
+        <v>219790</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12408,10 +12402,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>477460</v>
+        <v>477847</v>
       </c>
       <c r="R111" t="n">
-        <v>6951750</v>
+        <v>6951679</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12469,13 +12463,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154193</t>
+          <t>https://artportalen.se/Sighting/122154160</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>103969202</v>
+        <v>122154164</v>
       </c>
       <c r="B112" t="n">
         <v>99035</v>
@@ -12506,17 +12500,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>477499</v>
+        <v>477933</v>
       </c>
       <c r="R112" t="n">
-        <v>6951560</v>
+        <v>6951709</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12540,22 +12534,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12566,40 +12550,31 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103969202</t>
+          <t>https://artportalen.se/Sighting/122154164</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122154160</v>
+        <v>103969191</v>
       </c>
       <c r="B113" t="n">
-        <v>99035</v>
+        <v>99456</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12607,37 +12582,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477847</v>
+        <v>477557</v>
       </c>
       <c r="R113" t="n">
-        <v>6951679</v>
+        <v>6951591</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12661,12 +12636,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12677,31 +12662,40 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154160</t>
+          <t>https://artportalen.se/Sighting/103969191</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122154164</v>
+        <v>103969199</v>
       </c>
       <c r="B114" t="n">
-        <v>99035</v>
+        <v>99456</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12709,37 +12703,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477933</v>
+        <v>477403</v>
       </c>
       <c r="R114" t="n">
-        <v>6951709</v>
+        <v>6951589</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12763,12 +12757,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12779,31 +12783,40 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154164</t>
+          <t>https://artportalen.se/Sighting/103969199</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>103969191</v>
+        <v>122154190</v>
       </c>
       <c r="B115" t="n">
-        <v>99456</v>
+        <v>99022</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12811,37 +12824,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219880</v>
+        <v>220093</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477557</v>
+        <v>477407</v>
       </c>
       <c r="R115" t="n">
-        <v>6951591</v>
+        <v>6951732</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12865,22 +12878,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12891,40 +12894,31 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103969191</t>
+          <t>https://artportalen.se/Sighting/122154190</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>103969199</v>
+        <v>122154191</v>
       </c>
       <c r="B116" t="n">
-        <v>99456</v>
+        <v>99022</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12932,37 +12926,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219880</v>
+        <v>220093</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477403</v>
+        <v>477424</v>
       </c>
       <c r="R116" t="n">
-        <v>6951589</v>
+        <v>6951736</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12986,22 +12980,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13012,37 +12996,28 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103969199</t>
+          <t>https://artportalen.se/Sighting/122154191</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122154190</v>
+        <v>122154202</v>
       </c>
       <c r="B117" t="n">
         <v>99022</v>
@@ -13077,10 +13052,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>477407</v>
+        <v>477389</v>
       </c>
       <c r="R117" t="n">
-        <v>6951732</v>
+        <v>6951610</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13138,13 +13113,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154190</t>
+          <t>https://artportalen.se/Sighting/122154202</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122154191</v>
+        <v>122154204</v>
       </c>
       <c r="B118" t="n">
         <v>99022</v>
@@ -13179,10 +13154,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>477424</v>
+        <v>477373</v>
       </c>
       <c r="R118" t="n">
-        <v>6951736</v>
+        <v>6951613</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13240,13 +13215,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154191</t>
+          <t>https://artportalen.se/Sighting/122154204</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122154202</v>
+        <v>122154218</v>
       </c>
       <c r="B119" t="n">
         <v>99022</v>
@@ -13281,10 +13256,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>477389</v>
+        <v>477479</v>
       </c>
       <c r="R119" t="n">
-        <v>6951610</v>
+        <v>6951442</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13342,13 +13317,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154202</t>
+          <t>https://artportalen.se/Sighting/122154218</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122154204</v>
+        <v>122172652</v>
       </c>
       <c r="B120" t="n">
         <v>99022</v>
@@ -13383,10 +13358,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>477373</v>
+        <v>477755</v>
       </c>
       <c r="R120" t="n">
-        <v>6951613</v>
+        <v>6951671</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13433,27 +13408,27 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154204</t>
+          <t>https://artportalen.se/Sighting/122172652</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>122154218</v>
+        <v>129875187</v>
       </c>
       <c r="B121" t="n">
-        <v>99022</v>
+        <v>97989</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13461,37 +13436,41 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220093</v>
+        <v>221941</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>477479</v>
+        <v>477586</v>
       </c>
       <c r="R121" t="n">
-        <v>6951442</v>
+        <v>6951427</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13515,12 +13494,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13535,27 +13514,31 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154218</t>
+          <t>https://artportalen.se/Sighting/129875187</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122172652</v>
+        <v>122154205</v>
       </c>
       <c r="B122" t="n">
-        <v>99022</v>
+        <v>97983</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13563,21 +13546,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220093</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13587,10 +13570,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>477755</v>
+        <v>477367</v>
       </c>
       <c r="R122" t="n">
-        <v>6951671</v>
+        <v>6951594</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13637,27 +13620,27 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122172652</t>
+          <t>https://artportalen.se/Sighting/122154205</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129875187</v>
+        <v>122172654</v>
       </c>
       <c r="B123" t="n">
-        <v>97989</v>
+        <v>97983</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13665,16 +13648,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13682,24 +13665,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>477586</v>
+        <v>477639</v>
       </c>
       <c r="R123" t="n">
-        <v>6951427</v>
+        <v>6951706</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13723,12 +13702,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13743,28 +13722,24 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129875187</t>
+          <t>https://artportalen.se/Sighting/122172654</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122154205</v>
+        <v>122178222</v>
       </c>
       <c r="B124" t="n">
         <v>97983</v>
@@ -13799,7 +13774,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>477367</v>
+        <v>477540</v>
       </c>
       <c r="R124" t="n">
         <v>6951594</v>
@@ -13829,12 +13804,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13849,24 +13824,24 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154205</t>
+          <t>https://artportalen.se/Sighting/122178222</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122172654</v>
+        <v>122178225</v>
       </c>
       <c r="B125" t="n">
         <v>97983</v>
@@ -13901,10 +13876,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>477639</v>
+        <v>477580</v>
       </c>
       <c r="R125" t="n">
-        <v>6951706</v>
+        <v>6951617</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13931,12 +13906,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13951,27 +13926,27 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122172654</t>
+          <t>https://artportalen.se/Sighting/122178225</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122178222</v>
+        <v>103969155</v>
       </c>
       <c r="B126" t="n">
-        <v>97983</v>
+        <v>99140</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13979,37 +13954,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>477540</v>
+        <v>477554</v>
       </c>
       <c r="R126" t="n">
-        <v>6951594</v>
+        <v>6951438</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14033,12 +14008,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14049,31 +14034,40 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122178222</t>
+          <t>https://artportalen.se/Sighting/103969155</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122178225</v>
+        <v>122178248</v>
       </c>
       <c r="B127" t="n">
-        <v>97983</v>
+        <v>99140</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14081,21 +14075,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14105,10 +14099,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>477580</v>
+        <v>477538</v>
       </c>
       <c r="R127" t="n">
-        <v>6951617</v>
+        <v>6951419</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14166,13 +14160,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122178225</t>
+          <t>https://artportalen.se/Sighting/122178248</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>103969155</v>
+        <v>129875247</v>
       </c>
       <c r="B128" t="n">
         <v>99140</v>
@@ -14200,17 +14194,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>477554</v>
+        <v>477516</v>
       </c>
       <c r="R128" t="n">
-        <v>6951438</v>
+        <v>6951462</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14237,22 +14235,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14263,37 +14251,32 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103969155</t>
+          <t>https://artportalen.se/Sighting/129875247</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122178248</v>
+        <v>129875248</v>
       </c>
       <c r="B129" t="n">
         <v>99140</v>
@@ -14321,20 +14304,24 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>477538</v>
+        <v>477509</v>
       </c>
       <c r="R129" t="n">
-        <v>6951419</v>
+        <v>6951422</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14358,12 +14345,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14378,27 +14365,31 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122178248</t>
+          <t>https://artportalen.se/Sighting/129875248</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129875247</v>
+        <v>134590533</v>
       </c>
       <c r="B130" t="n">
-        <v>99140</v>
+        <v>103907</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14406,38 +14397,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>223284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>477516</v>
+        <v>477586</v>
       </c>
       <c r="R130" t="n">
-        <v>6951462</v>
+        <v>6951537</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14464,12 +14451,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14484,73 +14481,65 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129875247</t>
+          <t>https://artportalen.se/Sighting/134590533</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129875248</v>
+        <v>122178235</v>
       </c>
       <c r="B131" t="n">
-        <v>99140</v>
+        <v>79917</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221952</v>
+        <v>229821</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>477509</v>
+        <v>477573</v>
       </c>
       <c r="R131" t="n">
-        <v>6951422</v>
+        <v>6951539</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14574,12 +14563,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14594,69 +14583,65 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129875248</t>
+          <t>https://artportalen.se/Sighting/122178235</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134590533</v>
+        <v>122154212</v>
       </c>
       <c r="B132" t="n">
-        <v>103907</v>
+        <v>92329</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>223284</v>
+        <v>6040186</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>477586</v>
+        <v>477420</v>
       </c>
       <c r="R132" t="n">
-        <v>6951537</v>
+        <v>6951455</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14680,22 +14665,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14704,227 +14679,23 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134590533</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>122178235</v>
-      </c>
-      <c r="B133" t="n">
-        <v>79917</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q133" t="n">
-        <v>477573</v>
-      </c>
-      <c r="R133" t="n">
-        <v>6951539</v>
-      </c>
-      <c r="S133" t="n">
-        <v>5</v>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AD133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT133" t="inlineStr"/>
-      <c r="AW133" t="inlineStr">
-        <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/122178235</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>122154212</v>
-      </c>
-      <c r="B134" t="n">
-        <v>92329</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q134" t="n">
-        <v>477420</v>
-      </c>
-      <c r="R134" t="n">
-        <v>6951455</v>
-      </c>
-      <c r="S134" t="n">
-        <v>5</v>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AD134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF134" t="inlineStr"/>
-      <c r="AG134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT134" t="inlineStr"/>
-      <c r="AW134" t="inlineStr">
-        <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
-      <c r="AZ134" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122154212</t>
         </is>
@@ -15063,8 +14834,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17919-2024 artfynd.xlsx
+++ b/artfynd/A 17919-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ132"/>
+  <dimension ref="A1:AZ134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10836,48 +10836,53 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122154172</v>
+        <v>134592592</v>
       </c>
       <c r="B97" t="n">
-        <v>5179</v>
+        <v>57980</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Storstensjön, Storstensjön, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>477879</v>
+        <v>477445</v>
       </c>
       <c r="R97" t="n">
-        <v>6951648</v>
+        <v>6951715</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10901,12 +10906,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10921,65 +10931,65 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154172</t>
+          <t>https://artportalen.se/Sighting/134592592</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122154186</v>
+        <v>134592666</v>
       </c>
       <c r="B98" t="n">
-        <v>5179</v>
+        <v>57980</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>477370</v>
+        <v>477463</v>
       </c>
       <c r="R98" t="n">
-        <v>6951711</v>
+        <v>6951738</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11003,12 +11013,27 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11023,24 +11048,24 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154186</t>
+          <t>https://artportalen.se/Sighting/134592666</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122154187</v>
+        <v>122154172</v>
       </c>
       <c r="B99" t="n">
         <v>5179</v>
@@ -11075,10 +11100,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>477368</v>
+        <v>477879</v>
       </c>
       <c r="R99" t="n">
-        <v>6951718</v>
+        <v>6951648</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11136,16 +11161,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154187</t>
+          <t>https://artportalen.se/Sighting/122154172</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122154169</v>
+        <v>122154186</v>
       </c>
       <c r="B100" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11153,38 +11178,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>477886</v>
+        <v>477370</v>
       </c>
       <c r="R100" t="n">
-        <v>6951641</v>
+        <v>6951711</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11242,16 +11263,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154169</t>
+          <t>https://artportalen.se/Sighting/122154186</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122154215</v>
+        <v>122154187</v>
       </c>
       <c r="B101" t="n">
-        <v>57132</v>
+        <v>5179</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11259,21 +11280,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11283,10 +11304,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>477438</v>
+        <v>477368</v>
       </c>
       <c r="R101" t="n">
-        <v>6951412</v>
+        <v>6951718</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11344,13 +11365,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154215</t>
+          <t>https://artportalen.se/Sighting/122154187</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125657637</v>
+        <v>122154169</v>
       </c>
       <c r="B102" t="n">
         <v>57132</v>
@@ -11383,31 +11404,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>477459</v>
+        <v>477886</v>
       </c>
       <c r="R102" t="n">
-        <v>6951572</v>
+        <v>6951641</v>
       </c>
       <c r="S102" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11431,12 +11440,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11451,24 +11460,24 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657637</t>
+          <t>https://artportalen.se/Sighting/122154169</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125657638</v>
+        <v>122154215</v>
       </c>
       <c r="B103" t="n">
         <v>57132</v>
@@ -11496,36 +11505,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>477427</v>
+        <v>477438</v>
       </c>
       <c r="R103" t="n">
-        <v>6951523</v>
+        <v>6951412</v>
       </c>
       <c r="S103" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11549,12 +11542,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11569,27 +11562,27 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657638</t>
+          <t>https://artportalen.se/Sighting/122154215</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122154224</v>
+        <v>125657637</v>
       </c>
       <c r="B104" t="n">
-        <v>57144</v>
+        <v>57132</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11597,16 +11590,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11614,20 +11607,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>477538</v>
+        <v>477459</v>
       </c>
       <c r="R104" t="n">
-        <v>6951618</v>
+        <v>6951572</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11651,12 +11660,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11671,44 +11680,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154224</t>
+          <t>https://artportalen.se/Sighting/125657637</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125657634</v>
+        <v>125657638</v>
       </c>
       <c r="B105" t="n">
-        <v>57794</v>
+        <v>57132</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102621</v>
+        <v>102612</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11739,10 +11748,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>477644</v>
+        <v>477427</v>
       </c>
       <c r="R105" t="n">
-        <v>6951563</v>
+        <v>6951523</v>
       </c>
       <c r="S105" t="n">
         <v>50</v>
@@ -11769,12 +11778,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11800,33 +11809,33 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657634</t>
+          <t>https://artportalen.se/Sighting/125657638</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125657635</v>
+        <v>122154224</v>
       </c>
       <c r="B106" t="n">
-        <v>57794</v>
+        <v>57144</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>102621</v>
+        <v>102613</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11834,36 +11843,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>477530</v>
+        <v>477538</v>
       </c>
       <c r="R106" t="n">
-        <v>6951481</v>
+        <v>6951618</v>
       </c>
       <c r="S106" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11887,12 +11880,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11907,27 +11900,27 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Via Samuel Persson</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657635</t>
+          <t>https://artportalen.se/Sighting/122154224</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122154170</v>
+        <v>125657634</v>
       </c>
       <c r="B107" t="n">
-        <v>58057</v>
+        <v>57794</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11935,16 +11928,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11954,22 +11947,34 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>477882</v>
+        <v>477644</v>
       </c>
       <c r="R107" t="n">
-        <v>6951635</v>
+        <v>6951563</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11993,12 +11998,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12013,27 +12018,27 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Via Samuel Persson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154170</t>
+          <t>https://artportalen.se/Sighting/125657634</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125657636</v>
+        <v>125657635</v>
       </c>
       <c r="B108" t="n">
-        <v>58057</v>
+        <v>57794</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12041,16 +12046,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12058,12 +12063,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -12077,10 +12086,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>477560</v>
+        <v>477530</v>
       </c>
       <c r="R108" t="n">
-        <v>6951544</v>
+        <v>6951481</v>
       </c>
       <c r="S108" t="n">
         <v>50</v>
@@ -12138,33 +12147,33 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125657636</t>
+          <t>https://artportalen.se/Sighting/125657635</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>122154193</v>
+        <v>122154170</v>
       </c>
       <c r="B109" t="n">
-        <v>5199</v>
+        <v>58057</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12172,17 +12181,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>477460</v>
+        <v>477882</v>
       </c>
       <c r="R109" t="n">
-        <v>6951750</v>
+        <v>6951635</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12240,54 +12253,66 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154193</t>
+          <t>https://artportalen.se/Sighting/122154170</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>103969202</v>
+        <v>125657636</v>
       </c>
       <c r="B110" t="n">
-        <v>99035</v>
+        <v>58057</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>477499</v>
+        <v>477560</v>
       </c>
       <c r="R110" t="n">
-        <v>6951560</v>
+        <v>6951544</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12311,22 +12336,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>09:18</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12337,40 +12352,31 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Via Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103969202</t>
+          <t>https://artportalen.se/Sighting/125657636</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122154160</v>
+        <v>122154193</v>
       </c>
       <c r="B111" t="n">
-        <v>99035</v>
+        <v>5199</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12378,21 +12384,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219790</v>
+        <v>105930</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12402,10 +12408,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>477847</v>
+        <v>477460</v>
       </c>
       <c r="R111" t="n">
-        <v>6951679</v>
+        <v>6951750</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12463,13 +12469,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154160</t>
+          <t>https://artportalen.se/Sighting/122154193</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122154164</v>
+        <v>103969202</v>
       </c>
       <c r="B112" t="n">
         <v>99035</v>
@@ -12500,17 +12506,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>477933</v>
+        <v>477499</v>
       </c>
       <c r="R112" t="n">
-        <v>6951709</v>
+        <v>6951560</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12534,12 +12540,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12550,31 +12566,40 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154164</t>
+          <t>https://artportalen.se/Sighting/103969202</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>103969191</v>
+        <v>122154160</v>
       </c>
       <c r="B113" t="n">
-        <v>99456</v>
+        <v>99035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12582,37 +12607,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Piprörflon, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>477557</v>
+        <v>477847</v>
       </c>
       <c r="R113" t="n">
-        <v>6951591</v>
+        <v>6951679</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12636,22 +12661,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12662,40 +12677,31 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AS113" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103969191</t>
+          <t>https://artportalen.se/Sighting/122154160</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>103969199</v>
+        <v>122154164</v>
       </c>
       <c r="B114" t="n">
-        <v>99456</v>
+        <v>99035</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12703,37 +12709,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>477403</v>
+        <v>477933</v>
       </c>
       <c r="R114" t="n">
-        <v>6951589</v>
+        <v>6951709</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12757,22 +12763,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12783,40 +12779,31 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103969199</t>
+          <t>https://artportalen.se/Sighting/122154164</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122154190</v>
+        <v>103969191</v>
       </c>
       <c r="B115" t="n">
-        <v>99022</v>
+        <v>99456</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12824,37 +12811,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Piprörflon, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>477407</v>
+        <v>477557</v>
       </c>
       <c r="R115" t="n">
-        <v>6951732</v>
+        <v>6951591</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12878,12 +12865,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12894,31 +12891,40 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154190</t>
+          <t>https://artportalen.se/Sighting/103969191</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122154191</v>
+        <v>103969199</v>
       </c>
       <c r="B116" t="n">
-        <v>99022</v>
+        <v>99456</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12926,37 +12932,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220093</v>
+        <v>219880</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>477424</v>
+        <v>477403</v>
       </c>
       <c r="R116" t="n">
-        <v>6951736</v>
+        <v>6951589</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12980,12 +12986,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12996,28 +13012,37 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154191</t>
+          <t>https://artportalen.se/Sighting/103969199</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122154202</v>
+        <v>122154190</v>
       </c>
       <c r="B117" t="n">
         <v>99022</v>
@@ -13052,10 +13077,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>477389</v>
+        <v>477407</v>
       </c>
       <c r="R117" t="n">
-        <v>6951610</v>
+        <v>6951732</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13113,13 +13138,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154202</t>
+          <t>https://artportalen.se/Sighting/122154190</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>122154204</v>
+        <v>122154191</v>
       </c>
       <c r="B118" t="n">
         <v>99022</v>
@@ -13154,10 +13179,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>477373</v>
+        <v>477424</v>
       </c>
       <c r="R118" t="n">
-        <v>6951613</v>
+        <v>6951736</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13215,13 +13240,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154204</t>
+          <t>https://artportalen.se/Sighting/122154191</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>122154218</v>
+        <v>122154202</v>
       </c>
       <c r="B119" t="n">
         <v>99022</v>
@@ -13256,10 +13281,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>477479</v>
+        <v>477389</v>
       </c>
       <c r="R119" t="n">
-        <v>6951442</v>
+        <v>6951610</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13317,13 +13342,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154218</t>
+          <t>https://artportalen.se/Sighting/122154202</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122172652</v>
+        <v>122154204</v>
       </c>
       <c r="B120" t="n">
         <v>99022</v>
@@ -13358,10 +13383,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>477755</v>
+        <v>477373</v>
       </c>
       <c r="R120" t="n">
-        <v>6951671</v>
+        <v>6951613</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13408,27 +13433,27 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122172652</t>
+          <t>https://artportalen.se/Sighting/122154204</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129875187</v>
+        <v>122154218</v>
       </c>
       <c r="B121" t="n">
-        <v>97989</v>
+        <v>99022</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13436,41 +13461,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221941</v>
+        <v>220093</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>477586</v>
+        <v>477479</v>
       </c>
       <c r="R121" t="n">
-        <v>6951427</v>
+        <v>6951442</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13494,12 +13515,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13514,31 +13535,27 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129875187</t>
+          <t>https://artportalen.se/Sighting/122154218</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122154205</v>
+        <v>122172652</v>
       </c>
       <c r="B122" t="n">
-        <v>97983</v>
+        <v>99022</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13546,21 +13563,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13570,10 +13587,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>477367</v>
+        <v>477755</v>
       </c>
       <c r="R122" t="n">
-        <v>6951594</v>
+        <v>6951671</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13620,27 +13637,27 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122154205</t>
+          <t>https://artportalen.se/Sighting/122172652</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122172654</v>
+        <v>129875187</v>
       </c>
       <c r="B123" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13648,16 +13665,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13665,20 +13682,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>477639</v>
+        <v>477586</v>
       </c>
       <c r="R123" t="n">
-        <v>6951706</v>
+        <v>6951427</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13702,12 +13723,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13722,24 +13743,28 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122172654</t>
+          <t>https://artportalen.se/Sighting/129875187</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>122178222</v>
+        <v>122154205</v>
       </c>
       <c r="B124" t="n">
         <v>97983</v>
@@ -13774,7 +13799,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>477540</v>
+        <v>477367</v>
       </c>
       <c r="R124" t="n">
         <v>6951594</v>
@@ -13804,12 +13829,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13824,24 +13849,24 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122178222</t>
+          <t>https://artportalen.se/Sighting/122154205</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>122178225</v>
+        <v>122172654</v>
       </c>
       <c r="B125" t="n">
         <v>97983</v>
@@ -13876,10 +13901,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>477580</v>
+        <v>477639</v>
       </c>
       <c r="R125" t="n">
-        <v>6951617</v>
+        <v>6951706</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13906,12 +13931,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13926,27 +13951,27 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122178225</t>
+          <t>https://artportalen.se/Sighting/122172654</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>103969155</v>
+        <v>122178222</v>
       </c>
       <c r="B126" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13954,37 +13979,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Kläppsjön, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>477554</v>
+        <v>477540</v>
       </c>
       <c r="R126" t="n">
-        <v>6951438</v>
+        <v>6951594</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14008,22 +14033,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14034,40 +14049,31 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103969155</t>
+          <t>https://artportalen.se/Sighting/122178222</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122178248</v>
+        <v>122178225</v>
       </c>
       <c r="B127" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14075,21 +14081,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14099,10 +14105,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>477538</v>
+        <v>477580</v>
       </c>
       <c r="R127" t="n">
-        <v>6951419</v>
+        <v>6951617</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14160,13 +14166,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122178248</t>
+          <t>https://artportalen.se/Sighting/122178225</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129875247</v>
+        <v>103969155</v>
       </c>
       <c r="B128" t="n">
         <v>99140</v>
@@ -14194,21 +14200,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Kläppsjön, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>477516</v>
+        <v>477554</v>
       </c>
       <c r="R128" t="n">
-        <v>6951462</v>
+        <v>6951438</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14235,12 +14237,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2022-06-10</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14251,32 +14263,37 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129875247</t>
+          <t>https://artportalen.se/Sighting/103969155</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129875248</v>
+        <v>122178248</v>
       </c>
       <c r="B129" t="n">
         <v>99140</v>
@@ -14304,24 +14321,20 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>477509</v>
+        <v>477538</v>
       </c>
       <c r="R129" t="n">
-        <v>6951422</v>
+        <v>6951419</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14345,12 +14358,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14365,31 +14378,27 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129875248</t>
+          <t>https://artportalen.se/Sighting/122178248</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134590533</v>
+        <v>129875247</v>
       </c>
       <c r="B130" t="n">
-        <v>103907</v>
+        <v>99140</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14397,34 +14406,38 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>223284</v>
+        <v>221952</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>477586</v>
+        <v>477516</v>
       </c>
       <c r="R130" t="n">
-        <v>6951537</v>
+        <v>6951462</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14451,22 +14464,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>12:51</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14481,65 +14484,73 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134590533</t>
+          <t>https://artportalen.se/Sighting/129875247</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122178235</v>
+        <v>129875248</v>
       </c>
       <c r="B131" t="n">
-        <v>79917</v>
+        <v>99140</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>477573</v>
+        <v>477509</v>
       </c>
       <c r="R131" t="n">
-        <v>6951539</v>
+        <v>6951422</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14563,12 +14574,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14583,65 +14594,69 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122178235</t>
+          <t>https://artportalen.se/Sighting/129875248</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122154212</v>
+        <v>134590533</v>
       </c>
       <c r="B132" t="n">
-        <v>92329</v>
+        <v>103907</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6040186</v>
+        <v>223284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Kläppbergets naturreservat, Kläppbergets naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>477420</v>
+        <v>477586</v>
       </c>
       <c r="R132" t="n">
-        <v>6951455</v>
+        <v>6951537</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14665,12 +14680,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14679,23 +14704,227 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134590533</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>122178235</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>477573</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6951539</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122178235</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>122154212</v>
+      </c>
+      <c r="B134" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>477420</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6951455</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122154212</t>
         </is>
@@ -14834,6 +15063,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
